--- a/supplementary/Supplementary_Table_3_Trajectory_TwoAxis_LAM.xlsx
+++ b/supplementary/Supplementary_Table_3_Trajectory_TwoAxis_LAM.xlsx
@@ -12,21 +12,24 @@
     <sheet name="Continuum_states" sheetId="3" state="visible" r:id="rId3"/>
     <sheet name="Trajectory_topology" sheetId="4" state="visible" r:id="rId4"/>
     <sheet name="Method_concordance" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="Donor_jackknife" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="Multiroot_audit" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet name="Two_axis_donors" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet name="Two_axis_disease" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet name="Two_axis_meta" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet name="Threshold_grid" sheetId="11" state="visible" r:id="rId11"/>
-    <sheet name="LAM_signature_ledger" sheetId="12" state="visible" r:id="rId12"/>
-    <sheet name="LAM_availability" sheetId="13" state="visible" r:id="rId13"/>
-    <sheet name="LAM_donor_scores" sheetId="14" state="visible" r:id="rId14"/>
-    <sheet name="LAM_pair_tests" sheetId="15" state="visible" r:id="rId15"/>
-    <sheet name="LAM_meta" sheetId="16" state="visible" r:id="rId16"/>
+    <sheet name="Multiroot_endpoint_AUC" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="External_projection_topology" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="Donor_jackknife" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="Multiroot_audit" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet name="Two_axis_donors" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet name="Two_axis_disease" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet name="Two_axis_meta" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet name="Two_axis_meta_discovery" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet name="Threshold_grid" sheetId="14" state="visible" r:id="rId14"/>
+    <sheet name="LAM_signature_ledger" sheetId="15" state="visible" r:id="rId15"/>
+    <sheet name="LAM_availability" sheetId="16" state="visible" r:id="rId16"/>
+    <sheet name="LAM_donor_scores" sheetId="17" state="visible" r:id="rId17"/>
+    <sheet name="LAM_pair_tests" sheetId="18" state="visible" r:id="rId18"/>
+    <sheet name="LAM_meta" sheetId="19" state="visible" r:id="rId19"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Overview'!$A$10:$F$25</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">'Overview'!$A$1:$F$25</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Overview'!$A$10:$F$28</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">'Overview'!$A$1:$F$28</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Continuum_sampling'!$A$4:$E$191</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="1">'Continuum_sampling'!$1:$4</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="1">'Continuum_sampling'!$A$1:$E$191</definedName>
@@ -39,39 +42,48 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Method_concordance'!$A$4:$D$52</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="4">'Method_concordance'!$1:$4</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="4">'Method_concordance'!$A$1:$D$52</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'Donor_jackknife'!$A$4:$I$80</definedName>
-    <definedName name="_xlnm.Print_Titles" localSheetId="5">'Donor_jackknife'!$1:$4</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="5">'Donor_jackknife'!$A$1:$I$80</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'Multiroot_audit'!$A$4:$I$7</definedName>
-    <definedName name="_xlnm.Print_Titles" localSheetId="6">'Multiroot_audit'!$1:$4</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="6">'Multiroot_audit'!$A$1:$I$7</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'Two_axis_donors'!$A$4:$R$31</definedName>
-    <definedName name="_xlnm.Print_Titles" localSheetId="7">'Two_axis_donors'!$1:$4</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="7">'Two_axis_donors'!$A$1:$R$31</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">'Two_axis_disease'!$A$4:$K$26</definedName>
-    <definedName name="_xlnm.Print_Titles" localSheetId="8">'Two_axis_disease'!$1:$4</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="8">'Two_axis_disease'!$A$1:$K$26</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="9" hidden="1">'Two_axis_meta'!$A$4:$G$15</definedName>
-    <definedName name="_xlnm.Print_Titles" localSheetId="9">'Two_axis_meta'!$1:$4</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="9">'Two_axis_meta'!$A$1:$G$15</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="10" hidden="1">'Threshold_grid'!$A$4:$G$24</definedName>
-    <definedName name="_xlnm.Print_Titles" localSheetId="10">'Threshold_grid'!$1:$4</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="10">'Threshold_grid'!$A$1:$G$24</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="11" hidden="1">'LAM_signature_ledger'!$A$4:$I$52</definedName>
-    <definedName name="_xlnm.Print_Titles" localSheetId="11">'LAM_signature_ledger'!$1:$4</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="11">'LAM_signature_ledger'!$A$1:$I$52</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="12" hidden="1">'LAM_availability'!$A$4:$F$20</definedName>
-    <definedName name="_xlnm.Print_Titles" localSheetId="12">'LAM_availability'!$1:$4</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="12">'LAM_availability'!$A$1:$F$20</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="13" hidden="1">'LAM_donor_scores'!$A$4:$AG$72</definedName>
-    <definedName name="_xlnm.Print_Titles" localSheetId="13">'LAM_donor_scores'!$1:$4</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="13">'LAM_donor_scores'!$A$1:$AG$72</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="14" hidden="1">'LAM_pair_tests'!$A$4:$I$19</definedName>
-    <definedName name="_xlnm.Print_Titles" localSheetId="14">'LAM_pair_tests'!$1:$4</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="14">'LAM_pair_tests'!$A$1:$I$19</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="15" hidden="1">'LAM_meta'!$A$4:$G$9</definedName>
-    <definedName name="_xlnm.Print_Titles" localSheetId="15">'LAM_meta'!$1:$4</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="15">'LAM_meta'!$A$1:$G$9</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'Multiroot_endpoint_AUC'!$A$4:$L$10</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="5">'Multiroot_endpoint_AUC'!$1:$4</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="5">'Multiroot_endpoint_AUC'!$A$1:$L$10</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'External_projection_topology'!$A$4:$G$5</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="6">'External_projection_topology'!$1:$4</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="6">'External_projection_topology'!$A$1:$G$5</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'Donor_jackknife'!$A$4:$I$80</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="7">'Donor_jackknife'!$1:$4</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="7">'Donor_jackknife'!$A$1:$I$80</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">'Multiroot_audit'!$A$4:$I$7</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="8">'Multiroot_audit'!$1:$4</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="8">'Multiroot_audit'!$A$1:$I$7</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="9" hidden="1">'Two_axis_donors'!$A$4:$R$31</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="9">'Two_axis_donors'!$1:$4</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="9">'Two_axis_donors'!$A$1:$R$31</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="10" hidden="1">'Two_axis_disease'!$A$4:$K$26</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="10">'Two_axis_disease'!$1:$4</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="10">'Two_axis_disease'!$A$1:$K$26</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="11" hidden="1">'Two_axis_meta'!$A$4:$G$6</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="11">'Two_axis_meta'!$1:$4</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="11">'Two_axis_meta'!$A$1:$G$6</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="12" hidden="1">'Two_axis_meta_discovery'!$A$4:$G$15</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="12">'Two_axis_meta_discovery'!$1:$4</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="12">'Two_axis_meta_discovery'!$A$1:$G$15</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="13" hidden="1">'Threshold_grid'!$A$4:$G$24</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="13">'Threshold_grid'!$1:$4</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="13">'Threshold_grid'!$A$1:$G$24</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="14" hidden="1">'LAM_signature_ledger'!$A$4:$I$52</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="14">'LAM_signature_ledger'!$1:$4</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="14">'LAM_signature_ledger'!$A$1:$I$52</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="15" hidden="1">'LAM_availability'!$A$4:$F$20</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="15">'LAM_availability'!$1:$4</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="15">'LAM_availability'!$A$1:$F$20</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="16" hidden="1">'LAM_donor_scores'!$A$4:$AG$72</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="16">'LAM_donor_scores'!$1:$4</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="16">'LAM_donor_scores'!$A$1:$AG$72</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="17" hidden="1">'LAM_pair_tests'!$A$4:$I$19</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="17">'LAM_pair_tests'!$1:$4</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="17">'LAM_pair_tests'!$A$1:$I$19</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="18" hidden="1">'LAM_meta'!$A$4:$G$9</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="18">'LAM_meta'!$1:$4</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="18">'LAM_meta'!$A$1:$G$9</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -328,7 +340,59 @@
 </file>
 
 <file path=xl/tables/table10.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="10" name="T_Threshold_grid" displayName="T_Threshold_grid" ref="A4:G24" headerRowCount="1">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="10" name="T_Two_axis_disease" displayName="T_Two_axis_disease" ref="A4:K26" headerRowCount="1">
+  <autoFilter ref="A4:K26"/>
+  <tableColumns count="11">
+    <tableColumn id="1" name="dataset"/>
+    <tableColumn id="2" name="metric"/>
+    <tableColumn id="3" name="n_MS"/>
+    <tableColumn id="4" name="n_control"/>
+    <tableColumn id="5" name="mean_MS"/>
+    <tableColumn id="6" name="mean_control"/>
+    <tableColumn id="7" name="mean_difference_MS_minus_control"/>
+    <tableColumn id="8" name="standardized_mean_difference"/>
+    <tableColumn id="9" name="cliffs_delta"/>
+    <tableColumn id="10" name="exact_permutation_p"/>
+    <tableColumn id="11" name="fdr_bh_within_dataset"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table11.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="11" name="T_Two_axis_meta" displayName="T_Two_axis_meta" ref="A4:G6" headerRowCount="1">
+  <autoFilter ref="A4:G6"/>
+  <tableColumns count="7">
+    <tableColumn id="1" name="endpoint"/>
+    <tableColumn id="2" name="n_cohorts"/>
+    <tableColumn id="3" name="direction_concordant"/>
+    <tableColumn id="4" name="combined_z"/>
+    <tableColumn id="5" name="stouffer_p"/>
+    <tableColumn id="6" name="mean_standardized_effect"/>
+    <tableColumn id="7" name="fdr_bh"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table12.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="12" name="T_Two_axis_meta_discovery" displayName="T_Two_axis_meta_discovery" ref="A4:G15" headerRowCount="1">
+  <autoFilter ref="A4:G15"/>
+  <tableColumns count="7">
+    <tableColumn id="1" name="metric"/>
+    <tableColumn id="2" name="n_cohorts"/>
+    <tableColumn id="3" name="direction_concordant"/>
+    <tableColumn id="4" name="combined_z"/>
+    <tableColumn id="5" name="stouffer_p"/>
+    <tableColumn id="6" name="mean_standardized_effect"/>
+    <tableColumn id="7" name="fdr_bh"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table13.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="13" name="T_Threshold_grid" displayName="T_Threshold_grid" ref="A4:G24" headerRowCount="1">
   <autoFilter ref="A4:G24"/>
   <tableColumns count="7">
     <tableColumn id="1" name="pseudotime_cutoff"/>
@@ -343,8 +407,8 @@
 </table>
 </file>
 
-<file path=xl/tables/table11.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="11" name="T_LAM_signature_ledger" displayName="T_LAM_signature_ledger" ref="A4:I52" headerRowCount="1">
+<file path=xl/tables/table14.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="14" name="T_LAM_signature_ledger" displayName="T_LAM_signature_ledger" ref="A4:I52" headerRowCount="1">
   <autoFilter ref="A4:I52"/>
   <tableColumns count="9">
     <tableColumn id="1" name="signature"/>
@@ -361,8 +425,8 @@
 </table>
 </file>
 
-<file path=xl/tables/table12.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="12" name="T_LAM_availability" displayName="T_LAM_availability" ref="A4:F20" headerRowCount="1">
+<file path=xl/tables/table15.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="15" name="T_LAM_availability" displayName="T_LAM_availability" ref="A4:F20" headerRowCount="1">
   <autoFilter ref="A4:F20"/>
   <tableColumns count="6">
     <tableColumn id="1" name="dataset"/>
@@ -376,8 +440,8 @@
 </table>
 </file>
 
-<file path=xl/tables/table13.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="13" name="T_LAM_donor_scores" displayName="T_LAM_donor_scores" ref="A4:AG72" headerRowCount="1">
+<file path=xl/tables/table16.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="16" name="T_LAM_donor_scores" displayName="T_LAM_donor_scores" ref="A4:AG72" headerRowCount="1">
   <autoFilter ref="A4:AG72"/>
   <tableColumns count="33">
     <tableColumn id="1" name="dataset"/>
@@ -418,8 +482,8 @@
 </table>
 </file>
 
-<file path=xl/tables/table14.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="14" name="T_LAM_pair_tests" displayName="T_LAM_pair_tests" ref="A4:I19" headerRowCount="1">
+<file path=xl/tables/table17.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="17" name="T_LAM_pair_tests" displayName="T_LAM_pair_tests" ref="A4:I19" headerRowCount="1">
   <autoFilter ref="A4:I19"/>
   <tableColumns count="9">
     <tableColumn id="1" name="dataset"/>
@@ -436,8 +500,8 @@
 </table>
 </file>
 
-<file path=xl/tables/table15.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="15" name="T_LAM_meta" displayName="T_LAM_meta" ref="A4:G9" headerRowCount="1">
+<file path=xl/tables/table18.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="18" name="T_LAM_meta" displayName="T_LAM_meta" ref="A4:G9" headerRowCount="1">
   <autoFilter ref="A4:G9"/>
   <tableColumns count="7">
     <tableColumn id="1" name="endpoint"/>
@@ -510,7 +574,44 @@
 </file>
 
 <file path=xl/tables/table5.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="5" name="T_Donor_jackknife" displayName="T_Donor_jackknife" ref="A4:I80" headerRowCount="1">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="5" name="T_Multiroot_endpoint_AUC" displayName="T_Multiroot_endpoint_AUC" ref="A4:L10" headerRowCount="1">
+  <autoFilter ref="A4:L10"/>
+  <tableColumns count="12">
+    <tableColumn id="1" name="dataset"/>
+    <tableColumn id="2" name="representation"/>
+    <tableColumn id="3" name="method"/>
+    <tableColumn id="4" name="n_cells"/>
+    <tableColumn id="5" name="n_subjects"/>
+    <tableColumn id="6" name="n_root_donors"/>
+    <tableColumn id="7" name="n_root"/>
+    <tableColumn id="8" name="n_terminal"/>
+    <tableColumn id="9" name="full_terminal_vs_root_auc"/>
+    <tableColumn id="10" name="score_column"/>
+    <tableColumn id="11" name="source"/>
+    <tableColumn id="12" name="comparison"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table6.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="6" name="T_External_projection_topology" displayName="T_External_projection_topology" ref="A4:G5" headerRowCount="1">
+  <autoFilter ref="A4:G5"/>
+  <tableColumns count="7">
+    <tableColumn id="1" name="n_cells"/>
+    <tableColumn id="2" name="n_subjects"/>
+    <tableColumn id="3" name="n_root"/>
+    <tableColumn id="4" name="n_terminal"/>
+    <tableColumn id="5" name="state_order_spearman"/>
+    <tableColumn id="6" name="terminal_vs_root_auc"/>
+    <tableColumn id="7" name="terminal_score_cutpoint_from_discovery"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table7.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="7" name="T_Donor_jackknife" displayName="T_Donor_jackknife" ref="A4:I80" headerRowCount="1">
   <autoFilter ref="A4:I80"/>
   <tableColumns count="9">
     <tableColumn id="1" name="dataset"/>
@@ -527,8 +628,8 @@
 </table>
 </file>
 
-<file path=xl/tables/table6.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="6" name="T_Multiroot_audit" displayName="T_Multiroot_audit" ref="A4:I7" headerRowCount="1">
+<file path=xl/tables/table8.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="8" name="T_Multiroot_audit" displayName="T_Multiroot_audit" ref="A4:I7" headerRowCount="1">
   <autoFilter ref="A4:I7"/>
   <tableColumns count="9">
     <tableColumn id="1" name="dataset"/>
@@ -545,8 +646,8 @@
 </table>
 </file>
 
-<file path=xl/tables/table7.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="7" name="T_Two_axis_donors" displayName="T_Two_axis_donors" ref="A4:R31" headerRowCount="1">
+<file path=xl/tables/table9.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="9" name="T_Two_axis_donors" displayName="T_Two_axis_donors" ref="A4:R31" headerRowCount="1">
   <autoFilter ref="A4:R31"/>
   <tableColumns count="18">
     <tableColumn id="1" name="dataset"/>
@@ -567,42 +668,6 @@
     <tableColumn id="16" name="decoupled_inflammatory_fraction"/>
     <tableColumn id="17" name="continuous_decoupling_index"/>
     <tableColumn id="18" name="strict_BAM_mean_activation_residual"/>
-  </tableColumns>
-  <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
-</table>
-</file>
-
-<file path=xl/tables/table8.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="8" name="T_Two_axis_disease" displayName="T_Two_axis_disease" ref="A4:K26" headerRowCount="1">
-  <autoFilter ref="A4:K26"/>
-  <tableColumns count="11">
-    <tableColumn id="1" name="dataset"/>
-    <tableColumn id="2" name="metric"/>
-    <tableColumn id="3" name="n_MS"/>
-    <tableColumn id="4" name="n_control"/>
-    <tableColumn id="5" name="mean_MS"/>
-    <tableColumn id="6" name="mean_control"/>
-    <tableColumn id="7" name="mean_difference_MS_minus_control"/>
-    <tableColumn id="8" name="standardized_mean_difference"/>
-    <tableColumn id="9" name="cliffs_delta"/>
-    <tableColumn id="10" name="exact_permutation_p"/>
-    <tableColumn id="11" name="fdr_bh_within_dataset"/>
-  </tableColumns>
-  <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
-</table>
-</file>
-
-<file path=xl/tables/table9.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="9" name="T_Two_axis_meta" displayName="T_Two_axis_meta" ref="A4:G15" headerRowCount="1">
-  <autoFilter ref="A4:G15"/>
-  <tableColumns count="7">
-    <tableColumn id="1" name="metric"/>
-    <tableColumn id="2" name="n_cohorts"/>
-    <tableColumn id="3" name="direction_concordant"/>
-    <tableColumn id="4" name="combined_z"/>
-    <tableColumn id="5" name="stouffer_p"/>
-    <tableColumn id="6" name="mean_standardized_effect"/>
-    <tableColumn id="7" name="fdr_bh"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -897,7 +962,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:F25"/>
+  <dimension ref="A1:F28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -1034,7 +1099,7 @@
       </c>
       <c r="B13" s="7" t="inlineStr">
         <is>
-          <t>Root-to-terminal topology audit.</t>
+          <t>Single-root DPT and independent topology diagnostics; separate from the multiroot Figure 1e baseline.</t>
         </is>
       </c>
       <c r="C13" s="7" t="inlineStr">
@@ -1062,7 +1127,7 @@
       </c>
       <c r="B14" s="9" t="inlineStr">
         <is>
-          <t>Within-donor concordance of trajectory representations.</t>
+          <t>Within-cohort cell-level Spearman correlations among four trajectory representations; 48 entries from three 4-by-4 matrices, not donor comparisons.</t>
         </is>
       </c>
       <c r="C14" s="9" t="inlineStr">
@@ -1085,313 +1150,397 @@
     <row r="15">
       <c r="A15" s="6" t="inlineStr">
         <is>
-          <t>Donor_jackknife</t>
+          <t>Multiroot_endpoint_AUC</t>
         </is>
       </c>
       <c r="B15" s="7" t="inlineStr">
         <is>
-          <t>Leave-one-donor trajectory reconstruction audit.</t>
+          <t>Full-cohort multiroot DPT endpoint AUCs from saved cell scores; primary representation supplies the Figure 1e baseline.</t>
         </is>
       </c>
       <c r="C15" s="7" t="inlineStr">
         <is>
-          <t>results/trajectory/trajectory_donor_jackknife.csv</t>
+          <t>results/trajectory/full_multiroot_endpoint_auc.csv</t>
         </is>
       </c>
       <c r="D15" s="8" t="n">
-        <v>76</v>
+        <v>6</v>
       </c>
       <c r="E15" s="8" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="F15" s="7" t="inlineStr">
         <is>
-          <t>af4b9ea14146958549f5dbe5c2a318bdc1063dad0dac607748f220fa6a7e3b9a</t>
+          <t>b4a4b53717f3fb6f925f6607ac5c1290acda8035e5c34bc0cd78278c0049a312</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="6" t="inlineStr">
         <is>
-          <t>Multiroot_audit</t>
+          <t>External_projection_topology</t>
         </is>
       </c>
       <c r="B16" s="9" t="inlineStr">
         <is>
-          <t>Sensitivity to a multi-donor root definition.</t>
+          <t>External fixed-score projection: correlation with annotated state ordering and classical-monocyte versus BAM-like endpoint AUC.</t>
         </is>
       </c>
       <c r="C16" s="9" t="inlineStr">
         <is>
-          <t>results/trajectory/multiroot_DPT_qc.csv</t>
+          <t>results/external_validation/GSE328265_two_axis_projection/external_projection_topology.csv</t>
         </is>
       </c>
       <c r="D16" s="10" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E16" s="10" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="F16" s="9" t="inlineStr">
         <is>
-          <t>e79c4740e1a446f358bc55233f44ec9be9afbf3aac01b57364f31b1d4474c769</t>
+          <t>0f6d39a810e8351a9b08d3d804006a07bc3ca9961b4e525e2997ba81f7b1e619</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="6" t="inlineStr">
         <is>
-          <t>Two_axis_donors</t>
+          <t>Donor_jackknife</t>
         </is>
       </c>
       <c r="B17" s="7" t="inlineStr">
         <is>
-          <t>Donor-level differentiation, activation residual and decoupling scores.</t>
+          <t>Leave-one-donor trajectory reconstruction audit.</t>
         </is>
       </c>
       <c r="C17" s="7" t="inlineStr">
         <is>
-          <t>results/two_axis/two_axis_donor_scores.csv</t>
+          <t>results/trajectory/trajectory_donor_jackknife.csv</t>
         </is>
       </c>
       <c r="D17" s="8" t="n">
-        <v>27</v>
+        <v>76</v>
       </c>
       <c r="E17" s="8" t="n">
-        <v>18</v>
+        <v>9</v>
       </c>
       <c r="F17" s="7" t="inlineStr">
         <is>
-          <t>dc81d4211fb9f714a2abee6a12ce5f830fec24cb4b6c864625bad3e549de7476</t>
+          <t>af4b9ea14146958549f5dbe5c2a318bdc1063dad0dac607748f220fa6a7e3b9a</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="6" t="inlineStr">
         <is>
-          <t>Two_axis_disease</t>
+          <t>Multiroot_audit</t>
         </is>
       </c>
       <c r="B18" s="9" t="inlineStr">
         <is>
-          <t>Within-cohort disease tests for the two-axis endpoints.</t>
+          <t>Multi-donor-root DPT: gene-set concordance and correlations with annotated state ordering.</t>
         </is>
       </c>
       <c r="C18" s="9" t="inlineStr">
         <is>
-          <t>results/two_axis/two_axis_disease_tests.csv</t>
+          <t>results/trajectory/multiroot_DPT_qc.csv</t>
         </is>
       </c>
       <c r="D18" s="10" t="n">
-        <v>22</v>
+        <v>3</v>
       </c>
       <c r="E18" s="10" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="F18" s="9" t="inlineStr">
         <is>
-          <t>0187f79462824bd3214ae0929eaf1371b0fe83728a4ae38237c7b02ba238cbbb</t>
+          <t>e79c4740e1a446f358bc55233f44ec9be9afbf3aac01b57364f31b1d4474c769</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="6" t="inlineStr">
         <is>
-          <t>Two_axis_meta</t>
+          <t>Two_axis_donors</t>
         </is>
       </c>
       <c r="B19" s="7" t="inlineStr">
         <is>
-          <t>Cross-cohort two-axis meta-analysis.</t>
+          <t>Donor-level differentiation, activation residual and decoupling scores.</t>
         </is>
       </c>
       <c r="C19" s="7" t="inlineStr">
         <is>
-          <t>results/two_axis/two_axis_meta_tests.csv</t>
+          <t>results/two_axis/two_axis_donor_scores.csv</t>
         </is>
       </c>
       <c r="D19" s="8" t="n">
-        <v>11</v>
+        <v>27</v>
       </c>
       <c r="E19" s="8" t="n">
-        <v>7</v>
+        <v>18</v>
       </c>
       <c r="F19" s="7" t="inlineStr">
         <is>
-          <t>1601158215458bc7ef2c7c99b677766b96cc783e2b69922a9565256ae9ffd0d5</t>
+          <t>dc81d4211fb9f714a2abee6a12ce5f830fec24cb4b6c864625bad3e549de7476</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="6" t="inlineStr">
         <is>
-          <t>Threshold_grid</t>
+          <t>Two_axis_disease</t>
         </is>
       </c>
       <c r="B20" s="9" t="inlineStr">
         <is>
-          <t>Prespecified decoupling-threshold sensitivity grid.</t>
+          <t>Within-cohort disease tests for the two-axis endpoints.</t>
         </is>
       </c>
       <c r="C20" s="9" t="inlineStr">
         <is>
-          <t>results/two_axis/decoupling_threshold_meta_grid.csv</t>
+          <t>results/two_axis/two_axis_disease_tests.csv</t>
         </is>
       </c>
       <c r="D20" s="10" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="E20" s="10" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="F20" s="9" t="inlineStr">
         <is>
-          <t>ece0f9ed9b93d93f77d0ddc93494c3a4c3bfb2d566932056b73fcfea81d867b2</t>
+          <t>0187f79462824bd3214ae0929eaf1371b0fe83728a4ae38237c7b02ba238cbbb</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="6" t="inlineStr">
         <is>
-          <t>LAM_signature_ledger</t>
+          <t>Two_axis_meta</t>
         </is>
       </c>
       <c r="B21" s="7" t="inlineStr">
         <is>
-          <t>Mouse program membership and human ortholog ledger.</t>
+          <t>Primary disease meta-analysis across GSE138266, GSE286068 and new GSE328265 participants; BH correction across the two prespecified endpoints.</t>
         </is>
       </c>
       <c r="C21" s="7" t="inlineStr">
         <is>
-          <t>results/cross_species_lam/meningeal_LAM_signature_ledger.csv</t>
+          <t>results/external_validation/GSE328265_two_axis_projection/three_cohort_two_axis_meta.csv</t>
         </is>
       </c>
       <c r="D21" s="8" t="n">
-        <v>48</v>
+        <v>2</v>
       </c>
       <c r="E21" s="8" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="F21" s="7" t="inlineStr">
         <is>
-          <t>2aee74df75600d683e86b3d2937c2ada9376849b5e504de90d781e9120258bfa</t>
+          <t>9b83afe02b86923117b314322a20dfa5346a660e5c2f09f6f3a30bef11512567</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="6" t="inlineStr">
         <is>
-          <t>LAM_availability</t>
+          <t>Two_axis_meta_discovery</t>
         </is>
       </c>
       <c r="B22" s="9" t="inlineStr">
         <is>
-          <t>Per-cohort availability of ortholog-mapped LAM genes.</t>
+          <t>Discovery-only two-cohort meta-analysis across 11 two-axis endpoints; BH correction across this 11-test family.</t>
         </is>
       </c>
       <c r="C22" s="9" t="inlineStr">
         <is>
-          <t>results/cross_species_lam/LAM_signature_availability.csv</t>
+          <t>results/two_axis/two_axis_meta_tests.csv</t>
         </is>
       </c>
       <c r="D22" s="10" t="n">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="E22" s="10" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F22" s="9" t="inlineStr">
         <is>
-          <t>5317411ff3d8f042d1a667486070b578b33bd7b3d3d7d624c742eff5b326c124</t>
+          <t>1601158215458bc7ef2c7c99b677766b96cc783e2b69922a9565256ae9ffd0d5</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="6" t="inlineStr">
         <is>
-          <t>LAM_donor_scores</t>
+          <t>Threshold_grid</t>
         </is>
       </c>
       <c r="B23" s="7" t="inlineStr">
         <is>
-          <t>Donor-level raw and differentiation-adjusted LAM program scores.</t>
+          <t>Decoupling-threshold sensitivity grid in the two disease discovery cohorts, GSE138266 and GSE286068.</t>
         </is>
       </c>
       <c r="C23" s="7" t="inlineStr">
         <is>
-          <t>results/cross_species_lam/LAM_donor_scores.csv</t>
+          <t>results/two_axis/decoupling_threshold_meta_grid.csv</t>
         </is>
       </c>
       <c r="D23" s="8" t="n">
-        <v>68</v>
+        <v>20</v>
       </c>
       <c r="E23" s="8" t="n">
-        <v>33</v>
+        <v>7</v>
       </c>
       <c r="F23" s="7" t="inlineStr">
         <is>
-          <t>5078790d7c7a2c5f3e8e6b5b8fdd9fd7f6469dbaf60b380105405351adada815</t>
+          <t>ece0f9ed9b93d93f77d0ddc93494c3a4c3bfb2d566932056b73fcfea81d867b2</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="6" t="inlineStr">
         <is>
-          <t>LAM_pair_tests</t>
+          <t>LAM_signature_ledger</t>
         </is>
       </c>
       <c r="B24" s="9" t="inlineStr">
         <is>
-          <t>Within-cohort donor-paired decoupled-state LAM tests.</t>
+          <t>Mouse program membership and human ortholog ledger.</t>
         </is>
       </c>
       <c r="C24" s="9" t="inlineStr">
         <is>
-          <t>results/cross_species_lam/LAM_decoupled_pair_tests.csv</t>
+          <t>results/cross_species_lam/meningeal_LAM_signature_ledger.csv</t>
         </is>
       </c>
       <c r="D24" s="10" t="n">
-        <v>15</v>
+        <v>48</v>
       </c>
       <c r="E24" s="10" t="n">
         <v>9</v>
       </c>
       <c r="F24" s="9" t="inlineStr">
         <is>
-          <t>a9592eda3f001460e6aa51f8a495dd526b56a89a95db97472bd52713394339a9</t>
+          <t>2aee74df75600d683e86b3d2937c2ada9376849b5e504de90d781e9120258bfa</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="6" t="inlineStr">
         <is>
+          <t>LAM_availability</t>
+        </is>
+      </c>
+      <c r="B25" s="7" t="inlineStr">
+        <is>
+          <t>Per-cohort availability of requested scoring genes in the human LAM and ortholog-mapped mouse programs.</t>
+        </is>
+      </c>
+      <c r="C25" s="7" t="inlineStr">
+        <is>
+          <t>results/cross_species_lam/LAM_signature_availability.csv</t>
+        </is>
+      </c>
+      <c r="D25" s="8" t="n">
+        <v>16</v>
+      </c>
+      <c r="E25" s="8" t="n">
+        <v>6</v>
+      </c>
+      <c r="F25" s="7" t="inlineStr">
+        <is>
+          <t>5317411ff3d8f042d1a667486070b578b33bd7b3d3d7d624c742eff5b326c124</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="6" t="inlineStr">
+        <is>
+          <t>LAM_donor_scores</t>
+        </is>
+      </c>
+      <c r="B26" s="9" t="inlineStr">
+        <is>
+          <t>Donor-level raw and differentiation-adjusted LAM program scores.</t>
+        </is>
+      </c>
+      <c r="C26" s="9" t="inlineStr">
+        <is>
+          <t>results/cross_species_lam/LAM_donor_scores.csv</t>
+        </is>
+      </c>
+      <c r="D26" s="10" t="n">
+        <v>68</v>
+      </c>
+      <c r="E26" s="10" t="n">
+        <v>33</v>
+      </c>
+      <c r="F26" s="9" t="inlineStr">
+        <is>
+          <t>5078790d7c7a2c5f3e8e6b5b8fdd9fd7f6469dbaf60b380105405351adada815</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="6" t="inlineStr">
+        <is>
+          <t>LAM_pair_tests</t>
+        </is>
+      </c>
+      <c r="B27" s="7" t="inlineStr">
+        <is>
+          <t>Within-cohort donor-paired decoupled-state LAM tests.</t>
+        </is>
+      </c>
+      <c r="C27" s="7" t="inlineStr">
+        <is>
+          <t>results/cross_species_lam/LAM_decoupled_pair_tests.csv</t>
+        </is>
+      </c>
+      <c r="D27" s="8" t="n">
+        <v>15</v>
+      </c>
+      <c r="E27" s="8" t="n">
+        <v>9</v>
+      </c>
+      <c r="F27" s="7" t="inlineStr">
+        <is>
+          <t>a9592eda3f001460e6aa51f8a495dd526b56a89a95db97472bd52713394339a9</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="6" t="inlineStr">
+        <is>
           <t>LAM_meta</t>
         </is>
       </c>
-      <c r="B25" s="7" t="inlineStr">
+      <c r="B28" s="9" t="inlineStr">
         <is>
           <t>Cross-cohort LAM program meta-analysis.</t>
         </is>
       </c>
-      <c r="C25" s="7" t="inlineStr">
+      <c r="C28" s="9" t="inlineStr">
         <is>
           <t>results/cross_species_lam/LAM_decoupled_meta.csv</t>
         </is>
       </c>
-      <c r="D25" s="8" t="n">
+      <c r="D28" s="10" t="n">
         <v>5</v>
       </c>
-      <c r="E25" s="8" t="n">
+      <c r="E28" s="10" t="n">
         <v>7</v>
       </c>
-      <c r="F25" s="7" t="inlineStr">
+      <c r="F28" s="9" t="inlineStr">
         <is>
           <t>3a8c40d4b3163ea9cd78d2564998ff44f56e0b92d411e74f3fd31cbd6c52612f</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A10:F25"/>
+  <autoFilter ref="A10:F28"/>
   <mergeCells count="3">
     <mergeCell ref="A7:F8"/>
     <mergeCell ref="A3:F4"/>
@@ -1413,6 +1562,9 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A23" r:id="rId13"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A24" r:id="rId14"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A25" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A26" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A27" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A28" r:id="rId18"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" paperSize="9" fitToHeight="1" fitToWidth="1"/>
@@ -1420,6 +1572,2979 @@
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:R31"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="11" customWidth="1" min="1" max="1"/>
+    <col width="13" customWidth="1" min="2" max="2"/>
+    <col width="38" customWidth="1" min="3" max="3"/>
+    <col width="26" customWidth="1" min="4" max="4"/>
+    <col width="9" customWidth="1" min="5" max="5"/>
+    <col width="23" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="29" customWidth="1" min="8" max="8"/>
+    <col width="34" customWidth="1" min="9" max="9"/>
+    <col width="23" customWidth="1" min="10" max="10"/>
+    <col width="20" customWidth="1" min="11" max="11"/>
+    <col width="20" customWidth="1" min="12" max="12"/>
+    <col width="26" customWidth="1" min="13" max="13"/>
+    <col width="26" customWidth="1" min="14" max="14"/>
+    <col width="31" customWidth="1" min="15" max="15"/>
+    <col width="33" customWidth="1" min="16" max="16"/>
+    <col width="29" customWidth="1" min="17" max="17"/>
+    <col width="37" customWidth="1" min="18" max="18"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="24" customHeight="1">
+      <c r="A1" s="11" t="inlineStr">
+        <is>
+          <t>Donor-level differentiation, activation residual and decoupling scores.</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="26" customHeight="1">
+      <c r="A2" s="12" t="inlineStr">
+        <is>
+          <t>Source: results/two_axis/two_axis_donor_scores.csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="30" customHeight="1">
+      <c r="A4" s="13" t="inlineStr">
+        <is>
+          <t>dataset</t>
+        </is>
+      </c>
+      <c r="B4" s="13" t="inlineStr">
+        <is>
+          <t>subject_id</t>
+        </is>
+      </c>
+      <c r="C4" s="13" t="inlineStr">
+        <is>
+          <t>diagnosis</t>
+        </is>
+      </c>
+      <c r="D4" s="13" t="inlineStr">
+        <is>
+          <t>disease_group</t>
+        </is>
+      </c>
+      <c r="E4" s="13" t="inlineStr">
+        <is>
+          <t>is_MS</t>
+        </is>
+      </c>
+      <c r="F4" s="13" t="inlineStr">
+        <is>
+          <t>n_CSF_continuum_cells</t>
+        </is>
+      </c>
+      <c r="G4" s="13" t="inlineStr">
+        <is>
+          <t>n_strict_BAM</t>
+        </is>
+      </c>
+      <c r="H4" s="13" t="inlineStr">
+        <is>
+          <t>median_consensus_pseudotime</t>
+        </is>
+      </c>
+      <c r="I4" s="13" t="inlineStr">
+        <is>
+          <t>median_BAM_macrostate_membership</t>
+        </is>
+      </c>
+      <c r="J4" s="13" t="inlineStr">
+        <is>
+          <t>transitional_fraction</t>
+        </is>
+      </c>
+      <c r="K4" s="13" t="inlineStr">
+        <is>
+          <t>terminal_fraction</t>
+        </is>
+      </c>
+      <c r="L4" s="13" t="inlineStr">
+        <is>
+          <t>transition_entropy</t>
+        </is>
+      </c>
+      <c r="M4" s="13" t="inlineStr">
+        <is>
+          <t>mean_activation_residual</t>
+        </is>
+      </c>
+      <c r="N4" s="13" t="inlineStr">
+        <is>
+          <t>high_activation_fraction</t>
+        </is>
+      </c>
+      <c r="O4" s="13" t="inlineStr">
+        <is>
+          <t>activated_transition_fraction</t>
+        </is>
+      </c>
+      <c r="P4" s="13" t="inlineStr">
+        <is>
+          <t>decoupled_inflammatory_fraction</t>
+        </is>
+      </c>
+      <c r="Q4" s="13" t="inlineStr">
+        <is>
+          <t>continuous_decoupling_index</t>
+        </is>
+      </c>
+      <c r="R4" s="13" t="inlineStr">
+        <is>
+          <t>strict_BAM_mean_activation_residual</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="14" t="inlineStr">
+        <is>
+          <t>GSE138266</t>
+        </is>
+      </c>
+      <c r="B5" s="14" t="inlineStr">
+        <is>
+          <t>MS19270</t>
+        </is>
+      </c>
+      <c r="C5" s="14" t="inlineStr">
+        <is>
+          <t>Multiple Sclerosis</t>
+        </is>
+      </c>
+      <c r="D5" s="14" t="inlineStr">
+        <is>
+          <t>MS</t>
+        </is>
+      </c>
+      <c r="E5" s="17" t="b">
+        <v>1</v>
+      </c>
+      <c r="F5" s="15" t="n">
+        <v>104</v>
+      </c>
+      <c r="G5" s="15" t="n">
+        <v>41</v>
+      </c>
+      <c r="H5" s="16" t="n">
+        <v>0.7232599854469299</v>
+      </c>
+      <c r="I5" s="17" t="n">
+        <v>0.5388032417743196</v>
+      </c>
+      <c r="J5" s="17" t="n">
+        <v>0.7596153846153846</v>
+      </c>
+      <c r="K5" s="17" t="n">
+        <v>0.2403846153846154</v>
+      </c>
+      <c r="L5" s="17" t="n">
+        <v>0.5020177424645625</v>
+      </c>
+      <c r="M5" s="17" t="n">
+        <v>0.5567013394740564</v>
+      </c>
+      <c r="N5" s="17" t="n">
+        <v>0.4423076923076923</v>
+      </c>
+      <c r="O5" s="17" t="n">
+        <v>0.3461538461538461</v>
+      </c>
+      <c r="P5" s="17" t="n">
+        <v>0.3461538461538461</v>
+      </c>
+      <c r="Q5" s="17" t="n">
+        <v>0.1514648202239471</v>
+      </c>
+      <c r="R5" s="17" t="n">
+        <v>0.5911054974000713</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="14" t="inlineStr">
+        <is>
+          <t>GSE138266</t>
+        </is>
+      </c>
+      <c r="B6" s="14" t="inlineStr">
+        <is>
+          <t>MS49131</t>
+        </is>
+      </c>
+      <c r="C6" s="14" t="inlineStr">
+        <is>
+          <t>Multiple Sclerosis</t>
+        </is>
+      </c>
+      <c r="D6" s="14" t="inlineStr">
+        <is>
+          <t>MS</t>
+        </is>
+      </c>
+      <c r="E6" s="17" t="b">
+        <v>1</v>
+      </c>
+      <c r="F6" s="15" t="n">
+        <v>46</v>
+      </c>
+      <c r="G6" s="15" t="n">
+        <v>18</v>
+      </c>
+      <c r="H6" s="16" t="n">
+        <v>0.7833601236343384</v>
+      </c>
+      <c r="I6" s="17" t="n">
+        <v>0.2021073620961675</v>
+      </c>
+      <c r="J6" s="17" t="n">
+        <v>0.5869565217391305</v>
+      </c>
+      <c r="K6" s="17" t="n">
+        <v>0.4130434782608695</v>
+      </c>
+      <c r="L6" s="17" t="n">
+        <v>0.6170940766917039</v>
+      </c>
+      <c r="M6" s="17" t="n">
+        <v>0.8349914205798777</v>
+      </c>
+      <c r="N6" s="17" t="n">
+        <v>0.5217391304347826</v>
+      </c>
+      <c r="O6" s="17" t="n">
+        <v>0.3260869565217391</v>
+      </c>
+      <c r="P6" s="17" t="n">
+        <v>0.3260869565217391</v>
+      </c>
+      <c r="Q6" s="17" t="n">
+        <v>0.2646362940283152</v>
+      </c>
+      <c r="R6" s="17" t="n">
+        <v>0.4691126765948766</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="14" t="inlineStr">
+        <is>
+          <t>GSE138266</t>
+        </is>
+      </c>
+      <c r="B7" s="14" t="inlineStr">
+        <is>
+          <t>MS58637</t>
+        </is>
+      </c>
+      <c r="C7" s="14" t="inlineStr">
+        <is>
+          <t>Multiple Sclerosis</t>
+        </is>
+      </c>
+      <c r="D7" s="14" t="inlineStr">
+        <is>
+          <t>MS</t>
+        </is>
+      </c>
+      <c r="E7" s="17" t="b">
+        <v>1</v>
+      </c>
+      <c r="F7" s="15" t="n">
+        <v>40</v>
+      </c>
+      <c r="G7" s="15" t="n">
+        <v>26</v>
+      </c>
+      <c r="H7" s="16" t="n">
+        <v>0.877487450838089</v>
+      </c>
+      <c r="I7" s="17" t="n">
+        <v>0.5405228983253981</v>
+      </c>
+      <c r="J7" s="17" t="n">
+        <v>0.275</v>
+      </c>
+      <c r="K7" s="17" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="L7" s="17" t="n">
+        <v>0.6343594588921255</v>
+      </c>
+      <c r="M7" s="17" t="n">
+        <v>0.7403719693265879</v>
+      </c>
+      <c r="N7" s="17" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="O7" s="17" t="n">
+        <v>0.125</v>
+      </c>
+      <c r="P7" s="17" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="Q7" s="17" t="n">
+        <v>0.1183054677884492</v>
+      </c>
+      <c r="R7" s="17" t="n">
+        <v>0.8702095908011789</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="14" t="inlineStr">
+        <is>
+          <t>GSE138266</t>
+        </is>
+      </c>
+      <c r="B8" s="14" t="inlineStr">
+        <is>
+          <t>MS60249</t>
+        </is>
+      </c>
+      <c r="C8" s="14" t="inlineStr">
+        <is>
+          <t>Multiple Sclerosis</t>
+        </is>
+      </c>
+      <c r="D8" s="14" t="inlineStr">
+        <is>
+          <t>MS</t>
+        </is>
+      </c>
+      <c r="E8" s="17" t="b">
+        <v>1</v>
+      </c>
+      <c r="F8" s="15" t="n">
+        <v>92</v>
+      </c>
+      <c r="G8" s="15" t="n">
+        <v>38</v>
+      </c>
+      <c r="H8" s="16" t="n">
+        <v>0.8137178719043732</v>
+      </c>
+      <c r="I8" s="17" t="n">
+        <v>0.4733691433839063</v>
+      </c>
+      <c r="J8" s="17" t="n">
+        <v>0.4673913043478261</v>
+      </c>
+      <c r="K8" s="17" t="n">
+        <v>0.5108695652173914</v>
+      </c>
+      <c r="L8" s="17" t="n">
+        <v>0.7116657157845907</v>
+      </c>
+      <c r="M8" s="17" t="n">
+        <v>1.34008985270828</v>
+      </c>
+      <c r="N8" s="17" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="O8" s="17" t="n">
+        <v>0.3804347826086957</v>
+      </c>
+      <c r="P8" s="17" t="n">
+        <v>0.4021739130434782</v>
+      </c>
+      <c r="Q8" s="17" t="n">
+        <v>0.2949879041357146</v>
+      </c>
+      <c r="R8" s="17" t="n">
+        <v>1.400411591573747</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="14" t="inlineStr">
+        <is>
+          <t>GSE138266</t>
+        </is>
+      </c>
+      <c r="B9" s="14" t="inlineStr">
+        <is>
+          <t>MS71658</t>
+        </is>
+      </c>
+      <c r="C9" s="14" t="inlineStr">
+        <is>
+          <t>Multiple Sclerosis</t>
+        </is>
+      </c>
+      <c r="D9" s="14" t="inlineStr">
+        <is>
+          <t>MS</t>
+        </is>
+      </c>
+      <c r="E9" s="17" t="b">
+        <v>1</v>
+      </c>
+      <c r="F9" s="15" t="n">
+        <v>204</v>
+      </c>
+      <c r="G9" s="15" t="n">
+        <v>134</v>
+      </c>
+      <c r="H9" s="16" t="n">
+        <v>0.7869678437709808</v>
+      </c>
+      <c r="I9" s="17" t="n">
+        <v>0.5688260133761005</v>
+      </c>
+      <c r="J9" s="17" t="n">
+        <v>0.5637254901960784</v>
+      </c>
+      <c r="K9" s="17" t="n">
+        <v>0.4362745098039216</v>
+      </c>
+      <c r="L9" s="17" t="n">
+        <v>0.6235167574659428</v>
+      </c>
+      <c r="M9" s="17" t="n">
+        <v>0.4560201604800572</v>
+      </c>
+      <c r="N9" s="17" t="n">
+        <v>0.3627450980392157</v>
+      </c>
+      <c r="O9" s="17" t="n">
+        <v>0.2205882352941176</v>
+      </c>
+      <c r="P9" s="17" t="n">
+        <v>0.2205882352941176</v>
+      </c>
+      <c r="Q9" s="17" t="n">
+        <v>0.1034398564808644</v>
+      </c>
+      <c r="R9" s="17" t="n">
+        <v>0.4425691692294677</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="14" t="inlineStr">
+        <is>
+          <t>GSE138266</t>
+        </is>
+      </c>
+      <c r="B10" s="14" t="inlineStr">
+        <is>
+          <t>MS74594</t>
+        </is>
+      </c>
+      <c r="C10" s="14" t="inlineStr">
+        <is>
+          <t>Multiple Sclerosis</t>
+        </is>
+      </c>
+      <c r="D10" s="14" t="inlineStr">
+        <is>
+          <t>MS</t>
+        </is>
+      </c>
+      <c r="E10" s="17" t="b">
+        <v>1</v>
+      </c>
+      <c r="F10" s="15" t="n">
+        <v>45</v>
+      </c>
+      <c r="G10" s="15" t="n">
+        <v>24</v>
+      </c>
+      <c r="H10" s="16" t="n">
+        <v>0.7892842292785645</v>
+      </c>
+      <c r="I10" s="17" t="n">
+        <v>0.0880015537950961</v>
+      </c>
+      <c r="J10" s="17" t="n">
+        <v>0.5555555555555556</v>
+      </c>
+      <c r="K10" s="17" t="n">
+        <v>0.4444444444444444</v>
+      </c>
+      <c r="L10" s="17" t="n">
+        <v>0.6252993742043005</v>
+      </c>
+      <c r="M10" s="17" t="n">
+        <v>0.0194980246235419</v>
+      </c>
+      <c r="N10" s="17" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="O10" s="17" t="n">
+        <v>0.0888888888888888</v>
+      </c>
+      <c r="P10" s="17" t="n">
+        <v>0.0888888888888888</v>
+      </c>
+      <c r="Q10" s="17" t="n">
+        <v>-0.0001542660779688</v>
+      </c>
+      <c r="R10" s="17" t="n">
+        <v>0.0080175638454986</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="14" t="inlineStr">
+        <is>
+          <t>GSE138266</t>
+        </is>
+      </c>
+      <c r="B11" s="14" t="inlineStr">
+        <is>
+          <t>PST83775</t>
+        </is>
+      </c>
+      <c r="C11" s="14" t="inlineStr">
+        <is>
+          <t>idiopathic intracranial hypertension</t>
+        </is>
+      </c>
+      <c r="D11" s="14" t="inlineStr">
+        <is>
+          <t>IIH_control</t>
+        </is>
+      </c>
+      <c r="E11" s="17" t="b">
+        <v>0</v>
+      </c>
+      <c r="F11" s="15" t="n">
+        <v>196</v>
+      </c>
+      <c r="G11" s="15" t="n">
+        <v>134</v>
+      </c>
+      <c r="H11" s="16" t="n">
+        <v>0.8788898289203644</v>
+      </c>
+      <c r="I11" s="17" t="n">
+        <v>0.6104226298045529</v>
+      </c>
+      <c r="J11" s="17" t="n">
+        <v>0.3163265306122449</v>
+      </c>
+      <c r="K11" s="17" t="n">
+        <v>0.6785714285714286</v>
+      </c>
+      <c r="L11" s="17" t="n">
+        <v>0.5954251289881962</v>
+      </c>
+      <c r="M11" s="17" t="n">
+        <v>0.2411390982486199</v>
+      </c>
+      <c r="N11" s="17" t="n">
+        <v>0.2142857142857142</v>
+      </c>
+      <c r="O11" s="17" t="n">
+        <v>0.1020408163265306</v>
+      </c>
+      <c r="P11" s="17" t="n">
+        <v>0.1020408163265306</v>
+      </c>
+      <c r="Q11" s="17" t="n">
+        <v>0.0556461588055336</v>
+      </c>
+      <c r="R11" s="17" t="n">
+        <v>0.1249396387155572</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="14" t="inlineStr">
+        <is>
+          <t>GSE138266</t>
+        </is>
+      </c>
+      <c r="B12" s="14" t="inlineStr">
+        <is>
+          <t>PST95809</t>
+        </is>
+      </c>
+      <c r="C12" s="14" t="inlineStr">
+        <is>
+          <t>idiopathic intracranial hypertension</t>
+        </is>
+      </c>
+      <c r="D12" s="14" t="inlineStr">
+        <is>
+          <t>IIH_control</t>
+        </is>
+      </c>
+      <c r="E12" s="17" t="b">
+        <v>0</v>
+      </c>
+      <c r="F12" s="15" t="n">
+        <v>119</v>
+      </c>
+      <c r="G12" s="15" t="n">
+        <v>96</v>
+      </c>
+      <c r="H12" s="16" t="n">
+        <v>0.877813458442688</v>
+      </c>
+      <c r="I12" s="17" t="n">
+        <v>0.4169587572874052</v>
+      </c>
+      <c r="J12" s="17" t="n">
+        <v>0.2689075630252101</v>
+      </c>
+      <c r="K12" s="17" t="n">
+        <v>0.7310924369747899</v>
+      </c>
+      <c r="L12" s="17" t="n">
+        <v>0.5299132857268382</v>
+      </c>
+      <c r="M12" s="17" t="n">
+        <v>0.7944480896275485</v>
+      </c>
+      <c r="N12" s="17" t="n">
+        <v>0.5546218487394958</v>
+      </c>
+      <c r="O12" s="17" t="n">
+        <v>0.1512605042016806</v>
+      </c>
+      <c r="P12" s="17" t="n">
+        <v>0.1512605042016806</v>
+      </c>
+      <c r="Q12" s="17" t="n">
+        <v>0.1350077316683199</v>
+      </c>
+      <c r="R12" s="17" t="n">
+        <v>0.7674699153042578</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="14" t="inlineStr">
+        <is>
+          <t>GSE138266</t>
+        </is>
+      </c>
+      <c r="B13" s="14" t="inlineStr">
+        <is>
+          <t>PTC32190</t>
+        </is>
+      </c>
+      <c r="C13" s="14" t="inlineStr">
+        <is>
+          <t>idiopathic intracranial hypertension</t>
+        </is>
+      </c>
+      <c r="D13" s="14" t="inlineStr">
+        <is>
+          <t>IIH_control</t>
+        </is>
+      </c>
+      <c r="E13" s="17" t="b">
+        <v>0</v>
+      </c>
+      <c r="F13" s="15" t="n">
+        <v>702</v>
+      </c>
+      <c r="G13" s="15" t="n">
+        <v>444</v>
+      </c>
+      <c r="H13" s="16" t="n">
+        <v>0.8271615505218506</v>
+      </c>
+      <c r="I13" s="17" t="n">
+        <v>0.607546557451215</v>
+      </c>
+      <c r="J13" s="17" t="n">
+        <v>0.4131054131054131</v>
+      </c>
+      <c r="K13" s="17" t="n">
+        <v>0.5754985754985755</v>
+      </c>
+      <c r="L13" s="17" t="n">
+        <v>0.6682720172560471</v>
+      </c>
+      <c r="M13" s="17" t="n">
+        <v>-0.0301954668942068</v>
+      </c>
+      <c r="N13" s="17" t="n">
+        <v>0.150997150997151</v>
+      </c>
+      <c r="O13" s="17" t="n">
+        <v>0.0541310541310541</v>
+      </c>
+      <c r="P13" s="17" t="n">
+        <v>0.0569800569800569</v>
+      </c>
+      <c r="Q13" s="17" t="n">
+        <v>-0.0073492491272099</v>
+      </c>
+      <c r="R13" s="17" t="n">
+        <v>-0.0090943222271186</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="14" t="inlineStr">
+        <is>
+          <t>GSE138266</t>
+        </is>
+      </c>
+      <c r="B14" s="14" t="inlineStr">
+        <is>
+          <t>PTC41540</t>
+        </is>
+      </c>
+      <c r="C14" s="14" t="inlineStr">
+        <is>
+          <t>idiopathic intracranial hypertension</t>
+        </is>
+      </c>
+      <c r="D14" s="14" t="inlineStr">
+        <is>
+          <t>IIH_control</t>
+        </is>
+      </c>
+      <c r="E14" s="17" t="b">
+        <v>0</v>
+      </c>
+      <c r="F14" s="15" t="n">
+        <v>250</v>
+      </c>
+      <c r="G14" s="15" t="n">
+        <v>161</v>
+      </c>
+      <c r="H14" s="16" t="n">
+        <v>0.7846416831016541</v>
+      </c>
+      <c r="I14" s="17" t="n">
+        <v>0.5014953054743516</v>
+      </c>
+      <c r="J14" s="17" t="n">
+        <v>0.584</v>
+      </c>
+      <c r="K14" s="17" t="n">
+        <v>0.412</v>
+      </c>
+      <c r="L14" s="17" t="n">
+        <v>0.6385567637191237</v>
+      </c>
+      <c r="M14" s="17" t="n">
+        <v>0.1816929560457884</v>
+      </c>
+      <c r="N14" s="17" t="n">
+        <v>0.248</v>
+      </c>
+      <c r="O14" s="17" t="n">
+        <v>0.164</v>
+      </c>
+      <c r="P14" s="17" t="n">
+        <v>0.164</v>
+      </c>
+      <c r="Q14" s="17" t="n">
+        <v>0.0455162487864626</v>
+      </c>
+      <c r="R14" s="17" t="n">
+        <v>0.1531378175915024</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="14" t="inlineStr">
+        <is>
+          <t>GSE138266</t>
+        </is>
+      </c>
+      <c r="B15" s="14" t="inlineStr">
+        <is>
+          <t>PTC45044</t>
+        </is>
+      </c>
+      <c r="C15" s="14" t="inlineStr">
+        <is>
+          <t>idiopathic intracranial hypertension</t>
+        </is>
+      </c>
+      <c r="D15" s="14" t="inlineStr">
+        <is>
+          <t>IIH_control</t>
+        </is>
+      </c>
+      <c r="E15" s="17" t="b">
+        <v>0</v>
+      </c>
+      <c r="F15" s="15" t="n">
+        <v>652</v>
+      </c>
+      <c r="G15" s="15" t="n">
+        <v>500</v>
+      </c>
+      <c r="H15" s="16" t="n">
+        <v>0.8487563729286194</v>
+      </c>
+      <c r="I15" s="17" t="n">
+        <v>0.6223644764890602</v>
+      </c>
+      <c r="J15" s="17" t="n">
+        <v>0.3251533742331288</v>
+      </c>
+      <c r="K15" s="17" t="n">
+        <v>0.6733128834355828</v>
+      </c>
+      <c r="L15" s="17" t="n">
+        <v>0.5839736391845903</v>
+      </c>
+      <c r="M15" s="17" t="n">
+        <v>0.3520724684197478</v>
+      </c>
+      <c r="N15" s="17" t="n">
+        <v>0.3144171779141104</v>
+      </c>
+      <c r="O15" s="17" t="n">
+        <v>0.1088957055214723</v>
+      </c>
+      <c r="P15" s="17" t="n">
+        <v>0.1088957055214723</v>
+      </c>
+      <c r="Q15" s="17" t="n">
+        <v>0.0579700077840579</v>
+      </c>
+      <c r="R15" s="17" t="n">
+        <v>0.3466065865871055</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="14" t="inlineStr">
+        <is>
+          <t>GSE138266</t>
+        </is>
+      </c>
+      <c r="B16" s="14" t="inlineStr">
+        <is>
+          <t>PTC85037</t>
+        </is>
+      </c>
+      <c r="C16" s="14" t="inlineStr">
+        <is>
+          <t>idiopathic intracranial hypertension</t>
+        </is>
+      </c>
+      <c r="D16" s="14" t="inlineStr">
+        <is>
+          <t>IIH_control</t>
+        </is>
+      </c>
+      <c r="E16" s="17" t="b">
+        <v>0</v>
+      </c>
+      <c r="F16" s="15" t="n">
+        <v>19</v>
+      </c>
+      <c r="G16" s="15" t="n">
+        <v>10</v>
+      </c>
+      <c r="H16" s="16" t="n">
+        <v>0.7453516125679016</v>
+      </c>
+      <c r="I16" s="17" t="n">
+        <v>0.0985785027829916</v>
+      </c>
+      <c r="J16" s="17" t="n">
+        <v>0.6842105263157895</v>
+      </c>
+      <c r="K16" s="17" t="n">
+        <v>0.3157894736842105</v>
+      </c>
+      <c r="L16" s="17" t="n">
+        <v>0.5676751079529516</v>
+      </c>
+      <c r="M16" s="17" t="n">
+        <v>0.1289137961254477</v>
+      </c>
+      <c r="N16" s="17" t="n">
+        <v>0.2105263157894736</v>
+      </c>
+      <c r="O16" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="P16" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q16" s="17" t="n">
+        <v>0.0255336016337123</v>
+      </c>
+      <c r="R16" s="17" t="n">
+        <v>0.2736767976919746</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="14" t="inlineStr">
+        <is>
+          <t>GSE286068</t>
+        </is>
+      </c>
+      <c r="B17" s="14" t="inlineStr">
+        <is>
+          <t>CSF_scRNA1</t>
+        </is>
+      </c>
+      <c r="C17" s="14" t="inlineStr">
+        <is>
+          <t>SPMS</t>
+        </is>
+      </c>
+      <c r="D17" s="14" t="inlineStr">
+        <is>
+          <t>MS</t>
+        </is>
+      </c>
+      <c r="E17" s="17" t="b">
+        <v>1</v>
+      </c>
+      <c r="F17" s="15" t="n">
+        <v>728</v>
+      </c>
+      <c r="G17" s="15" t="n">
+        <v>389</v>
+      </c>
+      <c r="H17" s="16" t="n">
+        <v>0.5997858345508575</v>
+      </c>
+      <c r="I17" s="17" t="n">
+        <v>0.7748550405297984</v>
+      </c>
+      <c r="J17" s="17" t="n">
+        <v>0.5439560439560439</v>
+      </c>
+      <c r="K17" s="17" t="n">
+        <v>0.2074175824175824</v>
+      </c>
+      <c r="L17" s="17" t="n">
+        <v>0.9134424652587104</v>
+      </c>
+      <c r="M17" s="17" t="n">
+        <v>0.4187935862053222</v>
+      </c>
+      <c r="N17" s="17" t="n">
+        <v>0.2967032967032967</v>
+      </c>
+      <c r="O17" s="17" t="n">
+        <v>0.1689560439560439</v>
+      </c>
+      <c r="P17" s="17" t="n">
+        <v>0.2307692307692307</v>
+      </c>
+      <c r="Q17" s="17" t="n">
+        <v>0.1701529260598254</v>
+      </c>
+      <c r="R17" s="17" t="n">
+        <v>0.4881098765848582</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="14" t="inlineStr">
+        <is>
+          <t>GSE286068</t>
+        </is>
+      </c>
+      <c r="B18" s="14" t="inlineStr">
+        <is>
+          <t>CSF_scRNA2</t>
+        </is>
+      </c>
+      <c r="C18" s="14" t="inlineStr">
+        <is>
+          <t>Healthy donor</t>
+        </is>
+      </c>
+      <c r="D18" s="14" t="inlineStr">
+        <is>
+          <t>non_inflammatory_control</t>
+        </is>
+      </c>
+      <c r="E18" s="17" t="b">
+        <v>0</v>
+      </c>
+      <c r="F18" s="15" t="n">
+        <v>41</v>
+      </c>
+      <c r="G18" s="15" t="n">
+        <v>14</v>
+      </c>
+      <c r="H18" s="16" t="n">
+        <v>0.3422777652740478</v>
+      </c>
+      <c r="I18" s="17" t="n">
+        <v>0.6970149012169717</v>
+      </c>
+      <c r="J18" s="17" t="n">
+        <v>0.3658536585365853</v>
+      </c>
+      <c r="K18" s="17" t="n">
+        <v>0.0975609756097561</v>
+      </c>
+      <c r="L18" s="17" t="n">
+        <v>0.8455809448471829</v>
+      </c>
+      <c r="M18" s="17" t="n">
+        <v>0.2733118147864035</v>
+      </c>
+      <c r="N18" s="17" t="n">
+        <v>0.1707317073170731</v>
+      </c>
+      <c r="O18" s="17" t="n">
+        <v>0.073170731707317</v>
+      </c>
+      <c r="P18" s="17" t="n">
+        <v>0.1707317073170731</v>
+      </c>
+      <c r="Q18" s="17" t="n">
+        <v>0.1655574052944729</v>
+      </c>
+      <c r="R18" s="17" t="n">
+        <v>0.3192465908402339</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="14" t="inlineStr">
+        <is>
+          <t>GSE286068</t>
+        </is>
+      </c>
+      <c r="B19" s="14" t="inlineStr">
+        <is>
+          <t>CSF_scRNA3</t>
+        </is>
+      </c>
+      <c r="C19" s="14" t="inlineStr">
+        <is>
+          <t>PPMS</t>
+        </is>
+      </c>
+      <c r="D19" s="14" t="inlineStr">
+        <is>
+          <t>MS</t>
+        </is>
+      </c>
+      <c r="E19" s="17" t="b">
+        <v>1</v>
+      </c>
+      <c r="F19" s="15" t="n">
+        <v>89</v>
+      </c>
+      <c r="G19" s="15" t="n">
+        <v>25</v>
+      </c>
+      <c r="H19" s="16" t="n">
+        <v>0.3939515948295593</v>
+      </c>
+      <c r="I19" s="17" t="n">
+        <v>0.6326510364738918</v>
+      </c>
+      <c r="J19" s="17" t="n">
+        <v>0.3932584269662921</v>
+      </c>
+      <c r="K19" s="17" t="n">
+        <v>0.06741573033707859</v>
+      </c>
+      <c r="L19" s="17" t="n">
+        <v>0.802680137648844</v>
+      </c>
+      <c r="M19" s="17" t="n">
+        <v>0.1608467642387713</v>
+      </c>
+      <c r="N19" s="17" t="n">
+        <v>0.1910112359550561</v>
+      </c>
+      <c r="O19" s="17" t="n">
+        <v>0.0561797752808988</v>
+      </c>
+      <c r="P19" s="17" t="n">
+        <v>0.1797752808988764</v>
+      </c>
+      <c r="Q19" s="17" t="n">
+        <v>0.1082742016432019</v>
+      </c>
+      <c r="R19" s="17" t="n">
+        <v>0.0488250755185672</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="14" t="inlineStr">
+        <is>
+          <t>GSE286068</t>
+        </is>
+      </c>
+      <c r="B20" s="14" t="inlineStr">
+        <is>
+          <t>CSF_scRNA4</t>
+        </is>
+      </c>
+      <c r="C20" s="14" t="inlineStr">
+        <is>
+          <t>RRMS</t>
+        </is>
+      </c>
+      <c r="D20" s="14" t="inlineStr">
+        <is>
+          <t>MS</t>
+        </is>
+      </c>
+      <c r="E20" s="17" t="b">
+        <v>1</v>
+      </c>
+      <c r="F20" s="15" t="n">
+        <v>70</v>
+      </c>
+      <c r="G20" s="15" t="n">
+        <v>12</v>
+      </c>
+      <c r="H20" s="16" t="n">
+        <v>0.618537425994873</v>
+      </c>
+      <c r="I20" s="17" t="n">
+        <v>0.5268656107461651</v>
+      </c>
+      <c r="J20" s="17" t="n">
+        <v>0.4285714285714285</v>
+      </c>
+      <c r="K20" s="17" t="n">
+        <v>0.1857142857142857</v>
+      </c>
+      <c r="L20" s="17" t="n">
+        <v>0.9495980808532662</v>
+      </c>
+      <c r="M20" s="17" t="n">
+        <v>0.2026318458375899</v>
+      </c>
+      <c r="N20" s="17" t="n">
+        <v>0.1857142857142857</v>
+      </c>
+      <c r="O20" s="17" t="n">
+        <v>0.0714285714285714</v>
+      </c>
+      <c r="P20" s="17" t="n">
+        <v>0.1571428571428571</v>
+      </c>
+      <c r="Q20" s="17" t="n">
+        <v>0.1396327721348046</v>
+      </c>
+      <c r="R20" s="17" t="n">
+        <v>0.155102366100338</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="14" t="inlineStr">
+        <is>
+          <t>GSE286068</t>
+        </is>
+      </c>
+      <c r="B21" s="14" t="inlineStr">
+        <is>
+          <t>CSF_scRNA5</t>
+        </is>
+      </c>
+      <c r="C21" s="14" t="inlineStr">
+        <is>
+          <t>RRMS</t>
+        </is>
+      </c>
+      <c r="D21" s="14" t="inlineStr">
+        <is>
+          <t>MS</t>
+        </is>
+      </c>
+      <c r="E21" s="17" t="b">
+        <v>1</v>
+      </c>
+      <c r="F21" s="15" t="n">
+        <v>114</v>
+      </c>
+      <c r="G21" s="15" t="n">
+        <v>14</v>
+      </c>
+      <c r="H21" s="16" t="n">
+        <v>0.4016943573951721</v>
+      </c>
+      <c r="I21" s="17" t="n">
+        <v>0.4842861533699787</v>
+      </c>
+      <c r="J21" s="17" t="n">
+        <v>0.4122807017543859</v>
+      </c>
+      <c r="K21" s="17" t="n">
+        <v>0.09649122807017541</v>
+      </c>
+      <c r="L21" s="17" t="n">
+        <v>0.8557298152653974</v>
+      </c>
+      <c r="M21" s="17" t="n">
+        <v>0.3202765985807498</v>
+      </c>
+      <c r="N21" s="17" t="n">
+        <v>0.2631578947368421</v>
+      </c>
+      <c r="O21" s="17" t="n">
+        <v>0.1052631578947368</v>
+      </c>
+      <c r="P21" s="17" t="n">
+        <v>0.2456140350877192</v>
+      </c>
+      <c r="Q21" s="17" t="n">
+        <v>0.1986555635879445</v>
+      </c>
+      <c r="R21" s="17" t="n">
+        <v>-0.0031839905108558</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="14" t="inlineStr">
+        <is>
+          <t>GSE286068</t>
+        </is>
+      </c>
+      <c r="B22" s="14" t="inlineStr">
+        <is>
+          <t>CSF_scRNA6</t>
+        </is>
+      </c>
+      <c r="C22" s="14" t="inlineStr">
+        <is>
+          <t>PPMS</t>
+        </is>
+      </c>
+      <c r="D22" s="14" t="inlineStr">
+        <is>
+          <t>MS</t>
+        </is>
+      </c>
+      <c r="E22" s="17" t="b">
+        <v>1</v>
+      </c>
+      <c r="F22" s="15" t="n">
+        <v>133</v>
+      </c>
+      <c r="G22" s="15" t="n">
+        <v>28</v>
+      </c>
+      <c r="H22" s="16" t="n">
+        <v>0.2911870777606964</v>
+      </c>
+      <c r="I22" s="17" t="n">
+        <v>0.6466197147805202</v>
+      </c>
+      <c r="J22" s="17" t="n">
+        <v>0.2330827067669172</v>
+      </c>
+      <c r="K22" s="17" t="n">
+        <v>0.037593984962406</v>
+      </c>
+      <c r="L22" s="17" t="n">
+        <v>0.6307935682526351</v>
+      </c>
+      <c r="M22" s="17" t="n">
+        <v>1.008501339409448</v>
+      </c>
+      <c r="N22" s="17" t="n">
+        <v>0.5714285714285714</v>
+      </c>
+      <c r="O22" s="17" t="n">
+        <v>0.1353383458646616</v>
+      </c>
+      <c r="P22" s="17" t="n">
+        <v>0.5639097744360902</v>
+      </c>
+      <c r="Q22" s="17" t="n">
+        <v>0.692925050877644</v>
+      </c>
+      <c r="R22" s="17" t="n">
+        <v>0.8508070252186569</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="14" t="inlineStr">
+        <is>
+          <t>GSE286068</t>
+        </is>
+      </c>
+      <c r="B23" s="14" t="inlineStr">
+        <is>
+          <t>CSF_scRNA7</t>
+        </is>
+      </c>
+      <c r="C23" s="14" t="inlineStr">
+        <is>
+          <t>NIND</t>
+        </is>
+      </c>
+      <c r="D23" s="14" t="inlineStr">
+        <is>
+          <t>non_inflammatory_control</t>
+        </is>
+      </c>
+      <c r="E23" s="17" t="b">
+        <v>0</v>
+      </c>
+      <c r="F23" s="15" t="n">
+        <v>81</v>
+      </c>
+      <c r="G23" s="15" t="n">
+        <v>22</v>
+      </c>
+      <c r="H23" s="16" t="n">
+        <v>0.6219676733016968</v>
+      </c>
+      <c r="I23" s="17" t="n">
+        <v>0.3658678556878475</v>
+      </c>
+      <c r="J23" s="17" t="n">
+        <v>0.6049382716049383</v>
+      </c>
+      <c r="K23" s="17" t="n">
+        <v>0.1481481481481481</v>
+      </c>
+      <c r="L23" s="17" t="n">
+        <v>0.8486313325833185</v>
+      </c>
+      <c r="M23" s="17" t="n">
+        <v>0.0553154388295231</v>
+      </c>
+      <c r="N23" s="17" t="n">
+        <v>0.1481481481481481</v>
+      </c>
+      <c r="O23" s="17" t="n">
+        <v>0.074074074074074</v>
+      </c>
+      <c r="P23" s="17" t="n">
+        <v>0.0987654320987654</v>
+      </c>
+      <c r="Q23" s="17" t="n">
+        <v>0.0191025192646052</v>
+      </c>
+      <c r="R23" s="17" t="n">
+        <v>-0.0394997549569814</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="14" t="inlineStr">
+        <is>
+          <t>GSE286068</t>
+        </is>
+      </c>
+      <c r="B24" s="14" t="inlineStr">
+        <is>
+          <t>CSF_scRNA8</t>
+        </is>
+      </c>
+      <c r="C24" s="14" t="inlineStr">
+        <is>
+          <t>Healthy donor</t>
+        </is>
+      </c>
+      <c r="D24" s="14" t="inlineStr">
+        <is>
+          <t>non_inflammatory_control</t>
+        </is>
+      </c>
+      <c r="E24" s="17" t="b">
+        <v>0</v>
+      </c>
+      <c r="F24" s="15" t="n">
+        <v>20</v>
+      </c>
+      <c r="G24" s="15" t="n">
+        <v>7</v>
+      </c>
+      <c r="H24" s="16" t="n">
+        <v>0.7350404262542725</v>
+      </c>
+      <c r="I24" s="17" t="n">
+        <v>0.4168773682136881</v>
+      </c>
+      <c r="J24" s="17" t="n">
+        <v>0.65</v>
+      </c>
+      <c r="K24" s="17" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="L24" s="17" t="n">
+        <v>0.8068947387749437</v>
+      </c>
+      <c r="M24" s="17" t="n">
+        <v>0.1164619948809993</v>
+      </c>
+      <c r="N24" s="17" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="O24" s="17" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="P24" s="17" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="Q24" s="17" t="n">
+        <v>0.0380519642966923</v>
+      </c>
+      <c r="R24" s="17" t="n">
+        <v>0.0903057638965348</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="14" t="inlineStr">
+        <is>
+          <t>GSE286068</t>
+        </is>
+      </c>
+      <c r="B25" s="14" t="inlineStr">
+        <is>
+          <t>CSF_scRNA9</t>
+        </is>
+      </c>
+      <c r="C25" s="14" t="inlineStr">
+        <is>
+          <t>RRMS</t>
+        </is>
+      </c>
+      <c r="D25" s="14" t="inlineStr">
+        <is>
+          <t>MS</t>
+        </is>
+      </c>
+      <c r="E25" s="17" t="b">
+        <v>1</v>
+      </c>
+      <c r="F25" s="15" t="n">
+        <v>58</v>
+      </c>
+      <c r="G25" s="15" t="n">
+        <v>14</v>
+      </c>
+      <c r="H25" s="16" t="n">
+        <v>0.5796217322349548</v>
+      </c>
+      <c r="I25" s="17" t="n">
+        <v>0.5071729827569086</v>
+      </c>
+      <c r="J25" s="17" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="K25" s="17" t="n">
+        <v>0.1551724137931034</v>
+      </c>
+      <c r="L25" s="17" t="n">
+        <v>0.9128200510540844</v>
+      </c>
+      <c r="M25" s="17" t="n">
+        <v>0.2380087042917587</v>
+      </c>
+      <c r="N25" s="17" t="n">
+        <v>0.2068965517241379</v>
+      </c>
+      <c r="O25" s="17" t="n">
+        <v>0.0862068965517241</v>
+      </c>
+      <c r="P25" s="17" t="n">
+        <v>0.2068965517241379</v>
+      </c>
+      <c r="Q25" s="17" t="n">
+        <v>0.1993796407403401</v>
+      </c>
+      <c r="R25" s="17" t="n">
+        <v>0.1921966040739485</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="14" t="inlineStr">
+        <is>
+          <t>GSE286068</t>
+        </is>
+      </c>
+      <c r="B26" s="14" t="inlineStr">
+        <is>
+          <t>CSF_scRNA10</t>
+        </is>
+      </c>
+      <c r="C26" s="14" t="inlineStr">
+        <is>
+          <t>Healthy donor</t>
+        </is>
+      </c>
+      <c r="D26" s="14" t="inlineStr">
+        <is>
+          <t>non_inflammatory_control</t>
+        </is>
+      </c>
+      <c r="E26" s="17" t="b">
+        <v>0</v>
+      </c>
+      <c r="F26" s="15" t="n">
+        <v>183</v>
+      </c>
+      <c r="G26" s="15" t="n">
+        <v>11</v>
+      </c>
+      <c r="H26" s="16" t="n">
+        <v>0.8800538778305054</v>
+      </c>
+      <c r="I26" s="17" t="n">
+        <v>0.3447361317897924</v>
+      </c>
+      <c r="J26" s="17" t="n">
+        <v>0.2622950819672131</v>
+      </c>
+      <c r="K26" s="17" t="n">
+        <v>0.5737704918032787</v>
+      </c>
+      <c r="L26" s="17" t="n">
+        <v>0.8794828859471613</v>
+      </c>
+      <c r="M26" s="17" t="n">
+        <v>0.3274761840682968</v>
+      </c>
+      <c r="N26" s="17" t="n">
+        <v>0.3005464480874317</v>
+      </c>
+      <c r="O26" s="17" t="n">
+        <v>0.081967213114754</v>
+      </c>
+      <c r="P26" s="17" t="n">
+        <v>0.1420765027322404</v>
+      </c>
+      <c r="Q26" s="17" t="n">
+        <v>0.1109551965045805</v>
+      </c>
+      <c r="R26" s="17" t="n">
+        <v>0.2940583891118342</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="14" t="inlineStr">
+        <is>
+          <t>GSE286068</t>
+        </is>
+      </c>
+      <c r="B27" s="14" t="inlineStr">
+        <is>
+          <t>CSF_scRNA11</t>
+        </is>
+      </c>
+      <c r="C27" s="14" t="inlineStr">
+        <is>
+          <t>PPMS</t>
+        </is>
+      </c>
+      <c r="D27" s="14" t="inlineStr">
+        <is>
+          <t>MS</t>
+        </is>
+      </c>
+      <c r="E27" s="17" t="b">
+        <v>1</v>
+      </c>
+      <c r="F27" s="15" t="n">
+        <v>22</v>
+      </c>
+      <c r="G27" s="15" t="n">
+        <v>2</v>
+      </c>
+      <c r="H27" s="16" t="n">
+        <v>0.4797279387712478</v>
+      </c>
+      <c r="I27" s="17" t="n">
+        <v>0.449901944126573</v>
+      </c>
+      <c r="J27" s="17" t="n">
+        <v>0.2727272727272727</v>
+      </c>
+      <c r="K27" s="17" t="n">
+        <v>0.2727272727272727</v>
+      </c>
+      <c r="L27" s="17" t="n">
+        <v>0.9713067383178074</v>
+      </c>
+      <c r="M27" s="17" t="n">
+        <v>0.4123518802878557</v>
+      </c>
+      <c r="N27" s="17" t="n">
+        <v>0.3636363636363636</v>
+      </c>
+      <c r="O27" s="17" t="n">
+        <v>0.0909090909090909</v>
+      </c>
+      <c r="P27" s="17" t="n">
+        <v>0.3636363636363636</v>
+      </c>
+      <c r="Q27" s="17" t="n">
+        <v>0.2759952144058636</v>
+      </c>
+      <c r="R27" s="17" t="n">
+        <v>0.8380995515124885</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="14" t="inlineStr">
+        <is>
+          <t>GSE286068</t>
+        </is>
+      </c>
+      <c r="B28" s="14" t="inlineStr">
+        <is>
+          <t>CSF_scRNA12</t>
+        </is>
+      </c>
+      <c r="C28" s="14" t="inlineStr">
+        <is>
+          <t>PPMS</t>
+        </is>
+      </c>
+      <c r="D28" s="14" t="inlineStr">
+        <is>
+          <t>MS</t>
+        </is>
+      </c>
+      <c r="E28" s="17" t="b">
+        <v>1</v>
+      </c>
+      <c r="F28" s="15" t="n">
+        <v>189</v>
+      </c>
+      <c r="G28" s="15" t="n">
+        <v>40</v>
+      </c>
+      <c r="H28" s="16" t="n">
+        <v>0.6675202250480652</v>
+      </c>
+      <c r="I28" s="17" t="n">
+        <v>0.5559965982651031</v>
+      </c>
+      <c r="J28" s="17" t="n">
+        <v>0.3915343915343915</v>
+      </c>
+      <c r="K28" s="17" t="n">
+        <v>0.2592592592592592</v>
+      </c>
+      <c r="L28" s="17" t="n">
+        <v>0.9871662954233866</v>
+      </c>
+      <c r="M28" s="17" t="n">
+        <v>0.564363852940945</v>
+      </c>
+      <c r="N28" s="17" t="n">
+        <v>0.4074074074074074</v>
+      </c>
+      <c r="O28" s="17" t="n">
+        <v>0.1693121693121693</v>
+      </c>
+      <c r="P28" s="17" t="n">
+        <v>0.3121693121693121</v>
+      </c>
+      <c r="Q28" s="17" t="n">
+        <v>0.2666097764176057</v>
+      </c>
+      <c r="R28" s="17" t="n">
+        <v>0.735813608530019</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="14" t="inlineStr">
+        <is>
+          <t>GSE286068</t>
+        </is>
+      </c>
+      <c r="B29" s="14" t="inlineStr">
+        <is>
+          <t>CSF_scRNA13</t>
+        </is>
+      </c>
+      <c r="C29" s="14" t="inlineStr">
+        <is>
+          <t>PPMS</t>
+        </is>
+      </c>
+      <c r="D29" s="14" t="inlineStr">
+        <is>
+          <t>MS</t>
+        </is>
+      </c>
+      <c r="E29" s="17" t="b">
+        <v>1</v>
+      </c>
+      <c r="F29" s="15" t="n">
+        <v>92</v>
+      </c>
+      <c r="G29" s="15" t="n">
+        <v>14</v>
+      </c>
+      <c r="H29" s="16" t="n">
+        <v>0.7560646831989288</v>
+      </c>
+      <c r="I29" s="17" t="n">
+        <v>0.3412892983270439</v>
+      </c>
+      <c r="J29" s="17" t="n">
+        <v>0.4565217391304347</v>
+      </c>
+      <c r="K29" s="17" t="n">
+        <v>0.3478260869565217</v>
+      </c>
+      <c r="L29" s="17" t="n">
+        <v>0.9507269107073124</v>
+      </c>
+      <c r="M29" s="17" t="n">
+        <v>0.330206385875139</v>
+      </c>
+      <c r="N29" s="17" t="n">
+        <v>0.3043478260869565</v>
+      </c>
+      <c r="O29" s="17" t="n">
+        <v>0.1304347826086956</v>
+      </c>
+      <c r="P29" s="17" t="n">
+        <v>0.2065217391304347</v>
+      </c>
+      <c r="Q29" s="17" t="n">
+        <v>0.1522179888706367</v>
+      </c>
+      <c r="R29" s="17" t="n">
+        <v>0.2388277001697936</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="14" t="inlineStr">
+        <is>
+          <t>GSE286068</t>
+        </is>
+      </c>
+      <c r="B30" s="14" t="inlineStr">
+        <is>
+          <t>CSF_scRNA14</t>
+        </is>
+      </c>
+      <c r="C30" s="14" t="inlineStr">
+        <is>
+          <t>Healthy donor</t>
+        </is>
+      </c>
+      <c r="D30" s="14" t="inlineStr">
+        <is>
+          <t>non_inflammatory_control</t>
+        </is>
+      </c>
+      <c r="E30" s="17" t="b">
+        <v>0</v>
+      </c>
+      <c r="F30" s="15" t="n">
+        <v>30</v>
+      </c>
+      <c r="G30" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="H30" s="16" t="n">
+        <v>0.8058625161647797</v>
+      </c>
+      <c r="I30" s="17" t="n">
+        <v>0.3387421408871653</v>
+      </c>
+      <c r="J30" s="17" t="n">
+        <v>0.4666666666666667</v>
+      </c>
+      <c r="K30" s="17" t="n">
+        <v>0.5333333333333333</v>
+      </c>
+      <c r="L30" s="17" t="n">
+        <v>0.6289054987282648</v>
+      </c>
+      <c r="M30" s="17" t="n">
+        <v>0.3553199739134677</v>
+      </c>
+      <c r="N30" s="17" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="O30" s="17" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="P30" s="17" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="Q30" s="17" t="n">
+        <v>0.0697069023409308</v>
+      </c>
+      <c r="R30" s="17" t="n">
+        <v>-0.1023933917132645</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="14" t="inlineStr">
+        <is>
+          <t>GSE286068</t>
+        </is>
+      </c>
+      <c r="B31" s="14" t="inlineStr">
+        <is>
+          <t>CSF_scRNA15</t>
+        </is>
+      </c>
+      <c r="C31" s="14" t="inlineStr">
+        <is>
+          <t>RRMS</t>
+        </is>
+      </c>
+      <c r="D31" s="14" t="inlineStr">
+        <is>
+          <t>MS</t>
+        </is>
+      </c>
+      <c r="E31" s="17" t="b">
+        <v>1</v>
+      </c>
+      <c r="F31" s="15" t="n">
+        <v>5</v>
+      </c>
+      <c r="G31" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="H31" s="16" t="n">
+        <v>0.8545821905136108</v>
+      </c>
+      <c r="I31" s="17" t="n">
+        <v>0.3448569578434649</v>
+      </c>
+      <c r="J31" s="17" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="K31" s="17" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="L31" s="17" t="n">
+        <v>0.4554859150035952</v>
+      </c>
+      <c r="M31" s="17" t="n">
+        <v>1.004344821845164</v>
+      </c>
+      <c r="N31" s="17" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="O31" s="17" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="P31" s="17" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="Q31" s="17" t="n">
+        <v>0.2204508163942505</v>
+      </c>
+      <c r="R31" s="17" t="n"/>
+    </row>
+  </sheetData>
+  <autoFilter ref="A4:R31"/>
+  <mergeCells count="2">
+    <mergeCell ref="A2:R2"/>
+    <mergeCell ref="A1:R1"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
+  <tableParts count="1">
+    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+  </tableParts>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:K26"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="11" customWidth="1" min="1" max="1"/>
+    <col width="37" customWidth="1" min="2" max="2"/>
+    <col width="9" customWidth="1" min="3" max="3"/>
+    <col width="11" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="5" max="5"/>
+    <col width="20" customWidth="1" min="6" max="6"/>
+    <col width="34" customWidth="1" min="7" max="7"/>
+    <col width="30" customWidth="1" min="8" max="8"/>
+    <col width="21" customWidth="1" min="9" max="9"/>
+    <col width="21" customWidth="1" min="10" max="10"/>
+    <col width="23" customWidth="1" min="11" max="11"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="24" customHeight="1">
+      <c r="A1" s="11" t="inlineStr">
+        <is>
+          <t>Within-cohort disease tests for the two-axis endpoints.</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="26" customHeight="1">
+      <c r="A2" s="12" t="inlineStr">
+        <is>
+          <t>Source: results/two_axis/two_axis_disease_tests.csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="30" customHeight="1">
+      <c r="A4" s="13" t="inlineStr">
+        <is>
+          <t>dataset</t>
+        </is>
+      </c>
+      <c r="B4" s="13" t="inlineStr">
+        <is>
+          <t>metric</t>
+        </is>
+      </c>
+      <c r="C4" s="13" t="inlineStr">
+        <is>
+          <t>n_MS</t>
+        </is>
+      </c>
+      <c r="D4" s="13" t="inlineStr">
+        <is>
+          <t>n_control</t>
+        </is>
+      </c>
+      <c r="E4" s="13" t="inlineStr">
+        <is>
+          <t>mean_MS</t>
+        </is>
+      </c>
+      <c r="F4" s="13" t="inlineStr">
+        <is>
+          <t>mean_control</t>
+        </is>
+      </c>
+      <c r="G4" s="13" t="inlineStr">
+        <is>
+          <t>mean_difference_MS_minus_control</t>
+        </is>
+      </c>
+      <c r="H4" s="13" t="inlineStr">
+        <is>
+          <t>standardized_mean_difference</t>
+        </is>
+      </c>
+      <c r="I4" s="13" t="inlineStr">
+        <is>
+          <t>cliffs_delta</t>
+        </is>
+      </c>
+      <c r="J4" s="13" t="inlineStr">
+        <is>
+          <t>exact_permutation_p</t>
+        </is>
+      </c>
+      <c r="K4" s="13" t="inlineStr">
+        <is>
+          <t>fdr_bh_within_dataset</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="14" t="inlineStr">
+        <is>
+          <t>GSE138266</t>
+        </is>
+      </c>
+      <c r="B5" s="14" t="inlineStr">
+        <is>
+          <t>median_consensus_pseudotime</t>
+        </is>
+      </c>
+      <c r="C5" s="15" t="n">
+        <v>6</v>
+      </c>
+      <c r="D5" s="15" t="n">
+        <v>5</v>
+      </c>
+      <c r="E5" s="17" t="n">
+        <v>0.795679584145546</v>
+      </c>
+      <c r="F5" s="17" t="n">
+        <v>0.8434525787830353</v>
+      </c>
+      <c r="G5" s="17" t="n">
+        <v>-0.0477729946374893</v>
+      </c>
+      <c r="H5" s="17" t="n">
+        <v>-1.047498152877157</v>
+      </c>
+      <c r="I5" s="17" t="n">
+        <v>-0.6</v>
+      </c>
+      <c r="J5" s="16" t="n">
+        <v>0.1038961038961039</v>
+      </c>
+      <c r="K5" s="16" t="n">
+        <v>0.2182539682539682</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="14" t="inlineStr">
+        <is>
+          <t>GSE138266</t>
+        </is>
+      </c>
+      <c r="B6" s="14" t="inlineStr">
+        <is>
+          <t>median_BAM_macrostate_membership</t>
+        </is>
+      </c>
+      <c r="C6" s="15" t="n">
+        <v>6</v>
+      </c>
+      <c r="D6" s="15" t="n">
+        <v>5</v>
+      </c>
+      <c r="E6" s="17" t="n">
+        <v>0.4019383687918313</v>
+      </c>
+      <c r="F6" s="17" t="n">
+        <v>0.551757545301317</v>
+      </c>
+      <c r="G6" s="17" t="n">
+        <v>-0.1498191765094856</v>
+      </c>
+      <c r="H6" s="17" t="n">
+        <v>-0.9143769395948432</v>
+      </c>
+      <c r="I6" s="17" t="n">
+        <v>-0.5333333333333333</v>
+      </c>
+      <c r="J6" s="16" t="n">
+        <v>0.1991341991341991</v>
+      </c>
+      <c r="K6" s="16" t="n">
+        <v>0.219047619047619</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="14" t="inlineStr">
+        <is>
+          <t>GSE138266</t>
+        </is>
+      </c>
+      <c r="B7" s="14" t="inlineStr">
+        <is>
+          <t>transitional_fraction</t>
+        </is>
+      </c>
+      <c r="C7" s="15" t="n">
+        <v>6</v>
+      </c>
+      <c r="D7" s="15" t="n">
+        <v>5</v>
+      </c>
+      <c r="E7" s="17" t="n">
+        <v>0.5347073760756625</v>
+      </c>
+      <c r="F7" s="17" t="n">
+        <v>0.3814985761951993</v>
+      </c>
+      <c r="G7" s="17" t="n">
+        <v>0.1532087998804632</v>
+      </c>
+      <c r="H7" s="17" t="n">
+        <v>1.058153049767358</v>
+      </c>
+      <c r="I7" s="17" t="n">
+        <v>0.5333333333333333</v>
+      </c>
+      <c r="J7" s="16" t="n">
+        <v>0.119047619047619</v>
+      </c>
+      <c r="K7" s="16" t="n">
+        <v>0.2182539682539682</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="14" t="inlineStr">
+        <is>
+          <t>GSE138266</t>
+        </is>
+      </c>
+      <c r="B8" s="14" t="inlineStr">
+        <is>
+          <t>terminal_fraction</t>
+        </is>
+      </c>
+      <c r="C8" s="15" t="n">
+        <v>6</v>
+      </c>
+      <c r="D8" s="15" t="n">
+        <v>5</v>
+      </c>
+      <c r="E8" s="17" t="n">
+        <v>0.4575027688518737</v>
+      </c>
+      <c r="F8" s="17" t="n">
+        <v>0.6140950648960753</v>
+      </c>
+      <c r="G8" s="17" t="n">
+        <v>-0.1565922960442016</v>
+      </c>
+      <c r="H8" s="17" t="n">
+        <v>-1.122739571999737</v>
+      </c>
+      <c r="I8" s="17" t="n">
+        <v>-0.4666666666666667</v>
+      </c>
+      <c r="J8" s="16" t="n">
+        <v>0.1038961038961039</v>
+      </c>
+      <c r="K8" s="16" t="n">
+        <v>0.2182539682539682</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="14" t="inlineStr">
+        <is>
+          <t>GSE138266</t>
+        </is>
+      </c>
+      <c r="B9" s="14" t="inlineStr">
+        <is>
+          <t>transition_entropy</t>
+        </is>
+      </c>
+      <c r="C9" s="15" t="n">
+        <v>6</v>
+      </c>
+      <c r="D9" s="15" t="n">
+        <v>5</v>
+      </c>
+      <c r="E9" s="17" t="n">
+        <v>0.618992187583871</v>
+      </c>
+      <c r="F9" s="17" t="n">
+        <v>0.6032281669749592</v>
+      </c>
+      <c r="G9" s="17" t="n">
+        <v>0.0157640206089118</v>
+      </c>
+      <c r="H9" s="17" t="n">
+        <v>0.257018582726258</v>
+      </c>
+      <c r="I9" s="17" t="n">
+        <v>0.1333333333333333</v>
+      </c>
+      <c r="J9" s="16" t="n">
+        <v>0.6796536796536796</v>
+      </c>
+      <c r="K9" s="16" t="n">
+        <v>0.6796536796536796</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="14" t="inlineStr">
+        <is>
+          <t>GSE138266</t>
+        </is>
+      </c>
+      <c r="B10" s="14" t="inlineStr">
+        <is>
+          <t>mean_activation_residual</t>
+        </is>
+      </c>
+      <c r="C10" s="15" t="n">
+        <v>6</v>
+      </c>
+      <c r="D10" s="15" t="n">
+        <v>5</v>
+      </c>
+      <c r="E10" s="17" t="n">
+        <v>0.6579454611987335</v>
+      </c>
+      <c r="F10" s="17" t="n">
+        <v>0.3078314290894995</v>
+      </c>
+      <c r="G10" s="17" t="n">
+        <v>0.350114032109234</v>
+      </c>
+      <c r="H10" s="17" t="n">
+        <v>0.9088937157036748</v>
+      </c>
+      <c r="I10" s="17" t="n">
+        <v>0.5333333333333333</v>
+      </c>
+      <c r="J10" s="16" t="n">
+        <v>0.1688311688311688</v>
+      </c>
+      <c r="K10" s="16" t="n">
+        <v>0.219047619047619</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="14" t="inlineStr">
+        <is>
+          <t>GSE138266</t>
+        </is>
+      </c>
+      <c r="B11" s="14" t="inlineStr">
+        <is>
+          <t>high_activation_fraction</t>
+        </is>
+      </c>
+      <c r="C11" s="15" t="n">
+        <v>6</v>
+      </c>
+      <c r="D11" s="15" t="n">
+        <v>5</v>
+      </c>
+      <c r="E11" s="17" t="n">
+        <v>0.4627986534636151</v>
+      </c>
+      <c r="F11" s="17" t="n">
+        <v>0.2964643783872943</v>
+      </c>
+      <c r="G11" s="17" t="n">
+        <v>0.1663342750763207</v>
+      </c>
+      <c r="H11" s="17" t="n">
+        <v>0.9710602973417466</v>
+      </c>
+      <c r="I11" s="17" t="n">
+        <v>0.4666666666666667</v>
+      </c>
+      <c r="J11" s="16" t="n">
+        <v>0.1406926406926407</v>
+      </c>
+      <c r="K11" s="16" t="n">
+        <v>0.219047619047619</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="14" t="inlineStr">
+        <is>
+          <t>GSE138266</t>
+        </is>
+      </c>
+      <c r="B12" s="14" t="inlineStr">
+        <is>
+          <t>activated_transition_fraction</t>
+        </is>
+      </c>
+      <c r="C12" s="15" t="n">
+        <v>6</v>
+      </c>
+      <c r="D12" s="15" t="n">
+        <v>5</v>
+      </c>
+      <c r="E12" s="17" t="n">
+        <v>0.2478587849112145</v>
+      </c>
+      <c r="F12" s="17" t="n">
+        <v>0.1160656160361475</v>
+      </c>
+      <c r="G12" s="17" t="n">
+        <v>0.1317931688750669</v>
+      </c>
+      <c r="H12" s="17" t="n">
+        <v>1.379987111160227</v>
+      </c>
+      <c r="I12" s="17" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="J12" s="16" t="n">
+        <v>0.0627705627705627</v>
+      </c>
+      <c r="K12" s="16" t="n">
+        <v>0.2182539682539682</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="14" t="inlineStr">
+        <is>
+          <t>GSE138266</t>
+        </is>
+      </c>
+      <c r="B13" s="14" t="inlineStr">
+        <is>
+          <t>decoupled_inflammatory_fraction</t>
+        </is>
+      </c>
+      <c r="C13" s="15" t="n">
+        <v>6</v>
+      </c>
+      <c r="D13" s="15" t="n">
+        <v>5</v>
+      </c>
+      <c r="E13" s="17" t="n">
+        <v>0.2556486399836783</v>
+      </c>
+      <c r="F13" s="17" t="n">
+        <v>0.1166354166059481</v>
+      </c>
+      <c r="G13" s="17" t="n">
+        <v>0.1390132233777301</v>
+      </c>
+      <c r="H13" s="17" t="n">
+        <v>1.455513463279578</v>
+      </c>
+      <c r="I13" s="17" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="J13" s="16" t="n">
+        <v>0.0519480519480519</v>
+      </c>
+      <c r="K13" s="16" t="n">
+        <v>0.2182539682539682</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="14" t="inlineStr">
+        <is>
+          <t>GSE138266</t>
+        </is>
+      </c>
+      <c r="B14" s="14" t="inlineStr">
+        <is>
+          <t>continuous_decoupling_index</t>
+        </is>
+      </c>
+      <c r="C14" s="15" t="n">
+        <v>6</v>
+      </c>
+      <c r="D14" s="15" t="n">
+        <v>5</v>
+      </c>
+      <c r="E14" s="17" t="n">
+        <v>0.1554466794298869</v>
+      </c>
+      <c r="F14" s="17" t="n">
+        <v>0.0573581795834328</v>
+      </c>
+      <c r="G14" s="17" t="n">
+        <v>0.0980884998464541</v>
+      </c>
+      <c r="H14" s="17" t="n">
+        <v>1.111696233922438</v>
+      </c>
+      <c r="I14" s="17" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="J14" s="16" t="n">
+        <v>0.1082251082251082</v>
+      </c>
+      <c r="K14" s="16" t="n">
+        <v>0.2182539682539682</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="14" t="inlineStr">
+        <is>
+          <t>GSE138266</t>
+        </is>
+      </c>
+      <c r="B15" s="14" t="inlineStr">
+        <is>
+          <t>strict_BAM_mean_activation_residual</t>
+        </is>
+      </c>
+      <c r="C15" s="15" t="n">
+        <v>6</v>
+      </c>
+      <c r="D15" s="15" t="n">
+        <v>5</v>
+      </c>
+      <c r="E15" s="17" t="n">
+        <v>0.6302376815741401</v>
+      </c>
+      <c r="F15" s="17" t="n">
+        <v>0.2766119271942608</v>
+      </c>
+      <c r="G15" s="17" t="n">
+        <v>0.3536257543798792</v>
+      </c>
+      <c r="H15" s="17" t="n">
+        <v>0.8760870859390878</v>
+      </c>
+      <c r="I15" s="17" t="n">
+        <v>0.5333333333333333</v>
+      </c>
+      <c r="J15" s="16" t="n">
+        <v>0.1861471861471861</v>
+      </c>
+      <c r="K15" s="16" t="n">
+        <v>0.219047619047619</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="14" t="inlineStr">
+        <is>
+          <t>GSE286068</t>
+        </is>
+      </c>
+      <c r="B16" s="14" t="inlineStr">
+        <is>
+          <t>median_consensus_pseudotime</t>
+        </is>
+      </c>
+      <c r="C16" s="15" t="n">
+        <v>9</v>
+      </c>
+      <c r="D16" s="15" t="n">
+        <v>5</v>
+      </c>
+      <c r="E16" s="17" t="n">
+        <v>0.5320100966427062</v>
+      </c>
+      <c r="F16" s="17" t="n">
+        <v>0.6770404517650604</v>
+      </c>
+      <c r="G16" s="17" t="n">
+        <v>-0.1450303551223543</v>
+      </c>
+      <c r="H16" s="17" t="n">
+        <v>-0.8420773687660105</v>
+      </c>
+      <c r="I16" s="17" t="n">
+        <v>-0.5111111111111111</v>
+      </c>
+      <c r="J16" s="16" t="n">
+        <v>0.1548451548451548</v>
+      </c>
+      <c r="K16" s="16" t="n">
+        <v>0.2781593406593406</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="14" t="inlineStr">
+        <is>
+          <t>GSE286068</t>
+        </is>
+      </c>
+      <c r="B17" s="14" t="inlineStr">
+        <is>
+          <t>median_BAM_macrostate_membership</t>
+        </is>
+      </c>
+      <c r="C17" s="15" t="n">
+        <v>9</v>
+      </c>
+      <c r="D17" s="15" t="n">
+        <v>5</v>
+      </c>
+      <c r="E17" s="17" t="n">
+        <v>0.5466264865973315</v>
+      </c>
+      <c r="F17" s="17" t="n">
+        <v>0.432647679559093</v>
+      </c>
+      <c r="G17" s="17" t="n">
+        <v>0.1139788070382384</v>
+      </c>
+      <c r="H17" s="17" t="n">
+        <v>0.8455016999799456</v>
+      </c>
+      <c r="I17" s="17" t="n">
+        <v>0.5111111111111111</v>
+      </c>
+      <c r="J17" s="16" t="n">
+        <v>0.1543456543456543</v>
+      </c>
+      <c r="K17" s="16" t="n">
+        <v>0.2781593406593406</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="14" t="inlineStr">
+        <is>
+          <t>GSE286068</t>
+        </is>
+      </c>
+      <c r="B18" s="14" t="inlineStr">
+        <is>
+          <t>transitional_fraction</t>
+        </is>
+      </c>
+      <c r="C18" s="15" t="n">
+        <v>9</v>
+      </c>
+      <c r="D18" s="15" t="n">
+        <v>5</v>
+      </c>
+      <c r="E18" s="17" t="n">
+        <v>0.4035480790452407</v>
+      </c>
+      <c r="F18" s="17" t="n">
+        <v>0.4699507357550807</v>
+      </c>
+      <c r="G18" s="17" t="n">
+        <v>-0.0664026567098399</v>
+      </c>
+      <c r="H18" s="17" t="n">
+        <v>-0.5368980483429732</v>
+      </c>
+      <c r="I18" s="17" t="n">
+        <v>-0.2444444444444444</v>
+      </c>
+      <c r="J18" s="16" t="n">
+        <v>0.3491508491508491</v>
+      </c>
+      <c r="K18" s="16" t="n">
+        <v>0.3840659340659341</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="14" t="inlineStr">
+        <is>
+          <t>GSE286068</t>
+        </is>
+      </c>
+      <c r="B19" s="14" t="inlineStr">
+        <is>
+          <t>terminal_fraction</t>
+        </is>
+      </c>
+      <c r="C19" s="15" t="n">
+        <v>9</v>
+      </c>
+      <c r="D19" s="15" t="n">
+        <v>5</v>
+      </c>
+      <c r="E19" s="17" t="n">
+        <v>0.1810686493597428</v>
+      </c>
+      <c r="F19" s="17" t="n">
+        <v>0.3005625897789032</v>
+      </c>
+      <c r="G19" s="17" t="n">
+        <v>-0.1194939404191604</v>
+      </c>
+      <c r="H19" s="17" t="n">
+        <v>-0.7553702401849812</v>
+      </c>
+      <c r="I19" s="17" t="n">
+        <v>-0.2</v>
+      </c>
+      <c r="J19" s="16" t="n">
+        <v>0.2022977022977023</v>
+      </c>
+      <c r="K19" s="16" t="n">
+        <v>0.2781593406593406</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="14" t="inlineStr">
+        <is>
+          <t>GSE286068</t>
+        </is>
+      </c>
+      <c r="B20" s="14" t="inlineStr">
+        <is>
+          <t>transition_entropy</t>
+        </is>
+      </c>
+      <c r="C20" s="15" t="n">
+        <v>9</v>
+      </c>
+      <c r="D20" s="15" t="n">
+        <v>5</v>
+      </c>
+      <c r="E20" s="17" t="n">
+        <v>0.8860293403090495</v>
+      </c>
+      <c r="F20" s="17" t="n">
+        <v>0.8018990801761742</v>
+      </c>
+      <c r="G20" s="17" t="n">
+        <v>0.0841302601328752</v>
+      </c>
+      <c r="H20" s="17" t="n">
+        <v>0.7781439174329958</v>
+      </c>
+      <c r="I20" s="17" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="J20" s="16" t="n">
+        <v>0.1923076923076923</v>
+      </c>
+      <c r="K20" s="16" t="n">
+        <v>0.2781593406593406</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="14" t="inlineStr">
+        <is>
+          <t>GSE286068</t>
+        </is>
+      </c>
+      <c r="B21" s="14" t="inlineStr">
+        <is>
+          <t>mean_activation_residual</t>
+        </is>
+      </c>
+      <c r="C21" s="15" t="n">
+        <v>9</v>
+      </c>
+      <c r="D21" s="15" t="n">
+        <v>5</v>
+      </c>
+      <c r="E21" s="17" t="n">
+        <v>0.4062201064075089</v>
+      </c>
+      <c r="F21" s="17" t="n">
+        <v>0.2255770812957381</v>
+      </c>
+      <c r="G21" s="17" t="n">
+        <v>0.1806430251117707</v>
+      </c>
+      <c r="H21" s="17" t="n">
+        <v>0.8068831507598295</v>
+      </c>
+      <c r="I21" s="17" t="n">
+        <v>0.4666666666666667</v>
+      </c>
+      <c r="J21" s="16" t="n">
+        <v>0.1688311688311688</v>
+      </c>
+      <c r="K21" s="16" t="n">
+        <v>0.2781593406593406</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="14" t="inlineStr">
+        <is>
+          <t>GSE286068</t>
+        </is>
+      </c>
+      <c r="B22" s="14" t="inlineStr">
+        <is>
+          <t>high_activation_fraction</t>
+        </is>
+      </c>
+      <c r="C22" s="15" t="n">
+        <v>9</v>
+      </c>
+      <c r="D22" s="15" t="n">
+        <v>5</v>
+      </c>
+      <c r="E22" s="17" t="n">
+        <v>0.3100337148214352</v>
+      </c>
+      <c r="F22" s="17" t="n">
+        <v>0.2438852607105305</v>
+      </c>
+      <c r="G22" s="17" t="n">
+        <v>0.0661484541109047</v>
+      </c>
+      <c r="H22" s="17" t="n">
+        <v>0.5968982341569586</v>
+      </c>
+      <c r="I22" s="17" t="n">
+        <v>0.3333333333333333</v>
+      </c>
+      <c r="J22" s="16" t="n">
+        <v>0.3106893106893107</v>
+      </c>
+      <c r="K22" s="16" t="n">
+        <v>0.3797313797313797</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="14" t="inlineStr">
+        <is>
+          <t>GSE286068</t>
+        </is>
+      </c>
+      <c r="B23" s="14" t="inlineStr">
+        <is>
+          <t>activated_transition_fraction</t>
+        </is>
+      </c>
+      <c r="C23" s="15" t="n">
+        <v>9</v>
+      </c>
+      <c r="D23" s="15" t="n">
+        <v>5</v>
+      </c>
+      <c r="E23" s="17" t="n">
+        <v>0.1126698704229547</v>
+      </c>
+      <c r="F23" s="17" t="n">
+        <v>0.09584240377922899</v>
+      </c>
+      <c r="G23" s="17" t="n">
+        <v>0.0168274666437257</v>
+      </c>
+      <c r="H23" s="17" t="n">
+        <v>0.4411849936241344</v>
+      </c>
+      <c r="I23" s="17" t="n">
+        <v>0.2444444444444444</v>
+      </c>
+      <c r="J23" s="16" t="n">
+        <v>0.4365634365634365</v>
+      </c>
+      <c r="K23" s="16" t="n">
+        <v>0.4365634365634365</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="14" t="inlineStr">
+        <is>
+          <t>GSE286068</t>
+        </is>
+      </c>
+      <c r="B24" s="14" t="inlineStr">
+        <is>
+          <t>decoupled_inflammatory_fraction</t>
+        </is>
+      </c>
+      <c r="C24" s="15" t="n">
+        <v>9</v>
+      </c>
+      <c r="D24" s="15" t="n">
+        <v>5</v>
+      </c>
+      <c r="E24" s="17" t="n">
+        <v>0.2740483494438913</v>
+      </c>
+      <c r="F24" s="17" t="n">
+        <v>0.1523147284296158</v>
+      </c>
+      <c r="G24" s="17" t="n">
+        <v>0.1217336210142755</v>
+      </c>
+      <c r="H24" s="17" t="n">
+        <v>1.113613640530996</v>
+      </c>
+      <c r="I24" s="17" t="n">
+        <v>0.6888888888888889</v>
+      </c>
+      <c r="J24" s="16" t="n">
+        <v>0.0559440559440559</v>
+      </c>
+      <c r="K24" s="16" t="n">
+        <v>0.2781593406593406</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="14" t="inlineStr">
+        <is>
+          <t>GSE286068</t>
+        </is>
+      </c>
+      <c r="B25" s="14" t="inlineStr">
+        <is>
+          <t>continuous_decoupling_index</t>
+        </is>
+      </c>
+      <c r="C25" s="15" t="n">
+        <v>9</v>
+      </c>
+      <c r="D25" s="15" t="n">
+        <v>5</v>
+      </c>
+      <c r="E25" s="17" t="n">
+        <v>0.2448714594153185</v>
+      </c>
+      <c r="F25" s="17" t="n">
+        <v>0.0806747975402563</v>
+      </c>
+      <c r="G25" s="17" t="n">
+        <v>0.1641966618750621</v>
+      </c>
+      <c r="H25" s="17" t="n">
+        <v>1.106698680091002</v>
+      </c>
+      <c r="I25" s="17" t="n">
+        <v>0.8222222222222222</v>
+      </c>
+      <c r="J25" s="16" t="n">
+        <v>0.0369630369630369</v>
+      </c>
+      <c r="K25" s="16" t="n">
+        <v>0.2781593406593406</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="14" t="inlineStr">
+        <is>
+          <t>GSE286068</t>
+        </is>
+      </c>
+      <c r="B26" s="14" t="inlineStr">
+        <is>
+          <t>strict_BAM_mean_activation_residual</t>
+        </is>
+      </c>
+      <c r="C26" s="15" t="n">
+        <v>9</v>
+      </c>
+      <c r="D26" s="15" t="n">
+        <v>5</v>
+      </c>
+      <c r="E26" s="17" t="n">
+        <v>0.3938442019108682</v>
+      </c>
+      <c r="F26" s="17" t="n">
+        <v>0.1123435194356714</v>
+      </c>
+      <c r="G26" s="17" t="n">
+        <v>0.2815006824751968</v>
+      </c>
+      <c r="H26" s="17" t="n">
+        <v>0.9401439885128992</v>
+      </c>
+      <c r="I26" s="17" t="n">
+        <v>0.4666666666666667</v>
+      </c>
+      <c r="J26" s="16" t="n">
+        <v>0.1208791208791208</v>
+      </c>
+      <c r="K26" s="16" t="n">
+        <v>0.2781593406593406</v>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A4:K26"/>
+  <mergeCells count="2">
+    <mergeCell ref="A2:K2"/>
+    <mergeCell ref="A1:K1"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
+  <tableParts count="1">
+    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+  </tableParts>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:G6"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="33" customWidth="1" min="1" max="1"/>
+    <col width="11" customWidth="1" min="2" max="2"/>
+    <col width="22" customWidth="1" min="3" max="3"/>
+    <col width="20" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="5" max="5"/>
+    <col width="26" customWidth="1" min="6" max="6"/>
+    <col width="20" customWidth="1" min="7" max="7"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="24" customHeight="1">
+      <c r="A1" s="11" t="inlineStr">
+        <is>
+          <t>Primary disease meta-analysis across GSE138266, GSE286068 and new GSE328265 participants; BH correction across the two prespecified endpoints.</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="26" customHeight="1">
+      <c r="A2" s="12" t="inlineStr">
+        <is>
+          <t>Source: results/external_validation/GSE328265_two_axis_projection/three_cohort_two_axis_meta.csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="30" customHeight="1">
+      <c r="A4" s="13" t="inlineStr">
+        <is>
+          <t>endpoint</t>
+        </is>
+      </c>
+      <c r="B4" s="13" t="inlineStr">
+        <is>
+          <t>n_cohorts</t>
+        </is>
+      </c>
+      <c r="C4" s="13" t="inlineStr">
+        <is>
+          <t>direction_concordant</t>
+        </is>
+      </c>
+      <c r="D4" s="13" t="inlineStr">
+        <is>
+          <t>combined_z</t>
+        </is>
+      </c>
+      <c r="E4" s="13" t="inlineStr">
+        <is>
+          <t>stouffer_p</t>
+        </is>
+      </c>
+      <c r="F4" s="13" t="inlineStr">
+        <is>
+          <t>mean_standardized_effect</t>
+        </is>
+      </c>
+      <c r="G4" s="13" t="inlineStr">
+        <is>
+          <t>fdr_bh</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="14" t="inlineStr">
+        <is>
+          <t>continuous_decoupling_index</t>
+        </is>
+      </c>
+      <c r="B5" s="15" t="n">
+        <v>3</v>
+      </c>
+      <c r="C5" s="17" t="b">
+        <v>1</v>
+      </c>
+      <c r="D5" s="17" t="n">
+        <v>2.752995059780349</v>
+      </c>
+      <c r="E5" s="16" t="n">
+        <v>0.0059052787348498</v>
+      </c>
+      <c r="F5" s="17" t="n">
+        <v>0.9434639457498912</v>
+      </c>
+      <c r="G5" s="16" t="n">
+        <v>0.0077832065388081</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="14" t="inlineStr">
+        <is>
+          <t>decoupled_inflammatory_fraction</t>
+        </is>
+      </c>
+      <c r="B6" s="15" t="n">
+        <v>3</v>
+      </c>
+      <c r="C6" s="17" t="b">
+        <v>1</v>
+      </c>
+      <c r="D6" s="17" t="n">
+        <v>2.661332455985798</v>
+      </c>
+      <c r="E6" s="16" t="n">
+        <v>0.0077832065388081</v>
+      </c>
+      <c r="F6" s="17" t="n">
+        <v>1.020878479503806</v>
+      </c>
+      <c r="G6" s="16" t="n">
+        <v>0.0077832065388081</v>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A4:G6"/>
+  <mergeCells count="2">
+    <mergeCell ref="A2:G2"/>
+    <mergeCell ref="A1:G1"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
+  <tableParts count="1">
+    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+  </tableParts>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -1440,7 +4565,7 @@
     <row r="1" ht="24" customHeight="1">
       <c r="A1" s="11" t="inlineStr">
         <is>
-          <t>Cross-cohort two-axis meta-analysis.</t>
+          <t>Discovery-only two-cohort meta-analysis across 11 two-axis endpoints; BH correction across this 11-test family.</t>
         </is>
       </c>
     </row>
@@ -1777,7 +4902,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -1798,7 +4923,7 @@
     <row r="1" ht="24" customHeight="1">
       <c r="A1" s="11" t="inlineStr">
         <is>
-          <t>Prespecified decoupling-threshold sensitivity grid.</t>
+          <t>Decoupling-threshold sensitivity grid in the two disease discovery cohorts, GSE138266 and GSE286068.</t>
         </is>
       </c>
     </row>
@@ -2320,7 +5445,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -4479,7 +7604,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -4499,7 +7624,7 @@
     <row r="1" ht="24" customHeight="1">
       <c r="A1" s="11" t="inlineStr">
         <is>
-          <t>Per-cohort availability of ortholog-mapped LAM genes.</t>
+          <t>Per-cohort availability of requested scoring genes in the human LAM and ortholog-mapped mouse programs.</t>
         </is>
       </c>
     </row>
@@ -4944,7 +8069,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -11923,7 +15048,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -12543,7 +15668,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -18115,7 +21240,7 @@
     <row r="1" ht="24" customHeight="1">
       <c r="A1" s="11" t="inlineStr">
         <is>
-          <t>Root-to-terminal topology audit.</t>
+          <t>Single-root DPT and independent topology diagnostics; separate from the multiroot Figure 1e baseline.</t>
         </is>
       </c>
     </row>
@@ -18360,7 +21485,7 @@
     <row r="1" ht="24" customHeight="1">
       <c r="A1" s="11" t="inlineStr">
         <is>
-          <t>Within-donor concordance of trajectory representations.</t>
+          <t>Within-cohort cell-level Spearman correlations among four trajectory representations; 48 entries from three 4-by-4 matrices, not donor comparisons.</t>
         </is>
       </c>
     </row>
@@ -19368,6 +22493,525 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:L10"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="11" customWidth="1" min="1" max="1"/>
+    <col width="17" customWidth="1" min="2" max="2"/>
+    <col width="42" customWidth="1" min="3" max="3"/>
+    <col width="9" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="15" customWidth="1" min="6" max="6"/>
+    <col width="9" customWidth="1" min="7" max="7"/>
+    <col width="12" customWidth="1" min="8" max="8"/>
+    <col width="27" customWidth="1" min="9" max="9"/>
+    <col width="31" customWidth="1" min="10" max="10"/>
+    <col width="42" customWidth="1" min="11" max="11"/>
+    <col width="42" customWidth="1" min="12" max="12"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="24" customHeight="1">
+      <c r="A1" s="11" t="inlineStr">
+        <is>
+          <t>Full-cohort multiroot DPT endpoint AUCs from saved cell scores; primary representation supplies the Figure 1e baseline.</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="26" customHeight="1">
+      <c r="A2" s="12" t="inlineStr">
+        <is>
+          <t>Source: results/trajectory/full_multiroot_endpoint_auc.csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="30" customHeight="1">
+      <c r="A4" s="13" t="inlineStr">
+        <is>
+          <t>dataset</t>
+        </is>
+      </c>
+      <c r="B4" s="13" t="inlineStr">
+        <is>
+          <t>representation</t>
+        </is>
+      </c>
+      <c r="C4" s="13" t="inlineStr">
+        <is>
+          <t>method</t>
+        </is>
+      </c>
+      <c r="D4" s="13" t="inlineStr">
+        <is>
+          <t>n_cells</t>
+        </is>
+      </c>
+      <c r="E4" s="13" t="inlineStr">
+        <is>
+          <t>n_subjects</t>
+        </is>
+      </c>
+      <c r="F4" s="13" t="inlineStr">
+        <is>
+          <t>n_root_donors</t>
+        </is>
+      </c>
+      <c r="G4" s="13" t="inlineStr">
+        <is>
+          <t>n_root</t>
+        </is>
+      </c>
+      <c r="H4" s="13" t="inlineStr">
+        <is>
+          <t>n_terminal</t>
+        </is>
+      </c>
+      <c r="I4" s="13" t="inlineStr">
+        <is>
+          <t>full_terminal_vs_root_auc</t>
+        </is>
+      </c>
+      <c r="J4" s="13" t="inlineStr">
+        <is>
+          <t>score_column</t>
+        </is>
+      </c>
+      <c r="K4" s="13" t="inlineStr">
+        <is>
+          <t>source</t>
+        </is>
+      </c>
+      <c r="L4" s="13" t="inlineStr">
+        <is>
+          <t>comparison</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="14" t="inlineStr">
+        <is>
+          <t>GSE138266</t>
+        </is>
+      </c>
+      <c r="B5" s="14" t="inlineStr">
+        <is>
+          <t>primary</t>
+        </is>
+      </c>
+      <c r="C5" s="14" t="inlineStr">
+        <is>
+          <t>DPT: median percentile rank across donor roots</t>
+        </is>
+      </c>
+      <c r="D5" s="15" t="n">
+        <v>7153</v>
+      </c>
+      <c r="E5" s="15" t="n">
+        <v>12</v>
+      </c>
+      <c r="F5" s="15" t="n">
+        <v>10</v>
+      </c>
+      <c r="G5" s="15" t="n">
+        <v>3903</v>
+      </c>
+      <c r="H5" s="15" t="n">
+        <v>1626</v>
+      </c>
+      <c r="I5" s="17" t="n">
+        <v>0.9848029821574156</v>
+      </c>
+      <c r="J5" s="14" t="inlineStr">
+        <is>
+          <t>dpt_multiroot_primary</t>
+        </is>
+      </c>
+      <c r="K5" s="14" t="inlineStr">
+        <is>
+          <t>results/trajectory/continuum_objects/GSE138266_monocyte_BAM_continuum.h5ad</t>
+        </is>
+      </c>
+      <c r="L5" s="14" t="inlineStr">
+        <is>
+          <t>trajectory_role terminal_candidate versus root_candidate</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="14" t="inlineStr">
+        <is>
+          <t>GSE138266</t>
+        </is>
+      </c>
+      <c r="B6" s="14" t="inlineStr">
+        <is>
+          <t>marker_excluded</t>
+        </is>
+      </c>
+      <c r="C6" s="14" t="inlineStr">
+        <is>
+          <t>DPT: median percentile rank across donor roots</t>
+        </is>
+      </c>
+      <c r="D6" s="15" t="n">
+        <v>7153</v>
+      </c>
+      <c r="E6" s="15" t="n">
+        <v>12</v>
+      </c>
+      <c r="F6" s="15" t="n">
+        <v>10</v>
+      </c>
+      <c r="G6" s="15" t="n">
+        <v>3903</v>
+      </c>
+      <c r="H6" s="15" t="n">
+        <v>1626</v>
+      </c>
+      <c r="I6" s="17" t="n">
+        <v>0.9832763392968288</v>
+      </c>
+      <c r="J6" s="14" t="inlineStr">
+        <is>
+          <t>dpt_multiroot_marker_excluded</t>
+        </is>
+      </c>
+      <c r="K6" s="14" t="inlineStr">
+        <is>
+          <t>results/trajectory/continuum_objects/GSE138266_monocyte_BAM_continuum.h5ad</t>
+        </is>
+      </c>
+      <c r="L6" s="14" t="inlineStr">
+        <is>
+          <t>trajectory_role terminal_candidate versus root_candidate</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="14" t="inlineStr">
+        <is>
+          <t>GSE194078</t>
+        </is>
+      </c>
+      <c r="B7" s="14" t="inlineStr">
+        <is>
+          <t>primary</t>
+        </is>
+      </c>
+      <c r="C7" s="14" t="inlineStr">
+        <is>
+          <t>DPT: median percentile rank across donor roots</t>
+        </is>
+      </c>
+      <c r="D7" s="15" t="n">
+        <v>10432</v>
+      </c>
+      <c r="E7" s="15" t="n">
+        <v>11</v>
+      </c>
+      <c r="F7" s="15" t="n">
+        <v>11</v>
+      </c>
+      <c r="G7" s="15" t="n">
+        <v>5108</v>
+      </c>
+      <c r="H7" s="15" t="n">
+        <v>1096</v>
+      </c>
+      <c r="I7" s="17" t="n">
+        <v>0.8884284670103859</v>
+      </c>
+      <c r="J7" s="14" t="inlineStr">
+        <is>
+          <t>dpt_multiroot_primary</t>
+        </is>
+      </c>
+      <c r="K7" s="14" t="inlineStr">
+        <is>
+          <t>results/trajectory/continuum_objects/GSE194078_monocyte_BAM_continuum.h5ad</t>
+        </is>
+      </c>
+      <c r="L7" s="14" t="inlineStr">
+        <is>
+          <t>trajectory_role terminal_candidate versus root_candidate</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="14" t="inlineStr">
+        <is>
+          <t>GSE194078</t>
+        </is>
+      </c>
+      <c r="B8" s="14" t="inlineStr">
+        <is>
+          <t>marker_excluded</t>
+        </is>
+      </c>
+      <c r="C8" s="14" t="inlineStr">
+        <is>
+          <t>DPT: median percentile rank across donor roots</t>
+        </is>
+      </c>
+      <c r="D8" s="15" t="n">
+        <v>10432</v>
+      </c>
+      <c r="E8" s="15" t="n">
+        <v>11</v>
+      </c>
+      <c r="F8" s="15" t="n">
+        <v>11</v>
+      </c>
+      <c r="G8" s="15" t="n">
+        <v>5108</v>
+      </c>
+      <c r="H8" s="15" t="n">
+        <v>1096</v>
+      </c>
+      <c r="I8" s="17" t="n">
+        <v>0.9430641215439928</v>
+      </c>
+      <c r="J8" s="14" t="inlineStr">
+        <is>
+          <t>dpt_multiroot_marker_excluded</t>
+        </is>
+      </c>
+      <c r="K8" s="14" t="inlineStr">
+        <is>
+          <t>results/trajectory/continuum_objects/GSE194078_monocyte_BAM_continuum.h5ad</t>
+        </is>
+      </c>
+      <c r="L8" s="14" t="inlineStr">
+        <is>
+          <t>trajectory_role terminal_candidate versus root_candidate</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="14" t="inlineStr">
+        <is>
+          <t>GSE286068</t>
+        </is>
+      </c>
+      <c r="B9" s="14" t="inlineStr">
+        <is>
+          <t>primary</t>
+        </is>
+      </c>
+      <c r="C9" s="14" t="inlineStr">
+        <is>
+          <t>DPT: median percentile rank across donor roots</t>
+        </is>
+      </c>
+      <c r="D9" s="15" t="n">
+        <v>1855</v>
+      </c>
+      <c r="E9" s="15" t="n">
+        <v>15</v>
+      </c>
+      <c r="F9" s="15" t="n">
+        <v>13</v>
+      </c>
+      <c r="G9" s="15" t="n">
+        <v>742</v>
+      </c>
+      <c r="H9" s="15" t="n">
+        <v>593</v>
+      </c>
+      <c r="I9" s="17" t="n">
+        <v>0.6569717231128667</v>
+      </c>
+      <c r="J9" s="14" t="inlineStr">
+        <is>
+          <t>dpt_multiroot_primary</t>
+        </is>
+      </c>
+      <c r="K9" s="14" t="inlineStr">
+        <is>
+          <t>results/trajectory/continuum_objects/GSE286068_monocyte_BAM_continuum.h5ad</t>
+        </is>
+      </c>
+      <c r="L9" s="14" t="inlineStr">
+        <is>
+          <t>trajectory_role terminal_candidate versus root_candidate</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="14" t="inlineStr">
+        <is>
+          <t>GSE286068</t>
+        </is>
+      </c>
+      <c r="B10" s="14" t="inlineStr">
+        <is>
+          <t>marker_excluded</t>
+        </is>
+      </c>
+      <c r="C10" s="14" t="inlineStr">
+        <is>
+          <t>DPT: median percentile rank across donor roots</t>
+        </is>
+      </c>
+      <c r="D10" s="15" t="n">
+        <v>1855</v>
+      </c>
+      <c r="E10" s="15" t="n">
+        <v>15</v>
+      </c>
+      <c r="F10" s="15" t="n">
+        <v>13</v>
+      </c>
+      <c r="G10" s="15" t="n">
+        <v>742</v>
+      </c>
+      <c r="H10" s="15" t="n">
+        <v>593</v>
+      </c>
+      <c r="I10" s="17" t="n">
+        <v>0.6419128375522152</v>
+      </c>
+      <c r="J10" s="14" t="inlineStr">
+        <is>
+          <t>dpt_multiroot_marker_excluded</t>
+        </is>
+      </c>
+      <c r="K10" s="14" t="inlineStr">
+        <is>
+          <t>results/trajectory/continuum_objects/GSE286068_monocyte_BAM_continuum.h5ad</t>
+        </is>
+      </c>
+      <c r="L10" s="14" t="inlineStr">
+        <is>
+          <t>trajectory_role terminal_candidate versus root_candidate</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A4:L10"/>
+  <mergeCells count="2">
+    <mergeCell ref="A2:L2"/>
+    <mergeCell ref="A1:L1"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
+  <tableParts count="1">
+    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+  </tableParts>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:G5"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="9" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="9" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="22" customWidth="1" min="5" max="5"/>
+    <col width="22" customWidth="1" min="6" max="6"/>
+    <col width="40" customWidth="1" min="7" max="7"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="24" customHeight="1">
+      <c r="A1" s="11" t="inlineStr">
+        <is>
+          <t>External fixed-score projection: correlation with annotated state ordering and classical-monocyte versus BAM-like endpoint AUC.</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="26" customHeight="1">
+      <c r="A2" s="12" t="inlineStr">
+        <is>
+          <t>Source: results/external_validation/GSE328265_two_axis_projection/external_projection_topology.csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="30" customHeight="1">
+      <c r="A4" s="13" t="inlineStr">
+        <is>
+          <t>n_cells</t>
+        </is>
+      </c>
+      <c r="B4" s="13" t="inlineStr">
+        <is>
+          <t>n_subjects</t>
+        </is>
+      </c>
+      <c r="C4" s="13" t="inlineStr">
+        <is>
+          <t>n_root</t>
+        </is>
+      </c>
+      <c r="D4" s="13" t="inlineStr">
+        <is>
+          <t>n_terminal</t>
+        </is>
+      </c>
+      <c r="E4" s="13" t="inlineStr">
+        <is>
+          <t>state_order_spearman</t>
+        </is>
+      </c>
+      <c r="F4" s="13" t="inlineStr">
+        <is>
+          <t>terminal_vs_root_auc</t>
+        </is>
+      </c>
+      <c r="G4" s="13" t="inlineStr">
+        <is>
+          <t>terminal_score_cutpoint_from_discovery</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="15" t="n">
+        <v>3333</v>
+      </c>
+      <c r="B5" s="15" t="n">
+        <v>30</v>
+      </c>
+      <c r="C5" s="15" t="n">
+        <v>372</v>
+      </c>
+      <c r="D5" s="15" t="n">
+        <v>1194</v>
+      </c>
+      <c r="E5" s="17" t="n">
+        <v>0.5949148474253424</v>
+      </c>
+      <c r="F5" s="17" t="n">
+        <v>0.9982686731146774</v>
+      </c>
+      <c r="G5" s="17" t="n">
+        <v>0.4258517034068136</v>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A4:G5"/>
+  <mergeCells count="2">
+    <mergeCell ref="A2:G2"/>
+    <mergeCell ref="A1:G1"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
+  <tableParts count="1">
+    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+  </tableParts>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -22122,7 +25766,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -22145,7 +25789,7 @@
     <row r="1" ht="24" customHeight="1">
       <c r="A1" s="11" t="inlineStr">
         <is>
-          <t>Sensitivity to a multi-donor root definition.</t>
+          <t>Multi-donor-root DPT: gene-set concordance and correlations with annotated state ordering.</t>
         </is>
       </c>
     </row>
@@ -22308,2844 +25952,4 @@
     <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
   </tableParts>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr fitToPage="1"/>
-  </sheetPr>
-  <dimension ref="A1:R31"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="11" customWidth="1" min="1" max="1"/>
-    <col width="13" customWidth="1" min="2" max="2"/>
-    <col width="38" customWidth="1" min="3" max="3"/>
-    <col width="26" customWidth="1" min="4" max="4"/>
-    <col width="9" customWidth="1" min="5" max="5"/>
-    <col width="23" customWidth="1" min="6" max="6"/>
-    <col width="14" customWidth="1" min="7" max="7"/>
-    <col width="29" customWidth="1" min="8" max="8"/>
-    <col width="34" customWidth="1" min="9" max="9"/>
-    <col width="23" customWidth="1" min="10" max="10"/>
-    <col width="20" customWidth="1" min="11" max="11"/>
-    <col width="20" customWidth="1" min="12" max="12"/>
-    <col width="26" customWidth="1" min="13" max="13"/>
-    <col width="26" customWidth="1" min="14" max="14"/>
-    <col width="31" customWidth="1" min="15" max="15"/>
-    <col width="33" customWidth="1" min="16" max="16"/>
-    <col width="29" customWidth="1" min="17" max="17"/>
-    <col width="37" customWidth="1" min="18" max="18"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="24" customHeight="1">
-      <c r="A1" s="11" t="inlineStr">
-        <is>
-          <t>Donor-level differentiation, activation residual and decoupling scores.</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="26" customHeight="1">
-      <c r="A2" s="12" t="inlineStr">
-        <is>
-          <t>Source: results/two_axis/two_axis_donor_scores.csv</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="30" customHeight="1">
-      <c r="A4" s="13" t="inlineStr">
-        <is>
-          <t>dataset</t>
-        </is>
-      </c>
-      <c r="B4" s="13" t="inlineStr">
-        <is>
-          <t>subject_id</t>
-        </is>
-      </c>
-      <c r="C4" s="13" t="inlineStr">
-        <is>
-          <t>diagnosis</t>
-        </is>
-      </c>
-      <c r="D4" s="13" t="inlineStr">
-        <is>
-          <t>disease_group</t>
-        </is>
-      </c>
-      <c r="E4" s="13" t="inlineStr">
-        <is>
-          <t>is_MS</t>
-        </is>
-      </c>
-      <c r="F4" s="13" t="inlineStr">
-        <is>
-          <t>n_CSF_continuum_cells</t>
-        </is>
-      </c>
-      <c r="G4" s="13" t="inlineStr">
-        <is>
-          <t>n_strict_BAM</t>
-        </is>
-      </c>
-      <c r="H4" s="13" t="inlineStr">
-        <is>
-          <t>median_consensus_pseudotime</t>
-        </is>
-      </c>
-      <c r="I4" s="13" t="inlineStr">
-        <is>
-          <t>median_BAM_macrostate_membership</t>
-        </is>
-      </c>
-      <c r="J4" s="13" t="inlineStr">
-        <is>
-          <t>transitional_fraction</t>
-        </is>
-      </c>
-      <c r="K4" s="13" t="inlineStr">
-        <is>
-          <t>terminal_fraction</t>
-        </is>
-      </c>
-      <c r="L4" s="13" t="inlineStr">
-        <is>
-          <t>transition_entropy</t>
-        </is>
-      </c>
-      <c r="M4" s="13" t="inlineStr">
-        <is>
-          <t>mean_activation_residual</t>
-        </is>
-      </c>
-      <c r="N4" s="13" t="inlineStr">
-        <is>
-          <t>high_activation_fraction</t>
-        </is>
-      </c>
-      <c r="O4" s="13" t="inlineStr">
-        <is>
-          <t>activated_transition_fraction</t>
-        </is>
-      </c>
-      <c r="P4" s="13" t="inlineStr">
-        <is>
-          <t>decoupled_inflammatory_fraction</t>
-        </is>
-      </c>
-      <c r="Q4" s="13" t="inlineStr">
-        <is>
-          <t>continuous_decoupling_index</t>
-        </is>
-      </c>
-      <c r="R4" s="13" t="inlineStr">
-        <is>
-          <t>strict_BAM_mean_activation_residual</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="14" t="inlineStr">
-        <is>
-          <t>GSE138266</t>
-        </is>
-      </c>
-      <c r="B5" s="14" t="inlineStr">
-        <is>
-          <t>MS19270</t>
-        </is>
-      </c>
-      <c r="C5" s="14" t="inlineStr">
-        <is>
-          <t>Multiple Sclerosis</t>
-        </is>
-      </c>
-      <c r="D5" s="14" t="inlineStr">
-        <is>
-          <t>MS</t>
-        </is>
-      </c>
-      <c r="E5" s="17" t="b">
-        <v>1</v>
-      </c>
-      <c r="F5" s="15" t="n">
-        <v>104</v>
-      </c>
-      <c r="G5" s="15" t="n">
-        <v>41</v>
-      </c>
-      <c r="H5" s="16" t="n">
-        <v>0.7232599854469299</v>
-      </c>
-      <c r="I5" s="17" t="n">
-        <v>0.5388032417743196</v>
-      </c>
-      <c r="J5" s="17" t="n">
-        <v>0.7596153846153846</v>
-      </c>
-      <c r="K5" s="17" t="n">
-        <v>0.2403846153846154</v>
-      </c>
-      <c r="L5" s="17" t="n">
-        <v>0.5020177424645625</v>
-      </c>
-      <c r="M5" s="17" t="n">
-        <v>0.5567013394740564</v>
-      </c>
-      <c r="N5" s="17" t="n">
-        <v>0.4423076923076923</v>
-      </c>
-      <c r="O5" s="17" t="n">
-        <v>0.3461538461538461</v>
-      </c>
-      <c r="P5" s="17" t="n">
-        <v>0.3461538461538461</v>
-      </c>
-      <c r="Q5" s="17" t="n">
-        <v>0.1514648202239471</v>
-      </c>
-      <c r="R5" s="17" t="n">
-        <v>0.5911054974000713</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="14" t="inlineStr">
-        <is>
-          <t>GSE138266</t>
-        </is>
-      </c>
-      <c r="B6" s="14" t="inlineStr">
-        <is>
-          <t>MS49131</t>
-        </is>
-      </c>
-      <c r="C6" s="14" t="inlineStr">
-        <is>
-          <t>Multiple Sclerosis</t>
-        </is>
-      </c>
-      <c r="D6" s="14" t="inlineStr">
-        <is>
-          <t>MS</t>
-        </is>
-      </c>
-      <c r="E6" s="17" t="b">
-        <v>1</v>
-      </c>
-      <c r="F6" s="15" t="n">
-        <v>46</v>
-      </c>
-      <c r="G6" s="15" t="n">
-        <v>18</v>
-      </c>
-      <c r="H6" s="16" t="n">
-        <v>0.7833601236343384</v>
-      </c>
-      <c r="I6" s="17" t="n">
-        <v>0.2021073620961675</v>
-      </c>
-      <c r="J6" s="17" t="n">
-        <v>0.5869565217391305</v>
-      </c>
-      <c r="K6" s="17" t="n">
-        <v>0.4130434782608695</v>
-      </c>
-      <c r="L6" s="17" t="n">
-        <v>0.6170940766917039</v>
-      </c>
-      <c r="M6" s="17" t="n">
-        <v>0.8349914205798777</v>
-      </c>
-      <c r="N6" s="17" t="n">
-        <v>0.5217391304347826</v>
-      </c>
-      <c r="O6" s="17" t="n">
-        <v>0.3260869565217391</v>
-      </c>
-      <c r="P6" s="17" t="n">
-        <v>0.3260869565217391</v>
-      </c>
-      <c r="Q6" s="17" t="n">
-        <v>0.2646362940283152</v>
-      </c>
-      <c r="R6" s="17" t="n">
-        <v>0.4691126765948766</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="14" t="inlineStr">
-        <is>
-          <t>GSE138266</t>
-        </is>
-      </c>
-      <c r="B7" s="14" t="inlineStr">
-        <is>
-          <t>MS58637</t>
-        </is>
-      </c>
-      <c r="C7" s="14" t="inlineStr">
-        <is>
-          <t>Multiple Sclerosis</t>
-        </is>
-      </c>
-      <c r="D7" s="14" t="inlineStr">
-        <is>
-          <t>MS</t>
-        </is>
-      </c>
-      <c r="E7" s="17" t="b">
-        <v>1</v>
-      </c>
-      <c r="F7" s="15" t="n">
-        <v>40</v>
-      </c>
-      <c r="G7" s="15" t="n">
-        <v>26</v>
-      </c>
-      <c r="H7" s="16" t="n">
-        <v>0.877487450838089</v>
-      </c>
-      <c r="I7" s="17" t="n">
-        <v>0.5405228983253981</v>
-      </c>
-      <c r="J7" s="17" t="n">
-        <v>0.275</v>
-      </c>
-      <c r="K7" s="17" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="L7" s="17" t="n">
-        <v>0.6343594588921255</v>
-      </c>
-      <c r="M7" s="17" t="n">
-        <v>0.7403719693265879</v>
-      </c>
-      <c r="N7" s="17" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="O7" s="17" t="n">
-        <v>0.125</v>
-      </c>
-      <c r="P7" s="17" t="n">
-        <v>0.15</v>
-      </c>
-      <c r="Q7" s="17" t="n">
-        <v>0.1183054677884492</v>
-      </c>
-      <c r="R7" s="17" t="n">
-        <v>0.8702095908011789</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="14" t="inlineStr">
-        <is>
-          <t>GSE138266</t>
-        </is>
-      </c>
-      <c r="B8" s="14" t="inlineStr">
-        <is>
-          <t>MS60249</t>
-        </is>
-      </c>
-      <c r="C8" s="14" t="inlineStr">
-        <is>
-          <t>Multiple Sclerosis</t>
-        </is>
-      </c>
-      <c r="D8" s="14" t="inlineStr">
-        <is>
-          <t>MS</t>
-        </is>
-      </c>
-      <c r="E8" s="17" t="b">
-        <v>1</v>
-      </c>
-      <c r="F8" s="15" t="n">
-        <v>92</v>
-      </c>
-      <c r="G8" s="15" t="n">
-        <v>38</v>
-      </c>
-      <c r="H8" s="16" t="n">
-        <v>0.8137178719043732</v>
-      </c>
-      <c r="I8" s="17" t="n">
-        <v>0.4733691433839063</v>
-      </c>
-      <c r="J8" s="17" t="n">
-        <v>0.4673913043478261</v>
-      </c>
-      <c r="K8" s="17" t="n">
-        <v>0.5108695652173914</v>
-      </c>
-      <c r="L8" s="17" t="n">
-        <v>0.7116657157845907</v>
-      </c>
-      <c r="M8" s="17" t="n">
-        <v>1.34008985270828</v>
-      </c>
-      <c r="N8" s="17" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="O8" s="17" t="n">
-        <v>0.3804347826086957</v>
-      </c>
-      <c r="P8" s="17" t="n">
-        <v>0.4021739130434782</v>
-      </c>
-      <c r="Q8" s="17" t="n">
-        <v>0.2949879041357146</v>
-      </c>
-      <c r="R8" s="17" t="n">
-        <v>1.400411591573747</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="14" t="inlineStr">
-        <is>
-          <t>GSE138266</t>
-        </is>
-      </c>
-      <c r="B9" s="14" t="inlineStr">
-        <is>
-          <t>MS71658</t>
-        </is>
-      </c>
-      <c r="C9" s="14" t="inlineStr">
-        <is>
-          <t>Multiple Sclerosis</t>
-        </is>
-      </c>
-      <c r="D9" s="14" t="inlineStr">
-        <is>
-          <t>MS</t>
-        </is>
-      </c>
-      <c r="E9" s="17" t="b">
-        <v>1</v>
-      </c>
-      <c r="F9" s="15" t="n">
-        <v>204</v>
-      </c>
-      <c r="G9" s="15" t="n">
-        <v>134</v>
-      </c>
-      <c r="H9" s="16" t="n">
-        <v>0.7869678437709808</v>
-      </c>
-      <c r="I9" s="17" t="n">
-        <v>0.5688260133761005</v>
-      </c>
-      <c r="J9" s="17" t="n">
-        <v>0.5637254901960784</v>
-      </c>
-      <c r="K9" s="17" t="n">
-        <v>0.4362745098039216</v>
-      </c>
-      <c r="L9" s="17" t="n">
-        <v>0.6235167574659428</v>
-      </c>
-      <c r="M9" s="17" t="n">
-        <v>0.4560201604800572</v>
-      </c>
-      <c r="N9" s="17" t="n">
-        <v>0.3627450980392157</v>
-      </c>
-      <c r="O9" s="17" t="n">
-        <v>0.2205882352941176</v>
-      </c>
-      <c r="P9" s="17" t="n">
-        <v>0.2205882352941176</v>
-      </c>
-      <c r="Q9" s="17" t="n">
-        <v>0.1034398564808644</v>
-      </c>
-      <c r="R9" s="17" t="n">
-        <v>0.4425691692294677</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="14" t="inlineStr">
-        <is>
-          <t>GSE138266</t>
-        </is>
-      </c>
-      <c r="B10" s="14" t="inlineStr">
-        <is>
-          <t>MS74594</t>
-        </is>
-      </c>
-      <c r="C10" s="14" t="inlineStr">
-        <is>
-          <t>Multiple Sclerosis</t>
-        </is>
-      </c>
-      <c r="D10" s="14" t="inlineStr">
-        <is>
-          <t>MS</t>
-        </is>
-      </c>
-      <c r="E10" s="17" t="b">
-        <v>1</v>
-      </c>
-      <c r="F10" s="15" t="n">
-        <v>45</v>
-      </c>
-      <c r="G10" s="15" t="n">
-        <v>24</v>
-      </c>
-      <c r="H10" s="16" t="n">
-        <v>0.7892842292785645</v>
-      </c>
-      <c r="I10" s="17" t="n">
-        <v>0.0880015537950961</v>
-      </c>
-      <c r="J10" s="17" t="n">
-        <v>0.5555555555555556</v>
-      </c>
-      <c r="K10" s="17" t="n">
-        <v>0.4444444444444444</v>
-      </c>
-      <c r="L10" s="17" t="n">
-        <v>0.6252993742043005</v>
-      </c>
-      <c r="M10" s="17" t="n">
-        <v>0.0194980246235419</v>
-      </c>
-      <c r="N10" s="17" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="O10" s="17" t="n">
-        <v>0.0888888888888888</v>
-      </c>
-      <c r="P10" s="17" t="n">
-        <v>0.0888888888888888</v>
-      </c>
-      <c r="Q10" s="17" t="n">
-        <v>-0.0001542660779688</v>
-      </c>
-      <c r="R10" s="17" t="n">
-        <v>0.0080175638454986</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="14" t="inlineStr">
-        <is>
-          <t>GSE138266</t>
-        </is>
-      </c>
-      <c r="B11" s="14" t="inlineStr">
-        <is>
-          <t>PST83775</t>
-        </is>
-      </c>
-      <c r="C11" s="14" t="inlineStr">
-        <is>
-          <t>idiopathic intracranial hypertension</t>
-        </is>
-      </c>
-      <c r="D11" s="14" t="inlineStr">
-        <is>
-          <t>IIH_control</t>
-        </is>
-      </c>
-      <c r="E11" s="17" t="b">
-        <v>0</v>
-      </c>
-      <c r="F11" s="15" t="n">
-        <v>196</v>
-      </c>
-      <c r="G11" s="15" t="n">
-        <v>134</v>
-      </c>
-      <c r="H11" s="16" t="n">
-        <v>0.8788898289203644</v>
-      </c>
-      <c r="I11" s="17" t="n">
-        <v>0.6104226298045529</v>
-      </c>
-      <c r="J11" s="17" t="n">
-        <v>0.3163265306122449</v>
-      </c>
-      <c r="K11" s="17" t="n">
-        <v>0.6785714285714286</v>
-      </c>
-      <c r="L11" s="17" t="n">
-        <v>0.5954251289881962</v>
-      </c>
-      <c r="M11" s="17" t="n">
-        <v>0.2411390982486199</v>
-      </c>
-      <c r="N11" s="17" t="n">
-        <v>0.2142857142857142</v>
-      </c>
-      <c r="O11" s="17" t="n">
-        <v>0.1020408163265306</v>
-      </c>
-      <c r="P11" s="17" t="n">
-        <v>0.1020408163265306</v>
-      </c>
-      <c r="Q11" s="17" t="n">
-        <v>0.0556461588055336</v>
-      </c>
-      <c r="R11" s="17" t="n">
-        <v>0.1249396387155572</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="14" t="inlineStr">
-        <is>
-          <t>GSE138266</t>
-        </is>
-      </c>
-      <c r="B12" s="14" t="inlineStr">
-        <is>
-          <t>PST95809</t>
-        </is>
-      </c>
-      <c r="C12" s="14" t="inlineStr">
-        <is>
-          <t>idiopathic intracranial hypertension</t>
-        </is>
-      </c>
-      <c r="D12" s="14" t="inlineStr">
-        <is>
-          <t>IIH_control</t>
-        </is>
-      </c>
-      <c r="E12" s="17" t="b">
-        <v>0</v>
-      </c>
-      <c r="F12" s="15" t="n">
-        <v>119</v>
-      </c>
-      <c r="G12" s="15" t="n">
-        <v>96</v>
-      </c>
-      <c r="H12" s="16" t="n">
-        <v>0.877813458442688</v>
-      </c>
-      <c r="I12" s="17" t="n">
-        <v>0.4169587572874052</v>
-      </c>
-      <c r="J12" s="17" t="n">
-        <v>0.2689075630252101</v>
-      </c>
-      <c r="K12" s="17" t="n">
-        <v>0.7310924369747899</v>
-      </c>
-      <c r="L12" s="17" t="n">
-        <v>0.5299132857268382</v>
-      </c>
-      <c r="M12" s="17" t="n">
-        <v>0.7944480896275485</v>
-      </c>
-      <c r="N12" s="17" t="n">
-        <v>0.5546218487394958</v>
-      </c>
-      <c r="O12" s="17" t="n">
-        <v>0.1512605042016806</v>
-      </c>
-      <c r="P12" s="17" t="n">
-        <v>0.1512605042016806</v>
-      </c>
-      <c r="Q12" s="17" t="n">
-        <v>0.1350077316683199</v>
-      </c>
-      <c r="R12" s="17" t="n">
-        <v>0.7674699153042578</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="14" t="inlineStr">
-        <is>
-          <t>GSE138266</t>
-        </is>
-      </c>
-      <c r="B13" s="14" t="inlineStr">
-        <is>
-          <t>PTC32190</t>
-        </is>
-      </c>
-      <c r="C13" s="14" t="inlineStr">
-        <is>
-          <t>idiopathic intracranial hypertension</t>
-        </is>
-      </c>
-      <c r="D13" s="14" t="inlineStr">
-        <is>
-          <t>IIH_control</t>
-        </is>
-      </c>
-      <c r="E13" s="17" t="b">
-        <v>0</v>
-      </c>
-      <c r="F13" s="15" t="n">
-        <v>702</v>
-      </c>
-      <c r="G13" s="15" t="n">
-        <v>444</v>
-      </c>
-      <c r="H13" s="16" t="n">
-        <v>0.8271615505218506</v>
-      </c>
-      <c r="I13" s="17" t="n">
-        <v>0.607546557451215</v>
-      </c>
-      <c r="J13" s="17" t="n">
-        <v>0.4131054131054131</v>
-      </c>
-      <c r="K13" s="17" t="n">
-        <v>0.5754985754985755</v>
-      </c>
-      <c r="L13" s="17" t="n">
-        <v>0.6682720172560471</v>
-      </c>
-      <c r="M13" s="17" t="n">
-        <v>-0.0301954668942068</v>
-      </c>
-      <c r="N13" s="17" t="n">
-        <v>0.150997150997151</v>
-      </c>
-      <c r="O13" s="17" t="n">
-        <v>0.0541310541310541</v>
-      </c>
-      <c r="P13" s="17" t="n">
-        <v>0.0569800569800569</v>
-      </c>
-      <c r="Q13" s="17" t="n">
-        <v>-0.0073492491272099</v>
-      </c>
-      <c r="R13" s="17" t="n">
-        <v>-0.0090943222271186</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="14" t="inlineStr">
-        <is>
-          <t>GSE138266</t>
-        </is>
-      </c>
-      <c r="B14" s="14" t="inlineStr">
-        <is>
-          <t>PTC41540</t>
-        </is>
-      </c>
-      <c r="C14" s="14" t="inlineStr">
-        <is>
-          <t>idiopathic intracranial hypertension</t>
-        </is>
-      </c>
-      <c r="D14" s="14" t="inlineStr">
-        <is>
-          <t>IIH_control</t>
-        </is>
-      </c>
-      <c r="E14" s="17" t="b">
-        <v>0</v>
-      </c>
-      <c r="F14" s="15" t="n">
-        <v>250</v>
-      </c>
-      <c r="G14" s="15" t="n">
-        <v>161</v>
-      </c>
-      <c r="H14" s="16" t="n">
-        <v>0.7846416831016541</v>
-      </c>
-      <c r="I14" s="17" t="n">
-        <v>0.5014953054743516</v>
-      </c>
-      <c r="J14" s="17" t="n">
-        <v>0.584</v>
-      </c>
-      <c r="K14" s="17" t="n">
-        <v>0.412</v>
-      </c>
-      <c r="L14" s="17" t="n">
-        <v>0.6385567637191237</v>
-      </c>
-      <c r="M14" s="17" t="n">
-        <v>0.1816929560457884</v>
-      </c>
-      <c r="N14" s="17" t="n">
-        <v>0.248</v>
-      </c>
-      <c r="O14" s="17" t="n">
-        <v>0.164</v>
-      </c>
-      <c r="P14" s="17" t="n">
-        <v>0.164</v>
-      </c>
-      <c r="Q14" s="17" t="n">
-        <v>0.0455162487864626</v>
-      </c>
-      <c r="R14" s="17" t="n">
-        <v>0.1531378175915024</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="14" t="inlineStr">
-        <is>
-          <t>GSE138266</t>
-        </is>
-      </c>
-      <c r="B15" s="14" t="inlineStr">
-        <is>
-          <t>PTC45044</t>
-        </is>
-      </c>
-      <c r="C15" s="14" t="inlineStr">
-        <is>
-          <t>idiopathic intracranial hypertension</t>
-        </is>
-      </c>
-      <c r="D15" s="14" t="inlineStr">
-        <is>
-          <t>IIH_control</t>
-        </is>
-      </c>
-      <c r="E15" s="17" t="b">
-        <v>0</v>
-      </c>
-      <c r="F15" s="15" t="n">
-        <v>652</v>
-      </c>
-      <c r="G15" s="15" t="n">
-        <v>500</v>
-      </c>
-      <c r="H15" s="16" t="n">
-        <v>0.8487563729286194</v>
-      </c>
-      <c r="I15" s="17" t="n">
-        <v>0.6223644764890602</v>
-      </c>
-      <c r="J15" s="17" t="n">
-        <v>0.3251533742331288</v>
-      </c>
-      <c r="K15" s="17" t="n">
-        <v>0.6733128834355828</v>
-      </c>
-      <c r="L15" s="17" t="n">
-        <v>0.5839736391845903</v>
-      </c>
-      <c r="M15" s="17" t="n">
-        <v>0.3520724684197478</v>
-      </c>
-      <c r="N15" s="17" t="n">
-        <v>0.3144171779141104</v>
-      </c>
-      <c r="O15" s="17" t="n">
-        <v>0.1088957055214723</v>
-      </c>
-      <c r="P15" s="17" t="n">
-        <v>0.1088957055214723</v>
-      </c>
-      <c r="Q15" s="17" t="n">
-        <v>0.0579700077840579</v>
-      </c>
-      <c r="R15" s="17" t="n">
-        <v>0.3466065865871055</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="14" t="inlineStr">
-        <is>
-          <t>GSE138266</t>
-        </is>
-      </c>
-      <c r="B16" s="14" t="inlineStr">
-        <is>
-          <t>PTC85037</t>
-        </is>
-      </c>
-      <c r="C16" s="14" t="inlineStr">
-        <is>
-          <t>idiopathic intracranial hypertension</t>
-        </is>
-      </c>
-      <c r="D16" s="14" t="inlineStr">
-        <is>
-          <t>IIH_control</t>
-        </is>
-      </c>
-      <c r="E16" s="17" t="b">
-        <v>0</v>
-      </c>
-      <c r="F16" s="15" t="n">
-        <v>19</v>
-      </c>
-      <c r="G16" s="15" t="n">
-        <v>10</v>
-      </c>
-      <c r="H16" s="16" t="n">
-        <v>0.7453516125679016</v>
-      </c>
-      <c r="I16" s="17" t="n">
-        <v>0.0985785027829916</v>
-      </c>
-      <c r="J16" s="17" t="n">
-        <v>0.6842105263157895</v>
-      </c>
-      <c r="K16" s="17" t="n">
-        <v>0.3157894736842105</v>
-      </c>
-      <c r="L16" s="17" t="n">
-        <v>0.5676751079529516</v>
-      </c>
-      <c r="M16" s="17" t="n">
-        <v>0.1289137961254477</v>
-      </c>
-      <c r="N16" s="17" t="n">
-        <v>0.2105263157894736</v>
-      </c>
-      <c r="O16" s="17" t="n">
-        <v>0</v>
-      </c>
-      <c r="P16" s="17" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q16" s="17" t="n">
-        <v>0.0255336016337123</v>
-      </c>
-      <c r="R16" s="17" t="n">
-        <v>0.2736767976919746</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="14" t="inlineStr">
-        <is>
-          <t>GSE286068</t>
-        </is>
-      </c>
-      <c r="B17" s="14" t="inlineStr">
-        <is>
-          <t>CSF_scRNA1</t>
-        </is>
-      </c>
-      <c r="C17" s="14" t="inlineStr">
-        <is>
-          <t>SPMS</t>
-        </is>
-      </c>
-      <c r="D17" s="14" t="inlineStr">
-        <is>
-          <t>MS</t>
-        </is>
-      </c>
-      <c r="E17" s="17" t="b">
-        <v>1</v>
-      </c>
-      <c r="F17" s="15" t="n">
-        <v>728</v>
-      </c>
-      <c r="G17" s="15" t="n">
-        <v>389</v>
-      </c>
-      <c r="H17" s="16" t="n">
-        <v>0.5997858345508575</v>
-      </c>
-      <c r="I17" s="17" t="n">
-        <v>0.7748550405297984</v>
-      </c>
-      <c r="J17" s="17" t="n">
-        <v>0.5439560439560439</v>
-      </c>
-      <c r="K17" s="17" t="n">
-        <v>0.2074175824175824</v>
-      </c>
-      <c r="L17" s="17" t="n">
-        <v>0.9134424652587104</v>
-      </c>
-      <c r="M17" s="17" t="n">
-        <v>0.4187935862053222</v>
-      </c>
-      <c r="N17" s="17" t="n">
-        <v>0.2967032967032967</v>
-      </c>
-      <c r="O17" s="17" t="n">
-        <v>0.1689560439560439</v>
-      </c>
-      <c r="P17" s="17" t="n">
-        <v>0.2307692307692307</v>
-      </c>
-      <c r="Q17" s="17" t="n">
-        <v>0.1701529260598254</v>
-      </c>
-      <c r="R17" s="17" t="n">
-        <v>0.4881098765848582</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="14" t="inlineStr">
-        <is>
-          <t>GSE286068</t>
-        </is>
-      </c>
-      <c r="B18" s="14" t="inlineStr">
-        <is>
-          <t>CSF_scRNA2</t>
-        </is>
-      </c>
-      <c r="C18" s="14" t="inlineStr">
-        <is>
-          <t>Healthy donor</t>
-        </is>
-      </c>
-      <c r="D18" s="14" t="inlineStr">
-        <is>
-          <t>non_inflammatory_control</t>
-        </is>
-      </c>
-      <c r="E18" s="17" t="b">
-        <v>0</v>
-      </c>
-      <c r="F18" s="15" t="n">
-        <v>41</v>
-      </c>
-      <c r="G18" s="15" t="n">
-        <v>14</v>
-      </c>
-      <c r="H18" s="16" t="n">
-        <v>0.3422777652740478</v>
-      </c>
-      <c r="I18" s="17" t="n">
-        <v>0.6970149012169717</v>
-      </c>
-      <c r="J18" s="17" t="n">
-        <v>0.3658536585365853</v>
-      </c>
-      <c r="K18" s="17" t="n">
-        <v>0.0975609756097561</v>
-      </c>
-      <c r="L18" s="17" t="n">
-        <v>0.8455809448471829</v>
-      </c>
-      <c r="M18" s="17" t="n">
-        <v>0.2733118147864035</v>
-      </c>
-      <c r="N18" s="17" t="n">
-        <v>0.1707317073170731</v>
-      </c>
-      <c r="O18" s="17" t="n">
-        <v>0.073170731707317</v>
-      </c>
-      <c r="P18" s="17" t="n">
-        <v>0.1707317073170731</v>
-      </c>
-      <c r="Q18" s="17" t="n">
-        <v>0.1655574052944729</v>
-      </c>
-      <c r="R18" s="17" t="n">
-        <v>0.3192465908402339</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="14" t="inlineStr">
-        <is>
-          <t>GSE286068</t>
-        </is>
-      </c>
-      <c r="B19" s="14" t="inlineStr">
-        <is>
-          <t>CSF_scRNA3</t>
-        </is>
-      </c>
-      <c r="C19" s="14" t="inlineStr">
-        <is>
-          <t>PPMS</t>
-        </is>
-      </c>
-      <c r="D19" s="14" t="inlineStr">
-        <is>
-          <t>MS</t>
-        </is>
-      </c>
-      <c r="E19" s="17" t="b">
-        <v>1</v>
-      </c>
-      <c r="F19" s="15" t="n">
-        <v>89</v>
-      </c>
-      <c r="G19" s="15" t="n">
-        <v>25</v>
-      </c>
-      <c r="H19" s="16" t="n">
-        <v>0.3939515948295593</v>
-      </c>
-      <c r="I19" s="17" t="n">
-        <v>0.6326510364738918</v>
-      </c>
-      <c r="J19" s="17" t="n">
-        <v>0.3932584269662921</v>
-      </c>
-      <c r="K19" s="17" t="n">
-        <v>0.06741573033707859</v>
-      </c>
-      <c r="L19" s="17" t="n">
-        <v>0.802680137648844</v>
-      </c>
-      <c r="M19" s="17" t="n">
-        <v>0.1608467642387713</v>
-      </c>
-      <c r="N19" s="17" t="n">
-        <v>0.1910112359550561</v>
-      </c>
-      <c r="O19" s="17" t="n">
-        <v>0.0561797752808988</v>
-      </c>
-      <c r="P19" s="17" t="n">
-        <v>0.1797752808988764</v>
-      </c>
-      <c r="Q19" s="17" t="n">
-        <v>0.1082742016432019</v>
-      </c>
-      <c r="R19" s="17" t="n">
-        <v>0.0488250755185672</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="14" t="inlineStr">
-        <is>
-          <t>GSE286068</t>
-        </is>
-      </c>
-      <c r="B20" s="14" t="inlineStr">
-        <is>
-          <t>CSF_scRNA4</t>
-        </is>
-      </c>
-      <c r="C20" s="14" t="inlineStr">
-        <is>
-          <t>RRMS</t>
-        </is>
-      </c>
-      <c r="D20" s="14" t="inlineStr">
-        <is>
-          <t>MS</t>
-        </is>
-      </c>
-      <c r="E20" s="17" t="b">
-        <v>1</v>
-      </c>
-      <c r="F20" s="15" t="n">
-        <v>70</v>
-      </c>
-      <c r="G20" s="15" t="n">
-        <v>12</v>
-      </c>
-      <c r="H20" s="16" t="n">
-        <v>0.618537425994873</v>
-      </c>
-      <c r="I20" s="17" t="n">
-        <v>0.5268656107461651</v>
-      </c>
-      <c r="J20" s="17" t="n">
-        <v>0.4285714285714285</v>
-      </c>
-      <c r="K20" s="17" t="n">
-        <v>0.1857142857142857</v>
-      </c>
-      <c r="L20" s="17" t="n">
-        <v>0.9495980808532662</v>
-      </c>
-      <c r="M20" s="17" t="n">
-        <v>0.2026318458375899</v>
-      </c>
-      <c r="N20" s="17" t="n">
-        <v>0.1857142857142857</v>
-      </c>
-      <c r="O20" s="17" t="n">
-        <v>0.0714285714285714</v>
-      </c>
-      <c r="P20" s="17" t="n">
-        <v>0.1571428571428571</v>
-      </c>
-      <c r="Q20" s="17" t="n">
-        <v>0.1396327721348046</v>
-      </c>
-      <c r="R20" s="17" t="n">
-        <v>0.155102366100338</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="14" t="inlineStr">
-        <is>
-          <t>GSE286068</t>
-        </is>
-      </c>
-      <c r="B21" s="14" t="inlineStr">
-        <is>
-          <t>CSF_scRNA5</t>
-        </is>
-      </c>
-      <c r="C21" s="14" t="inlineStr">
-        <is>
-          <t>RRMS</t>
-        </is>
-      </c>
-      <c r="D21" s="14" t="inlineStr">
-        <is>
-          <t>MS</t>
-        </is>
-      </c>
-      <c r="E21" s="17" t="b">
-        <v>1</v>
-      </c>
-      <c r="F21" s="15" t="n">
-        <v>114</v>
-      </c>
-      <c r="G21" s="15" t="n">
-        <v>14</v>
-      </c>
-      <c r="H21" s="16" t="n">
-        <v>0.4016943573951721</v>
-      </c>
-      <c r="I21" s="17" t="n">
-        <v>0.4842861533699787</v>
-      </c>
-      <c r="J21" s="17" t="n">
-        <v>0.4122807017543859</v>
-      </c>
-      <c r="K21" s="17" t="n">
-        <v>0.09649122807017541</v>
-      </c>
-      <c r="L21" s="17" t="n">
-        <v>0.8557298152653974</v>
-      </c>
-      <c r="M21" s="17" t="n">
-        <v>0.3202765985807498</v>
-      </c>
-      <c r="N21" s="17" t="n">
-        <v>0.2631578947368421</v>
-      </c>
-      <c r="O21" s="17" t="n">
-        <v>0.1052631578947368</v>
-      </c>
-      <c r="P21" s="17" t="n">
-        <v>0.2456140350877192</v>
-      </c>
-      <c r="Q21" s="17" t="n">
-        <v>0.1986555635879445</v>
-      </c>
-      <c r="R21" s="17" t="n">
-        <v>-0.0031839905108558</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="14" t="inlineStr">
-        <is>
-          <t>GSE286068</t>
-        </is>
-      </c>
-      <c r="B22" s="14" t="inlineStr">
-        <is>
-          <t>CSF_scRNA6</t>
-        </is>
-      </c>
-      <c r="C22" s="14" t="inlineStr">
-        <is>
-          <t>PPMS</t>
-        </is>
-      </c>
-      <c r="D22" s="14" t="inlineStr">
-        <is>
-          <t>MS</t>
-        </is>
-      </c>
-      <c r="E22" s="17" t="b">
-        <v>1</v>
-      </c>
-      <c r="F22" s="15" t="n">
-        <v>133</v>
-      </c>
-      <c r="G22" s="15" t="n">
-        <v>28</v>
-      </c>
-      <c r="H22" s="16" t="n">
-        <v>0.2911870777606964</v>
-      </c>
-      <c r="I22" s="17" t="n">
-        <v>0.6466197147805202</v>
-      </c>
-      <c r="J22" s="17" t="n">
-        <v>0.2330827067669172</v>
-      </c>
-      <c r="K22" s="17" t="n">
-        <v>0.037593984962406</v>
-      </c>
-      <c r="L22" s="17" t="n">
-        <v>0.6307935682526351</v>
-      </c>
-      <c r="M22" s="17" t="n">
-        <v>1.008501339409448</v>
-      </c>
-      <c r="N22" s="17" t="n">
-        <v>0.5714285714285714</v>
-      </c>
-      <c r="O22" s="17" t="n">
-        <v>0.1353383458646616</v>
-      </c>
-      <c r="P22" s="17" t="n">
-        <v>0.5639097744360902</v>
-      </c>
-      <c r="Q22" s="17" t="n">
-        <v>0.692925050877644</v>
-      </c>
-      <c r="R22" s="17" t="n">
-        <v>0.8508070252186569</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="14" t="inlineStr">
-        <is>
-          <t>GSE286068</t>
-        </is>
-      </c>
-      <c r="B23" s="14" t="inlineStr">
-        <is>
-          <t>CSF_scRNA7</t>
-        </is>
-      </c>
-      <c r="C23" s="14" t="inlineStr">
-        <is>
-          <t>NIND</t>
-        </is>
-      </c>
-      <c r="D23" s="14" t="inlineStr">
-        <is>
-          <t>non_inflammatory_control</t>
-        </is>
-      </c>
-      <c r="E23" s="17" t="b">
-        <v>0</v>
-      </c>
-      <c r="F23" s="15" t="n">
-        <v>81</v>
-      </c>
-      <c r="G23" s="15" t="n">
-        <v>22</v>
-      </c>
-      <c r="H23" s="16" t="n">
-        <v>0.6219676733016968</v>
-      </c>
-      <c r="I23" s="17" t="n">
-        <v>0.3658678556878475</v>
-      </c>
-      <c r="J23" s="17" t="n">
-        <v>0.6049382716049383</v>
-      </c>
-      <c r="K23" s="17" t="n">
-        <v>0.1481481481481481</v>
-      </c>
-      <c r="L23" s="17" t="n">
-        <v>0.8486313325833185</v>
-      </c>
-      <c r="M23" s="17" t="n">
-        <v>0.0553154388295231</v>
-      </c>
-      <c r="N23" s="17" t="n">
-        <v>0.1481481481481481</v>
-      </c>
-      <c r="O23" s="17" t="n">
-        <v>0.074074074074074</v>
-      </c>
-      <c r="P23" s="17" t="n">
-        <v>0.0987654320987654</v>
-      </c>
-      <c r="Q23" s="17" t="n">
-        <v>0.0191025192646052</v>
-      </c>
-      <c r="R23" s="17" t="n">
-        <v>-0.0394997549569814</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="14" t="inlineStr">
-        <is>
-          <t>GSE286068</t>
-        </is>
-      </c>
-      <c r="B24" s="14" t="inlineStr">
-        <is>
-          <t>CSF_scRNA8</t>
-        </is>
-      </c>
-      <c r="C24" s="14" t="inlineStr">
-        <is>
-          <t>Healthy donor</t>
-        </is>
-      </c>
-      <c r="D24" s="14" t="inlineStr">
-        <is>
-          <t>non_inflammatory_control</t>
-        </is>
-      </c>
-      <c r="E24" s="17" t="b">
-        <v>0</v>
-      </c>
-      <c r="F24" s="15" t="n">
-        <v>20</v>
-      </c>
-      <c r="G24" s="15" t="n">
-        <v>7</v>
-      </c>
-      <c r="H24" s="16" t="n">
-        <v>0.7350404262542725</v>
-      </c>
-      <c r="I24" s="17" t="n">
-        <v>0.4168773682136881</v>
-      </c>
-      <c r="J24" s="17" t="n">
-        <v>0.65</v>
-      </c>
-      <c r="K24" s="17" t="n">
-        <v>0.15</v>
-      </c>
-      <c r="L24" s="17" t="n">
-        <v>0.8068947387749437</v>
-      </c>
-      <c r="M24" s="17" t="n">
-        <v>0.1164619948809993</v>
-      </c>
-      <c r="N24" s="17" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="O24" s="17" t="n">
-        <v>0.15</v>
-      </c>
-      <c r="P24" s="17" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="Q24" s="17" t="n">
-        <v>0.0380519642966923</v>
-      </c>
-      <c r="R24" s="17" t="n">
-        <v>0.0903057638965348</v>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="14" t="inlineStr">
-        <is>
-          <t>GSE286068</t>
-        </is>
-      </c>
-      <c r="B25" s="14" t="inlineStr">
-        <is>
-          <t>CSF_scRNA9</t>
-        </is>
-      </c>
-      <c r="C25" s="14" t="inlineStr">
-        <is>
-          <t>RRMS</t>
-        </is>
-      </c>
-      <c r="D25" s="14" t="inlineStr">
-        <is>
-          <t>MS</t>
-        </is>
-      </c>
-      <c r="E25" s="17" t="b">
-        <v>1</v>
-      </c>
-      <c r="F25" s="15" t="n">
-        <v>58</v>
-      </c>
-      <c r="G25" s="15" t="n">
-        <v>14</v>
-      </c>
-      <c r="H25" s="16" t="n">
-        <v>0.5796217322349548</v>
-      </c>
-      <c r="I25" s="17" t="n">
-        <v>0.5071729827569086</v>
-      </c>
-      <c r="J25" s="17" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="K25" s="17" t="n">
-        <v>0.1551724137931034</v>
-      </c>
-      <c r="L25" s="17" t="n">
-        <v>0.9128200510540844</v>
-      </c>
-      <c r="M25" s="17" t="n">
-        <v>0.2380087042917587</v>
-      </c>
-      <c r="N25" s="17" t="n">
-        <v>0.2068965517241379</v>
-      </c>
-      <c r="O25" s="17" t="n">
-        <v>0.0862068965517241</v>
-      </c>
-      <c r="P25" s="17" t="n">
-        <v>0.2068965517241379</v>
-      </c>
-      <c r="Q25" s="17" t="n">
-        <v>0.1993796407403401</v>
-      </c>
-      <c r="R25" s="17" t="n">
-        <v>0.1921966040739485</v>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="14" t="inlineStr">
-        <is>
-          <t>GSE286068</t>
-        </is>
-      </c>
-      <c r="B26" s="14" t="inlineStr">
-        <is>
-          <t>CSF_scRNA10</t>
-        </is>
-      </c>
-      <c r="C26" s="14" t="inlineStr">
-        <is>
-          <t>Healthy donor</t>
-        </is>
-      </c>
-      <c r="D26" s="14" t="inlineStr">
-        <is>
-          <t>non_inflammatory_control</t>
-        </is>
-      </c>
-      <c r="E26" s="17" t="b">
-        <v>0</v>
-      </c>
-      <c r="F26" s="15" t="n">
-        <v>183</v>
-      </c>
-      <c r="G26" s="15" t="n">
-        <v>11</v>
-      </c>
-      <c r="H26" s="16" t="n">
-        <v>0.8800538778305054</v>
-      </c>
-      <c r="I26" s="17" t="n">
-        <v>0.3447361317897924</v>
-      </c>
-      <c r="J26" s="17" t="n">
-        <v>0.2622950819672131</v>
-      </c>
-      <c r="K26" s="17" t="n">
-        <v>0.5737704918032787</v>
-      </c>
-      <c r="L26" s="17" t="n">
-        <v>0.8794828859471613</v>
-      </c>
-      <c r="M26" s="17" t="n">
-        <v>0.3274761840682968</v>
-      </c>
-      <c r="N26" s="17" t="n">
-        <v>0.3005464480874317</v>
-      </c>
-      <c r="O26" s="17" t="n">
-        <v>0.081967213114754</v>
-      </c>
-      <c r="P26" s="17" t="n">
-        <v>0.1420765027322404</v>
-      </c>
-      <c r="Q26" s="17" t="n">
-        <v>0.1109551965045805</v>
-      </c>
-      <c r="R26" s="17" t="n">
-        <v>0.2940583891118342</v>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="14" t="inlineStr">
-        <is>
-          <t>GSE286068</t>
-        </is>
-      </c>
-      <c r="B27" s="14" t="inlineStr">
-        <is>
-          <t>CSF_scRNA11</t>
-        </is>
-      </c>
-      <c r="C27" s="14" t="inlineStr">
-        <is>
-          <t>PPMS</t>
-        </is>
-      </c>
-      <c r="D27" s="14" t="inlineStr">
-        <is>
-          <t>MS</t>
-        </is>
-      </c>
-      <c r="E27" s="17" t="b">
-        <v>1</v>
-      </c>
-      <c r="F27" s="15" t="n">
-        <v>22</v>
-      </c>
-      <c r="G27" s="15" t="n">
-        <v>2</v>
-      </c>
-      <c r="H27" s="16" t="n">
-        <v>0.4797279387712478</v>
-      </c>
-      <c r="I27" s="17" t="n">
-        <v>0.449901944126573</v>
-      </c>
-      <c r="J27" s="17" t="n">
-        <v>0.2727272727272727</v>
-      </c>
-      <c r="K27" s="17" t="n">
-        <v>0.2727272727272727</v>
-      </c>
-      <c r="L27" s="17" t="n">
-        <v>0.9713067383178074</v>
-      </c>
-      <c r="M27" s="17" t="n">
-        <v>0.4123518802878557</v>
-      </c>
-      <c r="N27" s="17" t="n">
-        <v>0.3636363636363636</v>
-      </c>
-      <c r="O27" s="17" t="n">
-        <v>0.0909090909090909</v>
-      </c>
-      <c r="P27" s="17" t="n">
-        <v>0.3636363636363636</v>
-      </c>
-      <c r="Q27" s="17" t="n">
-        <v>0.2759952144058636</v>
-      </c>
-      <c r="R27" s="17" t="n">
-        <v>0.8380995515124885</v>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="14" t="inlineStr">
-        <is>
-          <t>GSE286068</t>
-        </is>
-      </c>
-      <c r="B28" s="14" t="inlineStr">
-        <is>
-          <t>CSF_scRNA12</t>
-        </is>
-      </c>
-      <c r="C28" s="14" t="inlineStr">
-        <is>
-          <t>PPMS</t>
-        </is>
-      </c>
-      <c r="D28" s="14" t="inlineStr">
-        <is>
-          <t>MS</t>
-        </is>
-      </c>
-      <c r="E28" s="17" t="b">
-        <v>1</v>
-      </c>
-      <c r="F28" s="15" t="n">
-        <v>189</v>
-      </c>
-      <c r="G28" s="15" t="n">
-        <v>40</v>
-      </c>
-      <c r="H28" s="16" t="n">
-        <v>0.6675202250480652</v>
-      </c>
-      <c r="I28" s="17" t="n">
-        <v>0.5559965982651031</v>
-      </c>
-      <c r="J28" s="17" t="n">
-        <v>0.3915343915343915</v>
-      </c>
-      <c r="K28" s="17" t="n">
-        <v>0.2592592592592592</v>
-      </c>
-      <c r="L28" s="17" t="n">
-        <v>0.9871662954233866</v>
-      </c>
-      <c r="M28" s="17" t="n">
-        <v>0.564363852940945</v>
-      </c>
-      <c r="N28" s="17" t="n">
-        <v>0.4074074074074074</v>
-      </c>
-      <c r="O28" s="17" t="n">
-        <v>0.1693121693121693</v>
-      </c>
-      <c r="P28" s="17" t="n">
-        <v>0.3121693121693121</v>
-      </c>
-      <c r="Q28" s="17" t="n">
-        <v>0.2666097764176057</v>
-      </c>
-      <c r="R28" s="17" t="n">
-        <v>0.735813608530019</v>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="14" t="inlineStr">
-        <is>
-          <t>GSE286068</t>
-        </is>
-      </c>
-      <c r="B29" s="14" t="inlineStr">
-        <is>
-          <t>CSF_scRNA13</t>
-        </is>
-      </c>
-      <c r="C29" s="14" t="inlineStr">
-        <is>
-          <t>PPMS</t>
-        </is>
-      </c>
-      <c r="D29" s="14" t="inlineStr">
-        <is>
-          <t>MS</t>
-        </is>
-      </c>
-      <c r="E29" s="17" t="b">
-        <v>1</v>
-      </c>
-      <c r="F29" s="15" t="n">
-        <v>92</v>
-      </c>
-      <c r="G29" s="15" t="n">
-        <v>14</v>
-      </c>
-      <c r="H29" s="16" t="n">
-        <v>0.7560646831989288</v>
-      </c>
-      <c r="I29" s="17" t="n">
-        <v>0.3412892983270439</v>
-      </c>
-      <c r="J29" s="17" t="n">
-        <v>0.4565217391304347</v>
-      </c>
-      <c r="K29" s="17" t="n">
-        <v>0.3478260869565217</v>
-      </c>
-      <c r="L29" s="17" t="n">
-        <v>0.9507269107073124</v>
-      </c>
-      <c r="M29" s="17" t="n">
-        <v>0.330206385875139</v>
-      </c>
-      <c r="N29" s="17" t="n">
-        <v>0.3043478260869565</v>
-      </c>
-      <c r="O29" s="17" t="n">
-        <v>0.1304347826086956</v>
-      </c>
-      <c r="P29" s="17" t="n">
-        <v>0.2065217391304347</v>
-      </c>
-      <c r="Q29" s="17" t="n">
-        <v>0.1522179888706367</v>
-      </c>
-      <c r="R29" s="17" t="n">
-        <v>0.2388277001697936</v>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="14" t="inlineStr">
-        <is>
-          <t>GSE286068</t>
-        </is>
-      </c>
-      <c r="B30" s="14" t="inlineStr">
-        <is>
-          <t>CSF_scRNA14</t>
-        </is>
-      </c>
-      <c r="C30" s="14" t="inlineStr">
-        <is>
-          <t>Healthy donor</t>
-        </is>
-      </c>
-      <c r="D30" s="14" t="inlineStr">
-        <is>
-          <t>non_inflammatory_control</t>
-        </is>
-      </c>
-      <c r="E30" s="17" t="b">
-        <v>0</v>
-      </c>
-      <c r="F30" s="15" t="n">
-        <v>30</v>
-      </c>
-      <c r="G30" s="15" t="n">
-        <v>1</v>
-      </c>
-      <c r="H30" s="16" t="n">
-        <v>0.8058625161647797</v>
-      </c>
-      <c r="I30" s="17" t="n">
-        <v>0.3387421408871653</v>
-      </c>
-      <c r="J30" s="17" t="n">
-        <v>0.4666666666666667</v>
-      </c>
-      <c r="K30" s="17" t="n">
-        <v>0.5333333333333333</v>
-      </c>
-      <c r="L30" s="17" t="n">
-        <v>0.6289054987282648</v>
-      </c>
-      <c r="M30" s="17" t="n">
-        <v>0.3553199739134677</v>
-      </c>
-      <c r="N30" s="17" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="O30" s="17" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="P30" s="17" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="Q30" s="17" t="n">
-        <v>0.0697069023409308</v>
-      </c>
-      <c r="R30" s="17" t="n">
-        <v>-0.1023933917132645</v>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="14" t="inlineStr">
-        <is>
-          <t>GSE286068</t>
-        </is>
-      </c>
-      <c r="B31" s="14" t="inlineStr">
-        <is>
-          <t>CSF_scRNA15</t>
-        </is>
-      </c>
-      <c r="C31" s="14" t="inlineStr">
-        <is>
-          <t>RRMS</t>
-        </is>
-      </c>
-      <c r="D31" s="14" t="inlineStr">
-        <is>
-          <t>MS</t>
-        </is>
-      </c>
-      <c r="E31" s="17" t="b">
-        <v>1</v>
-      </c>
-      <c r="F31" s="15" t="n">
-        <v>5</v>
-      </c>
-      <c r="G31" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="H31" s="16" t="n">
-        <v>0.8545821905136108</v>
-      </c>
-      <c r="I31" s="17" t="n">
-        <v>0.3448569578434649</v>
-      </c>
-      <c r="J31" s="17" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="K31" s="17" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="L31" s="17" t="n">
-        <v>0.4554859150035952</v>
-      </c>
-      <c r="M31" s="17" t="n">
-        <v>1.004344821845164</v>
-      </c>
-      <c r="N31" s="17" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="O31" s="17" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="P31" s="17" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="Q31" s="17" t="n">
-        <v>0.2204508163942505</v>
-      </c>
-      <c r="R31" s="17" t="n"/>
-    </row>
-  </sheetData>
-  <autoFilter ref="A4:R31"/>
-  <mergeCells count="2">
-    <mergeCell ref="A2:R2"/>
-    <mergeCell ref="A1:R1"/>
-  </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
-  <tableParts count="1">
-    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
-  </tableParts>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr fitToPage="1"/>
-  </sheetPr>
-  <dimension ref="A1:K26"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="11" customWidth="1" min="1" max="1"/>
-    <col width="37" customWidth="1" min="2" max="2"/>
-    <col width="9" customWidth="1" min="3" max="3"/>
-    <col width="11" customWidth="1" min="4" max="4"/>
-    <col width="20" customWidth="1" min="5" max="5"/>
-    <col width="20" customWidth="1" min="6" max="6"/>
-    <col width="34" customWidth="1" min="7" max="7"/>
-    <col width="30" customWidth="1" min="8" max="8"/>
-    <col width="21" customWidth="1" min="9" max="9"/>
-    <col width="21" customWidth="1" min="10" max="10"/>
-    <col width="23" customWidth="1" min="11" max="11"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="24" customHeight="1">
-      <c r="A1" s="11" t="inlineStr">
-        <is>
-          <t>Within-cohort disease tests for the two-axis endpoints.</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="26" customHeight="1">
-      <c r="A2" s="12" t="inlineStr">
-        <is>
-          <t>Source: results/two_axis/two_axis_disease_tests.csv</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="30" customHeight="1">
-      <c r="A4" s="13" t="inlineStr">
-        <is>
-          <t>dataset</t>
-        </is>
-      </c>
-      <c r="B4" s="13" t="inlineStr">
-        <is>
-          <t>metric</t>
-        </is>
-      </c>
-      <c r="C4" s="13" t="inlineStr">
-        <is>
-          <t>n_MS</t>
-        </is>
-      </c>
-      <c r="D4" s="13" t="inlineStr">
-        <is>
-          <t>n_control</t>
-        </is>
-      </c>
-      <c r="E4" s="13" t="inlineStr">
-        <is>
-          <t>mean_MS</t>
-        </is>
-      </c>
-      <c r="F4" s="13" t="inlineStr">
-        <is>
-          <t>mean_control</t>
-        </is>
-      </c>
-      <c r="G4" s="13" t="inlineStr">
-        <is>
-          <t>mean_difference_MS_minus_control</t>
-        </is>
-      </c>
-      <c r="H4" s="13" t="inlineStr">
-        <is>
-          <t>standardized_mean_difference</t>
-        </is>
-      </c>
-      <c r="I4" s="13" t="inlineStr">
-        <is>
-          <t>cliffs_delta</t>
-        </is>
-      </c>
-      <c r="J4" s="13" t="inlineStr">
-        <is>
-          <t>exact_permutation_p</t>
-        </is>
-      </c>
-      <c r="K4" s="13" t="inlineStr">
-        <is>
-          <t>fdr_bh_within_dataset</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="14" t="inlineStr">
-        <is>
-          <t>GSE138266</t>
-        </is>
-      </c>
-      <c r="B5" s="14" t="inlineStr">
-        <is>
-          <t>median_consensus_pseudotime</t>
-        </is>
-      </c>
-      <c r="C5" s="15" t="n">
-        <v>6</v>
-      </c>
-      <c r="D5" s="15" t="n">
-        <v>5</v>
-      </c>
-      <c r="E5" s="17" t="n">
-        <v>0.795679584145546</v>
-      </c>
-      <c r="F5" s="17" t="n">
-        <v>0.8434525787830353</v>
-      </c>
-      <c r="G5" s="17" t="n">
-        <v>-0.0477729946374893</v>
-      </c>
-      <c r="H5" s="17" t="n">
-        <v>-1.047498152877157</v>
-      </c>
-      <c r="I5" s="17" t="n">
-        <v>-0.6</v>
-      </c>
-      <c r="J5" s="16" t="n">
-        <v>0.1038961038961039</v>
-      </c>
-      <c r="K5" s="16" t="n">
-        <v>0.2182539682539682</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="14" t="inlineStr">
-        <is>
-          <t>GSE138266</t>
-        </is>
-      </c>
-      <c r="B6" s="14" t="inlineStr">
-        <is>
-          <t>median_BAM_macrostate_membership</t>
-        </is>
-      </c>
-      <c r="C6" s="15" t="n">
-        <v>6</v>
-      </c>
-      <c r="D6" s="15" t="n">
-        <v>5</v>
-      </c>
-      <c r="E6" s="17" t="n">
-        <v>0.4019383687918313</v>
-      </c>
-      <c r="F6" s="17" t="n">
-        <v>0.551757545301317</v>
-      </c>
-      <c r="G6" s="17" t="n">
-        <v>-0.1498191765094856</v>
-      </c>
-      <c r="H6" s="17" t="n">
-        <v>-0.9143769395948432</v>
-      </c>
-      <c r="I6" s="17" t="n">
-        <v>-0.5333333333333333</v>
-      </c>
-      <c r="J6" s="16" t="n">
-        <v>0.1991341991341991</v>
-      </c>
-      <c r="K6" s="16" t="n">
-        <v>0.219047619047619</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="14" t="inlineStr">
-        <is>
-          <t>GSE138266</t>
-        </is>
-      </c>
-      <c r="B7" s="14" t="inlineStr">
-        <is>
-          <t>transitional_fraction</t>
-        </is>
-      </c>
-      <c r="C7" s="15" t="n">
-        <v>6</v>
-      </c>
-      <c r="D7" s="15" t="n">
-        <v>5</v>
-      </c>
-      <c r="E7" s="17" t="n">
-        <v>0.5347073760756625</v>
-      </c>
-      <c r="F7" s="17" t="n">
-        <v>0.3814985761951993</v>
-      </c>
-      <c r="G7" s="17" t="n">
-        <v>0.1532087998804632</v>
-      </c>
-      <c r="H7" s="17" t="n">
-        <v>1.058153049767358</v>
-      </c>
-      <c r="I7" s="17" t="n">
-        <v>0.5333333333333333</v>
-      </c>
-      <c r="J7" s="16" t="n">
-        <v>0.119047619047619</v>
-      </c>
-      <c r="K7" s="16" t="n">
-        <v>0.2182539682539682</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="14" t="inlineStr">
-        <is>
-          <t>GSE138266</t>
-        </is>
-      </c>
-      <c r="B8" s="14" t="inlineStr">
-        <is>
-          <t>terminal_fraction</t>
-        </is>
-      </c>
-      <c r="C8" s="15" t="n">
-        <v>6</v>
-      </c>
-      <c r="D8" s="15" t="n">
-        <v>5</v>
-      </c>
-      <c r="E8" s="17" t="n">
-        <v>0.4575027688518737</v>
-      </c>
-      <c r="F8" s="17" t="n">
-        <v>0.6140950648960753</v>
-      </c>
-      <c r="G8" s="17" t="n">
-        <v>-0.1565922960442016</v>
-      </c>
-      <c r="H8" s="17" t="n">
-        <v>-1.122739571999737</v>
-      </c>
-      <c r="I8" s="17" t="n">
-        <v>-0.4666666666666667</v>
-      </c>
-      <c r="J8" s="16" t="n">
-        <v>0.1038961038961039</v>
-      </c>
-      <c r="K8" s="16" t="n">
-        <v>0.2182539682539682</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="14" t="inlineStr">
-        <is>
-          <t>GSE138266</t>
-        </is>
-      </c>
-      <c r="B9" s="14" t="inlineStr">
-        <is>
-          <t>transition_entropy</t>
-        </is>
-      </c>
-      <c r="C9" s="15" t="n">
-        <v>6</v>
-      </c>
-      <c r="D9" s="15" t="n">
-        <v>5</v>
-      </c>
-      <c r="E9" s="17" t="n">
-        <v>0.618992187583871</v>
-      </c>
-      <c r="F9" s="17" t="n">
-        <v>0.6032281669749592</v>
-      </c>
-      <c r="G9" s="17" t="n">
-        <v>0.0157640206089118</v>
-      </c>
-      <c r="H9" s="17" t="n">
-        <v>0.257018582726258</v>
-      </c>
-      <c r="I9" s="17" t="n">
-        <v>0.1333333333333333</v>
-      </c>
-      <c r="J9" s="16" t="n">
-        <v>0.6796536796536796</v>
-      </c>
-      <c r="K9" s="16" t="n">
-        <v>0.6796536796536796</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="14" t="inlineStr">
-        <is>
-          <t>GSE138266</t>
-        </is>
-      </c>
-      <c r="B10" s="14" t="inlineStr">
-        <is>
-          <t>mean_activation_residual</t>
-        </is>
-      </c>
-      <c r="C10" s="15" t="n">
-        <v>6</v>
-      </c>
-      <c r="D10" s="15" t="n">
-        <v>5</v>
-      </c>
-      <c r="E10" s="17" t="n">
-        <v>0.6579454611987335</v>
-      </c>
-      <c r="F10" s="17" t="n">
-        <v>0.3078314290894995</v>
-      </c>
-      <c r="G10" s="17" t="n">
-        <v>0.350114032109234</v>
-      </c>
-      <c r="H10" s="17" t="n">
-        <v>0.9088937157036748</v>
-      </c>
-      <c r="I10" s="17" t="n">
-        <v>0.5333333333333333</v>
-      </c>
-      <c r="J10" s="16" t="n">
-        <v>0.1688311688311688</v>
-      </c>
-      <c r="K10" s="16" t="n">
-        <v>0.219047619047619</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="14" t="inlineStr">
-        <is>
-          <t>GSE138266</t>
-        </is>
-      </c>
-      <c r="B11" s="14" t="inlineStr">
-        <is>
-          <t>high_activation_fraction</t>
-        </is>
-      </c>
-      <c r="C11" s="15" t="n">
-        <v>6</v>
-      </c>
-      <c r="D11" s="15" t="n">
-        <v>5</v>
-      </c>
-      <c r="E11" s="17" t="n">
-        <v>0.4627986534636151</v>
-      </c>
-      <c r="F11" s="17" t="n">
-        <v>0.2964643783872943</v>
-      </c>
-      <c r="G11" s="17" t="n">
-        <v>0.1663342750763207</v>
-      </c>
-      <c r="H11" s="17" t="n">
-        <v>0.9710602973417466</v>
-      </c>
-      <c r="I11" s="17" t="n">
-        <v>0.4666666666666667</v>
-      </c>
-      <c r="J11" s="16" t="n">
-        <v>0.1406926406926407</v>
-      </c>
-      <c r="K11" s="16" t="n">
-        <v>0.219047619047619</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="14" t="inlineStr">
-        <is>
-          <t>GSE138266</t>
-        </is>
-      </c>
-      <c r="B12" s="14" t="inlineStr">
-        <is>
-          <t>activated_transition_fraction</t>
-        </is>
-      </c>
-      <c r="C12" s="15" t="n">
-        <v>6</v>
-      </c>
-      <c r="D12" s="15" t="n">
-        <v>5</v>
-      </c>
-      <c r="E12" s="17" t="n">
-        <v>0.2478587849112145</v>
-      </c>
-      <c r="F12" s="17" t="n">
-        <v>0.1160656160361475</v>
-      </c>
-      <c r="G12" s="17" t="n">
-        <v>0.1317931688750669</v>
-      </c>
-      <c r="H12" s="17" t="n">
-        <v>1.379987111160227</v>
-      </c>
-      <c r="I12" s="17" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="J12" s="16" t="n">
-        <v>0.0627705627705627</v>
-      </c>
-      <c r="K12" s="16" t="n">
-        <v>0.2182539682539682</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="14" t="inlineStr">
-        <is>
-          <t>GSE138266</t>
-        </is>
-      </c>
-      <c r="B13" s="14" t="inlineStr">
-        <is>
-          <t>decoupled_inflammatory_fraction</t>
-        </is>
-      </c>
-      <c r="C13" s="15" t="n">
-        <v>6</v>
-      </c>
-      <c r="D13" s="15" t="n">
-        <v>5</v>
-      </c>
-      <c r="E13" s="17" t="n">
-        <v>0.2556486399836783</v>
-      </c>
-      <c r="F13" s="17" t="n">
-        <v>0.1166354166059481</v>
-      </c>
-      <c r="G13" s="17" t="n">
-        <v>0.1390132233777301</v>
-      </c>
-      <c r="H13" s="17" t="n">
-        <v>1.455513463279578</v>
-      </c>
-      <c r="I13" s="17" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="J13" s="16" t="n">
-        <v>0.0519480519480519</v>
-      </c>
-      <c r="K13" s="16" t="n">
-        <v>0.2182539682539682</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="14" t="inlineStr">
-        <is>
-          <t>GSE138266</t>
-        </is>
-      </c>
-      <c r="B14" s="14" t="inlineStr">
-        <is>
-          <t>continuous_decoupling_index</t>
-        </is>
-      </c>
-      <c r="C14" s="15" t="n">
-        <v>6</v>
-      </c>
-      <c r="D14" s="15" t="n">
-        <v>5</v>
-      </c>
-      <c r="E14" s="17" t="n">
-        <v>0.1554466794298869</v>
-      </c>
-      <c r="F14" s="17" t="n">
-        <v>0.0573581795834328</v>
-      </c>
-      <c r="G14" s="17" t="n">
-        <v>0.0980884998464541</v>
-      </c>
-      <c r="H14" s="17" t="n">
-        <v>1.111696233922438</v>
-      </c>
-      <c r="I14" s="17" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="J14" s="16" t="n">
-        <v>0.1082251082251082</v>
-      </c>
-      <c r="K14" s="16" t="n">
-        <v>0.2182539682539682</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="14" t="inlineStr">
-        <is>
-          <t>GSE138266</t>
-        </is>
-      </c>
-      <c r="B15" s="14" t="inlineStr">
-        <is>
-          <t>strict_BAM_mean_activation_residual</t>
-        </is>
-      </c>
-      <c r="C15" s="15" t="n">
-        <v>6</v>
-      </c>
-      <c r="D15" s="15" t="n">
-        <v>5</v>
-      </c>
-      <c r="E15" s="17" t="n">
-        <v>0.6302376815741401</v>
-      </c>
-      <c r="F15" s="17" t="n">
-        <v>0.2766119271942608</v>
-      </c>
-      <c r="G15" s="17" t="n">
-        <v>0.3536257543798792</v>
-      </c>
-      <c r="H15" s="17" t="n">
-        <v>0.8760870859390878</v>
-      </c>
-      <c r="I15" s="17" t="n">
-        <v>0.5333333333333333</v>
-      </c>
-      <c r="J15" s="16" t="n">
-        <v>0.1861471861471861</v>
-      </c>
-      <c r="K15" s="16" t="n">
-        <v>0.219047619047619</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="14" t="inlineStr">
-        <is>
-          <t>GSE286068</t>
-        </is>
-      </c>
-      <c r="B16" s="14" t="inlineStr">
-        <is>
-          <t>median_consensus_pseudotime</t>
-        </is>
-      </c>
-      <c r="C16" s="15" t="n">
-        <v>9</v>
-      </c>
-      <c r="D16" s="15" t="n">
-        <v>5</v>
-      </c>
-      <c r="E16" s="17" t="n">
-        <v>0.5320100966427062</v>
-      </c>
-      <c r="F16" s="17" t="n">
-        <v>0.6770404517650604</v>
-      </c>
-      <c r="G16" s="17" t="n">
-        <v>-0.1450303551223543</v>
-      </c>
-      <c r="H16" s="17" t="n">
-        <v>-0.8420773687660105</v>
-      </c>
-      <c r="I16" s="17" t="n">
-        <v>-0.5111111111111111</v>
-      </c>
-      <c r="J16" s="16" t="n">
-        <v>0.1548451548451548</v>
-      </c>
-      <c r="K16" s="16" t="n">
-        <v>0.2781593406593406</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="14" t="inlineStr">
-        <is>
-          <t>GSE286068</t>
-        </is>
-      </c>
-      <c r="B17" s="14" t="inlineStr">
-        <is>
-          <t>median_BAM_macrostate_membership</t>
-        </is>
-      </c>
-      <c r="C17" s="15" t="n">
-        <v>9</v>
-      </c>
-      <c r="D17" s="15" t="n">
-        <v>5</v>
-      </c>
-      <c r="E17" s="17" t="n">
-        <v>0.5466264865973315</v>
-      </c>
-      <c r="F17" s="17" t="n">
-        <v>0.432647679559093</v>
-      </c>
-      <c r="G17" s="17" t="n">
-        <v>0.1139788070382384</v>
-      </c>
-      <c r="H17" s="17" t="n">
-        <v>0.8455016999799456</v>
-      </c>
-      <c r="I17" s="17" t="n">
-        <v>0.5111111111111111</v>
-      </c>
-      <c r="J17" s="16" t="n">
-        <v>0.1543456543456543</v>
-      </c>
-      <c r="K17" s="16" t="n">
-        <v>0.2781593406593406</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="14" t="inlineStr">
-        <is>
-          <t>GSE286068</t>
-        </is>
-      </c>
-      <c r="B18" s="14" t="inlineStr">
-        <is>
-          <t>transitional_fraction</t>
-        </is>
-      </c>
-      <c r="C18" s="15" t="n">
-        <v>9</v>
-      </c>
-      <c r="D18" s="15" t="n">
-        <v>5</v>
-      </c>
-      <c r="E18" s="17" t="n">
-        <v>0.4035480790452407</v>
-      </c>
-      <c r="F18" s="17" t="n">
-        <v>0.4699507357550807</v>
-      </c>
-      <c r="G18" s="17" t="n">
-        <v>-0.0664026567098399</v>
-      </c>
-      <c r="H18" s="17" t="n">
-        <v>-0.5368980483429732</v>
-      </c>
-      <c r="I18" s="17" t="n">
-        <v>-0.2444444444444444</v>
-      </c>
-      <c r="J18" s="16" t="n">
-        <v>0.3491508491508491</v>
-      </c>
-      <c r="K18" s="16" t="n">
-        <v>0.3840659340659341</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="14" t="inlineStr">
-        <is>
-          <t>GSE286068</t>
-        </is>
-      </c>
-      <c r="B19" s="14" t="inlineStr">
-        <is>
-          <t>terminal_fraction</t>
-        </is>
-      </c>
-      <c r="C19" s="15" t="n">
-        <v>9</v>
-      </c>
-      <c r="D19" s="15" t="n">
-        <v>5</v>
-      </c>
-      <c r="E19" s="17" t="n">
-        <v>0.1810686493597428</v>
-      </c>
-      <c r="F19" s="17" t="n">
-        <v>0.3005625897789032</v>
-      </c>
-      <c r="G19" s="17" t="n">
-        <v>-0.1194939404191604</v>
-      </c>
-      <c r="H19" s="17" t="n">
-        <v>-0.7553702401849812</v>
-      </c>
-      <c r="I19" s="17" t="n">
-        <v>-0.2</v>
-      </c>
-      <c r="J19" s="16" t="n">
-        <v>0.2022977022977023</v>
-      </c>
-      <c r="K19" s="16" t="n">
-        <v>0.2781593406593406</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="14" t="inlineStr">
-        <is>
-          <t>GSE286068</t>
-        </is>
-      </c>
-      <c r="B20" s="14" t="inlineStr">
-        <is>
-          <t>transition_entropy</t>
-        </is>
-      </c>
-      <c r="C20" s="15" t="n">
-        <v>9</v>
-      </c>
-      <c r="D20" s="15" t="n">
-        <v>5</v>
-      </c>
-      <c r="E20" s="17" t="n">
-        <v>0.8860293403090495</v>
-      </c>
-      <c r="F20" s="17" t="n">
-        <v>0.8018990801761742</v>
-      </c>
-      <c r="G20" s="17" t="n">
-        <v>0.0841302601328752</v>
-      </c>
-      <c r="H20" s="17" t="n">
-        <v>0.7781439174329958</v>
-      </c>
-      <c r="I20" s="17" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="J20" s="16" t="n">
-        <v>0.1923076923076923</v>
-      </c>
-      <c r="K20" s="16" t="n">
-        <v>0.2781593406593406</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="14" t="inlineStr">
-        <is>
-          <t>GSE286068</t>
-        </is>
-      </c>
-      <c r="B21" s="14" t="inlineStr">
-        <is>
-          <t>mean_activation_residual</t>
-        </is>
-      </c>
-      <c r="C21" s="15" t="n">
-        <v>9</v>
-      </c>
-      <c r="D21" s="15" t="n">
-        <v>5</v>
-      </c>
-      <c r="E21" s="17" t="n">
-        <v>0.4062201064075089</v>
-      </c>
-      <c r="F21" s="17" t="n">
-        <v>0.2255770812957381</v>
-      </c>
-      <c r="G21" s="17" t="n">
-        <v>0.1806430251117707</v>
-      </c>
-      <c r="H21" s="17" t="n">
-        <v>0.8068831507598295</v>
-      </c>
-      <c r="I21" s="17" t="n">
-        <v>0.4666666666666667</v>
-      </c>
-      <c r="J21" s="16" t="n">
-        <v>0.1688311688311688</v>
-      </c>
-      <c r="K21" s="16" t="n">
-        <v>0.2781593406593406</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="14" t="inlineStr">
-        <is>
-          <t>GSE286068</t>
-        </is>
-      </c>
-      <c r="B22" s="14" t="inlineStr">
-        <is>
-          <t>high_activation_fraction</t>
-        </is>
-      </c>
-      <c r="C22" s="15" t="n">
-        <v>9</v>
-      </c>
-      <c r="D22" s="15" t="n">
-        <v>5</v>
-      </c>
-      <c r="E22" s="17" t="n">
-        <v>0.3100337148214352</v>
-      </c>
-      <c r="F22" s="17" t="n">
-        <v>0.2438852607105305</v>
-      </c>
-      <c r="G22" s="17" t="n">
-        <v>0.0661484541109047</v>
-      </c>
-      <c r="H22" s="17" t="n">
-        <v>0.5968982341569586</v>
-      </c>
-      <c r="I22" s="17" t="n">
-        <v>0.3333333333333333</v>
-      </c>
-      <c r="J22" s="16" t="n">
-        <v>0.3106893106893107</v>
-      </c>
-      <c r="K22" s="16" t="n">
-        <v>0.3797313797313797</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="14" t="inlineStr">
-        <is>
-          <t>GSE286068</t>
-        </is>
-      </c>
-      <c r="B23" s="14" t="inlineStr">
-        <is>
-          <t>activated_transition_fraction</t>
-        </is>
-      </c>
-      <c r="C23" s="15" t="n">
-        <v>9</v>
-      </c>
-      <c r="D23" s="15" t="n">
-        <v>5</v>
-      </c>
-      <c r="E23" s="17" t="n">
-        <v>0.1126698704229547</v>
-      </c>
-      <c r="F23" s="17" t="n">
-        <v>0.09584240377922899</v>
-      </c>
-      <c r="G23" s="17" t="n">
-        <v>0.0168274666437257</v>
-      </c>
-      <c r="H23" s="17" t="n">
-        <v>0.4411849936241344</v>
-      </c>
-      <c r="I23" s="17" t="n">
-        <v>0.2444444444444444</v>
-      </c>
-      <c r="J23" s="16" t="n">
-        <v>0.4365634365634365</v>
-      </c>
-      <c r="K23" s="16" t="n">
-        <v>0.4365634365634365</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="14" t="inlineStr">
-        <is>
-          <t>GSE286068</t>
-        </is>
-      </c>
-      <c r="B24" s="14" t="inlineStr">
-        <is>
-          <t>decoupled_inflammatory_fraction</t>
-        </is>
-      </c>
-      <c r="C24" s="15" t="n">
-        <v>9</v>
-      </c>
-      <c r="D24" s="15" t="n">
-        <v>5</v>
-      </c>
-      <c r="E24" s="17" t="n">
-        <v>0.2740483494438913</v>
-      </c>
-      <c r="F24" s="17" t="n">
-        <v>0.1523147284296158</v>
-      </c>
-      <c r="G24" s="17" t="n">
-        <v>0.1217336210142755</v>
-      </c>
-      <c r="H24" s="17" t="n">
-        <v>1.113613640530996</v>
-      </c>
-      <c r="I24" s="17" t="n">
-        <v>0.6888888888888889</v>
-      </c>
-      <c r="J24" s="16" t="n">
-        <v>0.0559440559440559</v>
-      </c>
-      <c r="K24" s="16" t="n">
-        <v>0.2781593406593406</v>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="14" t="inlineStr">
-        <is>
-          <t>GSE286068</t>
-        </is>
-      </c>
-      <c r="B25" s="14" t="inlineStr">
-        <is>
-          <t>continuous_decoupling_index</t>
-        </is>
-      </c>
-      <c r="C25" s="15" t="n">
-        <v>9</v>
-      </c>
-      <c r="D25" s="15" t="n">
-        <v>5</v>
-      </c>
-      <c r="E25" s="17" t="n">
-        <v>0.2448714594153185</v>
-      </c>
-      <c r="F25" s="17" t="n">
-        <v>0.0806747975402563</v>
-      </c>
-      <c r="G25" s="17" t="n">
-        <v>0.1641966618750621</v>
-      </c>
-      <c r="H25" s="17" t="n">
-        <v>1.106698680091002</v>
-      </c>
-      <c r="I25" s="17" t="n">
-        <v>0.8222222222222222</v>
-      </c>
-      <c r="J25" s="16" t="n">
-        <v>0.0369630369630369</v>
-      </c>
-      <c r="K25" s="16" t="n">
-        <v>0.2781593406593406</v>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="14" t="inlineStr">
-        <is>
-          <t>GSE286068</t>
-        </is>
-      </c>
-      <c r="B26" s="14" t="inlineStr">
-        <is>
-          <t>strict_BAM_mean_activation_residual</t>
-        </is>
-      </c>
-      <c r="C26" s="15" t="n">
-        <v>9</v>
-      </c>
-      <c r="D26" s="15" t="n">
-        <v>5</v>
-      </c>
-      <c r="E26" s="17" t="n">
-        <v>0.3938442019108682</v>
-      </c>
-      <c r="F26" s="17" t="n">
-        <v>0.1123435194356714</v>
-      </c>
-      <c r="G26" s="17" t="n">
-        <v>0.2815006824751968</v>
-      </c>
-      <c r="H26" s="17" t="n">
-        <v>0.9401439885128992</v>
-      </c>
-      <c r="I26" s="17" t="n">
-        <v>0.4666666666666667</v>
-      </c>
-      <c r="J26" s="16" t="n">
-        <v>0.1208791208791208</v>
-      </c>
-      <c r="K26" s="16" t="n">
-        <v>0.2781593406593406</v>
-      </c>
-    </row>
-  </sheetData>
-  <autoFilter ref="A4:K26"/>
-  <mergeCells count="2">
-    <mergeCell ref="A2:K2"/>
-    <mergeCell ref="A1:K1"/>
-  </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
-  <tableParts count="1">
-    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
-  </tableParts>
-</worksheet>
 </file>